--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,6 +883,6649 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130222731</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92094</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>504091</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7022065</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130222714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91641</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>504091</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7021759</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130222749</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91655</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>504067</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7021774</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130222710</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91641</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>504160</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7021867</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130222716</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91641</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>504095</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7021805</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130222732</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92094</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>504202</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7022015</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130222712</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91641</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>504057</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7021765</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130222705</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>504210</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7022007</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130222701</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83073</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>504090</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7021787</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130222736</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91939</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>658</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>504081</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7021794</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130222702</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83073</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>504100</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7021801</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130222730</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80104</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>504166</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7021800</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130222713</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91641</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>504135</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7021768</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130222724</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57741</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>504139</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7021798</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130222711</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91641</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>504154</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7021848</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130222706</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>504083</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7021773</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130222700</v>
+      </c>
+      <c r="B20" t="n">
+        <v>83073</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>504099</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7021769</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130222727</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92364</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>67</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>504089</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7021772</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130222720</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57741</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>503952</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7022000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130222757</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>504170</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7021800</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130222725</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57900</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>504058</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7021715</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130222753</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>504059</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7021781</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130222755</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>504177</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7021847</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130222743</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91637</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>504223</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7022010</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130222750</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91661</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>504216</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7022005</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130222752</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>504097</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7021762</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130222722</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57741</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>503979</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7022007</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130222746</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91637</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>503973</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7021998</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130222734</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91939</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>658</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>504221</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7022011</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130222704</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>504208</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7022015</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130222719</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92359</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>504219</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7022014</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130222742</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91637</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>504227</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7022001</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130222715</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91641</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>504083</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7021787</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130222756</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>504101</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7021774</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130222718</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92359</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>504098</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7022064</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130222728</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80104</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>504090</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7021781</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130222709</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91641</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>504104</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7021877</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130222729</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80104</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>504173</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7021803</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130222708</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91641</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>504191</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7022006</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>130222735</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91939</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>658</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>504166</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7021986</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130222733</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92094</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>504161</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7021869</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130222744</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91637</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>504178</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7021976</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130222745</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91637</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>504130</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7021754</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130222726</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80229</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>504106</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7021741</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130222699</v>
+      </c>
+      <c r="B48" t="n">
+        <v>83073</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>504118</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7021776</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130222707</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>504161</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7021806</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130222758</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>504172</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7021818</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>130222738</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78107</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>504087</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7021791</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>130222703</v>
+      </c>
+      <c r="B52" t="n">
+        <v>83073</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>504170</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7021803</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>130222737</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78107</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>504108</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7021877</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>130222723</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57741</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>504117</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7021735</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>130222739</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98833</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>504054</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7021735</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor finns på fyndplatsen.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>130222747</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91655</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>504210</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7022007</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>130222754</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>504081</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7021796</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>130222751</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91661</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>504218</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7022019</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>130222721</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57741</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>503954</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7021984</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>130222748</v>
+      </c>
+      <c r="B60" t="n">
+        <v>91655</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>504123</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7021748</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>130222740</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98833</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>504087</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7021765</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Minst 8 plantor på fyndplatsen.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>130222741</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91637</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>504078</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7022057</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130222714</v>
+        <v>130222710</v>
       </c>
       <c r="B5" t="n">
         <v>91641</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504091</v>
+        <v>504160</v>
       </c>
       <c r="R5" t="n">
-        <v>7021759</v>
+        <v>7021867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130222710</v>
+        <v>130222714</v>
       </c>
       <c r="B7" t="n">
         <v>91641</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504160</v>
+        <v>504091</v>
       </c>
       <c r="R7" t="n">
-        <v>7021867</v>
+        <v>7021759</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,32 +1340,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130222716</v>
+        <v>130222732</v>
       </c>
       <c r="B8" t="n">
-        <v>91641</v>
+        <v>92094</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504095</v>
+        <v>504202</v>
       </c>
       <c r="R8" t="n">
-        <v>7021805</v>
+        <v>7022015</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,6 +1433,21 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1450,32 +1465,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130222732</v>
+        <v>130222712</v>
       </c>
       <c r="B9" t="n">
-        <v>92094</v>
+        <v>91641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504202</v>
+        <v>504057</v>
       </c>
       <c r="R9" t="n">
-        <v>7022015</v>
+        <v>7021765</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,21 +1558,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1575,7 +1575,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130222712</v>
+        <v>130222716</v>
       </c>
       <c r="B10" t="n">
         <v>91641</v>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504057</v>
+        <v>504095</v>
       </c>
       <c r="R10" t="n">
-        <v>7021765</v>
+        <v>7021805</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,32 +1685,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130222705</v>
+        <v>130222736</v>
       </c>
       <c r="B11" t="n">
-        <v>91605</v>
+        <v>91939</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504210</v>
+        <v>504081</v>
       </c>
       <c r="R11" t="n">
-        <v>7022007</v>
+        <v>7021794</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,37 +1795,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130222701</v>
+        <v>130222705</v>
       </c>
       <c r="B12" t="n">
-        <v>83073</v>
+        <v>91605</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1833,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504090</v>
+        <v>504210</v>
       </c>
       <c r="R12" t="n">
-        <v>7021787</v>
+        <v>7022007</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,10 +1905,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130222736</v>
+        <v>130222701</v>
       </c>
       <c r="B13" t="n">
-        <v>91939</v>
+        <v>83073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1912,30 +1916,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504081</v>
+        <v>504090</v>
       </c>
       <c r="R13" t="n">
-        <v>7021794</v>
+        <v>7021787</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130222702</v>
+        <v>130222724</v>
       </c>
       <c r="B14" t="n">
-        <v>83073</v>
+        <v>57741</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,26 +2022,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2049,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504100</v>
+        <v>504139</v>
       </c>
       <c r="R14" t="n">
-        <v>7021801</v>
+        <v>7021798</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2087,13 +2092,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2117,37 +2126,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222730</v>
+        <v>130222713</v>
       </c>
       <c r="B15" t="n">
-        <v>80104</v>
+        <v>91641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2155,10 +2168,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504166</v>
+        <v>504135</v>
       </c>
       <c r="R15" t="n">
-        <v>7021800</v>
+        <v>7021768</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,7 +2236,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130222713</v>
+        <v>130222711</v>
       </c>
       <c r="B16" t="n">
         <v>91641</v>
@@ -2265,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504135</v>
+        <v>504154</v>
       </c>
       <c r="R16" t="n">
-        <v>7021768</v>
+        <v>7021848</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2333,10 +2346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130222724</v>
+        <v>130222702</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>83073</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2344,31 +2357,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2376,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>504139</v>
+        <v>504100</v>
       </c>
       <c r="R17" t="n">
-        <v>7021798</v>
+        <v>7021801</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2414,17 +2422,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2448,41 +2452,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130222711</v>
+        <v>130222730</v>
       </c>
       <c r="B18" t="n">
-        <v>91641</v>
+        <v>80104</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504154</v>
+        <v>504166</v>
       </c>
       <c r="R18" t="n">
-        <v>7021848</v>
+        <v>7021800</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,32 +2558,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130222706</v>
+        <v>130222727</v>
       </c>
       <c r="B19" t="n">
-        <v>91605</v>
+        <v>92364</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>67</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504083</v>
+        <v>504089</v>
       </c>
       <c r="R19" t="n">
-        <v>7021773</v>
+        <v>7021772</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2651,6 +2651,21 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2668,37 +2683,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130222700</v>
+        <v>130222706</v>
       </c>
       <c r="B20" t="n">
-        <v>83073</v>
+        <v>91605</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2706,10 +2725,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504099</v>
+        <v>504083</v>
       </c>
       <c r="R20" t="n">
-        <v>7021769</v>
+        <v>7021773</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,41 +2793,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130222727</v>
+        <v>130222700</v>
       </c>
       <c r="B21" t="n">
-        <v>92364</v>
+        <v>83073</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>67</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2816,10 +2831,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>504089</v>
+        <v>504099</v>
       </c>
       <c r="R21" t="n">
-        <v>7021772</v>
+        <v>7021769</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2867,21 +2882,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130222720</v>
+        <v>130222753</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,31 +2910,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2942,10 +2937,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503952</v>
+        <v>504059</v>
       </c>
       <c r="R22" t="n">
-        <v>7022000</v>
+        <v>7021781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2980,17 +2975,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3120,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130222725</v>
+        <v>130222720</v>
       </c>
       <c r="B24" t="n">
-        <v>57900</v>
+        <v>57741</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,50 +3122,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504058</v>
+        <v>503952</v>
       </c>
       <c r="R24" t="n">
-        <v>7021715</v>
+        <v>7022000</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3207,6 +3190,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3238,10 +3226,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130222753</v>
+        <v>130222725</v>
       </c>
       <c r="B25" t="n">
-        <v>79095</v>
+        <v>57900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3249,37 +3237,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>504059</v>
+        <v>504058</v>
       </c>
       <c r="R25" t="n">
-        <v>7021781</v>
+        <v>7021715</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3320,7 +3321,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3344,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130222755</v>
+        <v>130222743</v>
       </c>
       <c r="B26" t="n">
-        <v>79095</v>
+        <v>91637</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,26 +3355,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3382,10 +3386,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504177</v>
+        <v>504223</v>
       </c>
       <c r="R26" t="n">
-        <v>7021847</v>
+        <v>7022010</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3433,6 +3437,21 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3450,10 +3469,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130222743</v>
+        <v>130222755</v>
       </c>
       <c r="B27" t="n">
-        <v>91637</v>
+        <v>79095</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3461,30 +3480,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3492,10 +3507,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504223</v>
+        <v>504177</v>
       </c>
       <c r="R27" t="n">
-        <v>7022010</v>
+        <v>7021847</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3543,21 +3558,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3787,40 +3787,39 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130222722</v>
+        <v>130222704</v>
       </c>
       <c r="B30" t="n">
-        <v>57741</v>
+        <v>91605</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3830,10 +3829,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503979</v>
+        <v>504208</v>
       </c>
       <c r="R30" t="n">
-        <v>7022007</v>
+        <v>7022015</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3868,17 +3867,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3902,32 +3897,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130222746</v>
+        <v>130222719</v>
       </c>
       <c r="B31" t="n">
-        <v>91637</v>
+        <v>92359</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3944,10 +3939,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503973</v>
+        <v>504219</v>
       </c>
       <c r="R31" t="n">
-        <v>7021998</v>
+        <v>7022014</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3995,21 +3990,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4027,10 +4007,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130222734</v>
+        <v>130222746</v>
       </c>
       <c r="B32" t="n">
-        <v>91939</v>
+        <v>91637</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4038,21 +4018,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4069,10 +4049,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504221</v>
+        <v>503973</v>
       </c>
       <c r="R32" t="n">
-        <v>7022011</v>
+        <v>7021998</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4152,39 +4132,40 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130222704</v>
+        <v>130222722</v>
       </c>
       <c r="B33" t="n">
-        <v>91605</v>
+        <v>57741</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4194,10 +4175,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504208</v>
+        <v>503979</v>
       </c>
       <c r="R33" t="n">
-        <v>7022015</v>
+        <v>7022007</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4232,13 +4213,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4262,32 +4247,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130222719</v>
+        <v>130222734</v>
       </c>
       <c r="B34" t="n">
-        <v>92359</v>
+        <v>91939</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4304,10 +4289,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504219</v>
+        <v>504221</v>
       </c>
       <c r="R34" t="n">
-        <v>7022014</v>
+        <v>7022011</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4355,6 +4340,21 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5130,10 +5130,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130222708</v>
+        <v>130222735</v>
       </c>
       <c r="B42" t="n">
-        <v>91641</v>
+        <v>91939</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504191</v>
+        <v>504166</v>
       </c>
       <c r="R42" t="n">
-        <v>7022006</v>
+        <v>7021986</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5223,6 +5223,21 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5240,10 +5255,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130222735</v>
+        <v>130222708</v>
       </c>
       <c r="B43" t="n">
-        <v>91939</v>
+        <v>91641</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5251,21 +5266,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5282,10 +5297,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504166</v>
+        <v>504191</v>
       </c>
       <c r="R43" t="n">
-        <v>7021986</v>
+        <v>7022006</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5333,21 +5348,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6168,10 +6168,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130222738</v>
+        <v>130222703</v>
       </c>
       <c r="B51" t="n">
-        <v>78107</v>
+        <v>83073</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6179,21 +6179,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6206,10 +6206,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504087</v>
+        <v>504170</v>
       </c>
       <c r="R51" t="n">
-        <v>7021791</v>
+        <v>7021803</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6274,10 +6274,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130222703</v>
+        <v>130222738</v>
       </c>
       <c r="B52" t="n">
-        <v>83073</v>
+        <v>78107</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504170</v>
+        <v>504087</v>
       </c>
       <c r="R52" t="n">
-        <v>7021803</v>
+        <v>7021791</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6601,46 +6601,41 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130222739</v>
+        <v>130222747</v>
       </c>
       <c r="B55" t="n">
-        <v>98833</v>
+        <v>91655</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6648,10 +6643,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504054</v>
+        <v>504210</v>
       </c>
       <c r="R55" t="n">
-        <v>7021735</v>
+        <v>7022007</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6684,11 +6679,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Minst 3 plantor finns på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6721,10 +6711,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130222747</v>
+        <v>130222754</v>
       </c>
       <c r="B56" t="n">
-        <v>91655</v>
+        <v>79095</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6732,30 +6722,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6763,10 +6749,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504210</v>
+        <v>504081</v>
       </c>
       <c r="R56" t="n">
-        <v>7022007</v>
+        <v>7021796</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6831,37 +6817,46 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130222754</v>
+        <v>130222739</v>
       </c>
       <c r="B57" t="n">
-        <v>79095</v>
+        <v>98833</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6869,10 +6864,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504081</v>
+        <v>504054</v>
       </c>
       <c r="R57" t="n">
-        <v>7021796</v>
+        <v>7021735</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6905,6 +6900,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor finns på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6937,10 +6937,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130222751</v>
+        <v>130222748</v>
       </c>
       <c r="B58" t="n">
-        <v>91661</v>
+        <v>91655</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6948,19 +6948,23 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
@@ -6975,10 +6979,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504218</v>
+        <v>504123</v>
       </c>
       <c r="R58" t="n">
-        <v>7022019</v>
+        <v>7021748</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7026,21 +7030,6 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7058,10 +7047,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130222721</v>
+        <v>130222741</v>
       </c>
       <c r="B59" t="n">
-        <v>57741</v>
+        <v>91637</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7069,29 +7058,28 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7101,10 +7089,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503954</v>
+        <v>504078</v>
       </c>
       <c r="R59" t="n">
-        <v>7021984</v>
+        <v>7022057</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7139,23 +7127,34 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7173,41 +7172,46 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130222748</v>
+        <v>130222740</v>
       </c>
       <c r="B60" t="n">
-        <v>91655</v>
+        <v>98833</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7215,10 +7219,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504123</v>
+        <v>504087</v>
       </c>
       <c r="R60" t="n">
-        <v>7021748</v>
+        <v>7021765</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7251,6 +7255,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Minst 8 plantor på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7283,46 +7292,37 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130222740</v>
+        <v>130222751</v>
       </c>
       <c r="B61" t="n">
-        <v>98833</v>
+        <v>91661</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504087</v>
+        <v>504218</v>
       </c>
       <c r="R61" t="n">
-        <v>7021765</v>
+        <v>7022019</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7368,11 +7368,6 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Minst 8 plantor på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7386,6 +7381,21 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7403,10 +7413,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130222741</v>
+        <v>130222721</v>
       </c>
       <c r="B62" t="n">
-        <v>91637</v>
+        <v>57741</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7414,28 +7424,29 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7445,10 +7456,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>504078</v>
+        <v>503954</v>
       </c>
       <c r="R62" t="n">
-        <v>7022057</v>
+        <v>7021984</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7483,34 +7494,23 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>130222731</v>
       </c>
       <c r="B4" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>130222710</v>
       </c>
       <c r="B5" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>130222749</v>
       </c>
       <c r="B6" t="n">
-        <v>91655</v>
+        <v>91742</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>130222714</v>
       </c>
       <c r="B7" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>130222732</v>
       </c>
       <c r="B8" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>130222712</v>
       </c>
       <c r="B9" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>130222716</v>
       </c>
       <c r="B10" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130222736</v>
+        <v>130222701</v>
       </c>
       <c r="B11" t="n">
-        <v>91939</v>
+        <v>83158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,30 +1696,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1727,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504081</v>
+        <v>504090</v>
       </c>
       <c r="R11" t="n">
-        <v>7021794</v>
+        <v>7021787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,7 +1794,7 @@
         <v>130222705</v>
       </c>
       <c r="B12" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,10 +1901,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130222701</v>
+        <v>130222736</v>
       </c>
       <c r="B13" t="n">
-        <v>83073</v>
+        <v>92026</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,26 +1912,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504090</v>
+        <v>504081</v>
       </c>
       <c r="R13" t="n">
-        <v>7021787</v>
+        <v>7021794</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130222724</v>
+        <v>130222702</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>83158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,31 +2022,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2054,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504139</v>
+        <v>504100</v>
       </c>
       <c r="R14" t="n">
-        <v>7021798</v>
+        <v>7021801</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,17 +2087,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2126,41 +2117,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222713</v>
+        <v>130222730</v>
       </c>
       <c r="B15" t="n">
-        <v>91641</v>
+        <v>80189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2168,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504135</v>
+        <v>504166</v>
       </c>
       <c r="R15" t="n">
-        <v>7021768</v>
+        <v>7021800</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130222711</v>
+        <v>130222724</v>
       </c>
       <c r="B16" t="n">
-        <v>91641</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,28 +2234,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2278,10 +2266,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504154</v>
+        <v>504139</v>
       </c>
       <c r="R16" t="n">
-        <v>7021848</v>
+        <v>7021798</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,13 +2304,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2346,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130222702</v>
+        <v>130222711</v>
       </c>
       <c r="B17" t="n">
-        <v>83073</v>
+        <v>91728</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,26 +2349,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2384,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>504100</v>
+        <v>504154</v>
       </c>
       <c r="R17" t="n">
-        <v>7021801</v>
+        <v>7021848</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,37 +2448,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130222730</v>
+        <v>130222713</v>
       </c>
       <c r="B18" t="n">
-        <v>80104</v>
+        <v>91728</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504166</v>
+        <v>504135</v>
       </c>
       <c r="R18" t="n">
-        <v>7021800</v>
+        <v>7021768</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,32 +2558,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130222727</v>
+        <v>130222706</v>
       </c>
       <c r="B19" t="n">
-        <v>92364</v>
+        <v>91692</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>67</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504089</v>
+        <v>504083</v>
       </c>
       <c r="R19" t="n">
-        <v>7021772</v>
+        <v>7021773</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2651,21 +2651,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2683,41 +2668,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130222706</v>
+        <v>130222700</v>
       </c>
       <c r="B20" t="n">
-        <v>91605</v>
+        <v>83158</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2725,10 +2706,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504083</v>
+        <v>504099</v>
       </c>
       <c r="R20" t="n">
-        <v>7021773</v>
+        <v>7021769</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2793,37 +2774,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130222700</v>
+        <v>130222727</v>
       </c>
       <c r="B21" t="n">
-        <v>83073</v>
+        <v>92451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>67</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2831,10 +2816,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>504099</v>
+        <v>504089</v>
       </c>
       <c r="R21" t="n">
-        <v>7021769</v>
+        <v>7021772</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2882,6 +2867,21 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130222753</v>
+        <v>130222757</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>504059</v>
+        <v>504170</v>
       </c>
       <c r="R22" t="n">
-        <v>7021781</v>
+        <v>7021800</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3005,10 +3005,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130222757</v>
+        <v>130222720</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,26 +3016,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3043,10 +3048,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504170</v>
+        <v>503952</v>
       </c>
       <c r="R23" t="n">
-        <v>7021800</v>
+        <v>7022000</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3081,13 +3086,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3111,10 +3120,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130222720</v>
+        <v>130222753</v>
       </c>
       <c r="B24" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,31 +3131,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3154,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503952</v>
+        <v>504059</v>
       </c>
       <c r="R24" t="n">
-        <v>7022000</v>
+        <v>7021781</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3192,17 +3196,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3229,7 +3229,7 @@
         <v>130222725</v>
       </c>
       <c r="B25" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>130222743</v>
       </c>
       <c r="B26" t="n">
-        <v>91637</v>
+        <v>91724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>130222755</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3575,10 +3575,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130222750</v>
+        <v>130222752</v>
       </c>
       <c r="B28" t="n">
-        <v>91661</v>
+        <v>79180</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3586,26 +3586,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504216</v>
+        <v>504097</v>
       </c>
       <c r="R28" t="n">
-        <v>7022005</v>
+        <v>7021762</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3681,10 +3681,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130222752</v>
+        <v>130222750</v>
       </c>
       <c r="B29" t="n">
-        <v>79095</v>
+        <v>91748</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3692,26 +3692,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504097</v>
+        <v>504216</v>
       </c>
       <c r="R29" t="n">
-        <v>7021762</v>
+        <v>7022005</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3787,39 +3787,40 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130222704</v>
+        <v>130222722</v>
       </c>
       <c r="B30" t="n">
-        <v>91605</v>
+        <v>57826</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3829,10 +3830,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504208</v>
+        <v>503979</v>
       </c>
       <c r="R30" t="n">
-        <v>7022015</v>
+        <v>7022007</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3867,13 +3868,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3897,41 +3902,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130222719</v>
+        <v>130222756</v>
       </c>
       <c r="B31" t="n">
-        <v>92359</v>
+        <v>79180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3939,10 +3940,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504219</v>
+        <v>504101</v>
       </c>
       <c r="R31" t="n">
-        <v>7022014</v>
+        <v>7021774</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4007,10 +4008,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130222746</v>
+        <v>130222742</v>
       </c>
       <c r="B32" t="n">
-        <v>91637</v>
+        <v>91724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4049,10 +4050,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503973</v>
+        <v>504227</v>
       </c>
       <c r="R32" t="n">
-        <v>7021998</v>
+        <v>7022001</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4100,21 +4101,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4132,10 +4118,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130222722</v>
+        <v>130222746</v>
       </c>
       <c r="B33" t="n">
-        <v>57741</v>
+        <v>91724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4143,29 +4129,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4175,10 +4160,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503979</v>
+        <v>503973</v>
       </c>
       <c r="R33" t="n">
-        <v>7022007</v>
+        <v>7021998</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4213,23 +4198,34 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4247,32 +4243,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130222734</v>
+        <v>130222704</v>
       </c>
       <c r="B34" t="n">
-        <v>91939</v>
+        <v>91692</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4289,10 +4285,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504221</v>
+        <v>504208</v>
       </c>
       <c r="R34" t="n">
-        <v>7022011</v>
+        <v>7022015</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4340,21 +4336,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4372,10 +4353,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130222742</v>
+        <v>130222734</v>
       </c>
       <c r="B35" t="n">
-        <v>91637</v>
+        <v>92026</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4383,21 +4364,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4414,10 +4395,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504227</v>
+        <v>504221</v>
       </c>
       <c r="R35" t="n">
-        <v>7022001</v>
+        <v>7022011</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4465,6 +4446,21 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4482,32 +4478,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130222715</v>
+        <v>130222719</v>
       </c>
       <c r="B36" t="n">
-        <v>91641</v>
+        <v>92446</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4524,10 +4520,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504083</v>
+        <v>504219</v>
       </c>
       <c r="R36" t="n">
-        <v>7021787</v>
+        <v>7022014</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4592,10 +4588,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130222756</v>
+        <v>130222715</v>
       </c>
       <c r="B37" t="n">
-        <v>79095</v>
+        <v>91728</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4603,26 +4599,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4630,10 +4630,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504101</v>
+        <v>504083</v>
       </c>
       <c r="R37" t="n">
-        <v>7021774</v>
+        <v>7021787</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4701,7 +4701,7 @@
         <v>130222718</v>
       </c>
       <c r="B38" t="n">
-        <v>92359</v>
+        <v>92446</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>130222728</v>
       </c>
       <c r="B39" t="n">
-        <v>80104</v>
+        <v>80189</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>130222709</v>
       </c>
       <c r="B40" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>130222729</v>
       </c>
       <c r="B41" t="n">
-        <v>80104</v>
+        <v>80189</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>130222735</v>
       </c>
       <c r="B42" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>130222708</v>
       </c>
       <c r="B43" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5365,41 +5365,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130222733</v>
+        <v>130222726</v>
       </c>
       <c r="B44" t="n">
-        <v>92094</v>
+        <v>80314</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5407,10 +5403,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504161</v>
+        <v>504106</v>
       </c>
       <c r="R44" t="n">
-        <v>7021869</v>
+        <v>7021741</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5458,21 +5454,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5490,10 +5471,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130222744</v>
+        <v>130222699</v>
       </c>
       <c r="B45" t="n">
-        <v>91637</v>
+        <v>83158</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5501,30 +5482,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5532,10 +5509,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504178</v>
+        <v>504118</v>
       </c>
       <c r="R45" t="n">
-        <v>7021976</v>
+        <v>7021776</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5583,21 +5560,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5615,32 +5577,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130222745</v>
+        <v>130222733</v>
       </c>
       <c r="B46" t="n">
-        <v>91637</v>
+        <v>92181</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5657,10 +5619,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504130</v>
+        <v>504161</v>
       </c>
       <c r="R46" t="n">
-        <v>7021754</v>
+        <v>7021869</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5740,37 +5702,41 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130222726</v>
+        <v>130222744</v>
       </c>
       <c r="B47" t="n">
-        <v>80229</v>
+        <v>91724</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5778,10 +5744,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504106</v>
+        <v>504178</v>
       </c>
       <c r="R47" t="n">
-        <v>7021741</v>
+        <v>7021976</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5829,6 +5795,21 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5846,10 +5827,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130222699</v>
+        <v>130222745</v>
       </c>
       <c r="B48" t="n">
-        <v>83073</v>
+        <v>91724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5857,26 +5838,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5884,10 +5869,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504118</v>
+        <v>504130</v>
       </c>
       <c r="R48" t="n">
-        <v>7021776</v>
+        <v>7021754</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5935,6 +5920,21 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5955,7 +5955,7 @@
         <v>130222707</v>
       </c>
       <c r="B49" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>130222758</v>
       </c>
       <c r="B50" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>130222703</v>
       </c>
       <c r="B51" t="n">
-        <v>83073</v>
+        <v>83158</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>130222738</v>
       </c>
       <c r="B52" t="n">
-        <v>78107</v>
+        <v>78192</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>130222737</v>
       </c>
       <c r="B53" t="n">
-        <v>78107</v>
+        <v>78192</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>130222723</v>
       </c>
       <c r="B54" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>130222747</v>
       </c>
       <c r="B55" t="n">
-        <v>91655</v>
+        <v>91742</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6711,37 +6711,46 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130222754</v>
+        <v>130222739</v>
       </c>
       <c r="B56" t="n">
-        <v>79095</v>
+        <v>98920</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6749,10 +6758,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504081</v>
+        <v>504054</v>
       </c>
       <c r="R56" t="n">
-        <v>7021796</v>
+        <v>7021735</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6785,6 +6794,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor finns på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6817,46 +6831,37 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130222739</v>
+        <v>130222754</v>
       </c>
       <c r="B57" t="n">
-        <v>98833</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6864,10 +6869,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504054</v>
+        <v>504081</v>
       </c>
       <c r="R57" t="n">
-        <v>7021735</v>
+        <v>7021796</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6900,11 +6905,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Minst 3 plantor finns på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6937,10 +6937,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130222748</v>
+        <v>130222751</v>
       </c>
       <c r="B58" t="n">
-        <v>91655</v>
+        <v>91748</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6948,23 +6948,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
@@ -6979,10 +6975,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504123</v>
+        <v>504218</v>
       </c>
       <c r="R58" t="n">
-        <v>7021748</v>
+        <v>7022019</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7030,6 +7026,21 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7047,10 +7058,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130222741</v>
+        <v>130222748</v>
       </c>
       <c r="B59" t="n">
-        <v>91637</v>
+        <v>91742</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7058,21 +7069,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7089,10 +7100,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504078</v>
+        <v>504123</v>
       </c>
       <c r="R59" t="n">
-        <v>7022057</v>
+        <v>7021748</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7140,21 +7151,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7172,46 +7168,42 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130222740</v>
+        <v>130222721</v>
       </c>
       <c r="B60" t="n">
-        <v>98833</v>
+        <v>57826</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7219,10 +7211,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504087</v>
+        <v>503954</v>
       </c>
       <c r="R60" t="n">
-        <v>7021765</v>
+        <v>7021984</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7259,7 +7251,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Minst 8 plantor på fyndplatsen.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7268,7 +7260,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7292,37 +7283,46 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130222751</v>
+        <v>130222740</v>
       </c>
       <c r="B61" t="n">
-        <v>91661</v>
+        <v>98920</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504218</v>
+        <v>504087</v>
       </c>
       <c r="R61" t="n">
-        <v>7022019</v>
+        <v>7021765</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7368,6 +7368,11 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Minst 8 plantor på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7381,21 +7386,6 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7413,10 +7403,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130222721</v>
+        <v>130222741</v>
       </c>
       <c r="B62" t="n">
-        <v>57741</v>
+        <v>91724</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7424,29 +7414,28 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7456,10 +7445,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503954</v>
+        <v>504078</v>
       </c>
       <c r="R62" t="n">
-        <v>7021984</v>
+        <v>7022057</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7494,23 +7483,34 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130222757</v>
+        <v>130222725</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>57985</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,37 +2910,50 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>504170</v>
+        <v>504058</v>
       </c>
       <c r="R22" t="n">
-        <v>7021800</v>
+        <v>7021715</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2981,7 +2994,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3005,10 +3017,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130222720</v>
+        <v>130222753</v>
       </c>
       <c r="B23" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3016,31 +3028,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3048,10 +3055,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503952</v>
+        <v>504059</v>
       </c>
       <c r="R23" t="n">
-        <v>7022000</v>
+        <v>7021781</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3086,17 +3093,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3120,7 +3123,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130222753</v>
+        <v>130222757</v>
       </c>
       <c r="B24" t="n">
         <v>79180</v>
@@ -3158,10 +3161,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504059</v>
+        <v>504170</v>
       </c>
       <c r="R24" t="n">
-        <v>7021781</v>
+        <v>7021800</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3226,10 +3229,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130222725</v>
+        <v>130222720</v>
       </c>
       <c r="B25" t="n">
-        <v>57985</v>
+        <v>57826</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,50 +3240,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>504058</v>
+        <v>503952</v>
       </c>
       <c r="R25" t="n">
-        <v>7021715</v>
+        <v>7022000</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3313,6 +3308,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130222725</v>
+        <v>130222753</v>
       </c>
       <c r="B22" t="n">
-        <v>57985</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,50 +2910,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>504058</v>
+        <v>504059</v>
       </c>
       <c r="R22" t="n">
-        <v>7021715</v>
+        <v>7021781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2994,6 +2981,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3017,7 +3005,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130222753</v>
+        <v>130222757</v>
       </c>
       <c r="B23" t="n">
         <v>79180</v>
@@ -3055,10 +3043,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504059</v>
+        <v>504170</v>
       </c>
       <c r="R23" t="n">
-        <v>7021781</v>
+        <v>7021800</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3123,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130222757</v>
+        <v>130222720</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3134,26 +3122,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3161,10 +3154,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504170</v>
+        <v>503952</v>
       </c>
       <c r="R24" t="n">
-        <v>7021800</v>
+        <v>7022000</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3199,13 +3192,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3229,10 +3226,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130222720</v>
+        <v>130222725</v>
       </c>
       <c r="B25" t="n">
-        <v>57826</v>
+        <v>57985</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,42 +3237,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503952</v>
+        <v>504058</v>
       </c>
       <c r="R25" t="n">
-        <v>7022000</v>
+        <v>7021715</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3308,11 +3313,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130222710</v>
+        <v>130222714</v>
       </c>
       <c r="B5" t="n">
         <v>91728</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504160</v>
+        <v>504091</v>
       </c>
       <c r="R5" t="n">
-        <v>7021867</v>
+        <v>7021759</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130222749</v>
+        <v>130222710</v>
       </c>
       <c r="B6" t="n">
-        <v>91742</v>
+        <v>91728</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504067</v>
+        <v>504160</v>
       </c>
       <c r="R6" t="n">
-        <v>7021774</v>
+        <v>7021867</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130222714</v>
+        <v>130222749</v>
       </c>
       <c r="B7" t="n">
-        <v>91728</v>
+        <v>91742</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504091</v>
+        <v>504067</v>
       </c>
       <c r="R7" t="n">
-        <v>7021759</v>
+        <v>7021774</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130222712</v>
+        <v>130222716</v>
       </c>
       <c r="B9" t="n">
         <v>91728</v>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504057</v>
+        <v>504095</v>
       </c>
       <c r="R9" t="n">
-        <v>7021765</v>
+        <v>7021805</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130222716</v>
+        <v>130222712</v>
       </c>
       <c r="B10" t="n">
         <v>91728</v>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504095</v>
+        <v>504057</v>
       </c>
       <c r="R10" t="n">
-        <v>7021805</v>
+        <v>7021765</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130222701</v>
+        <v>130222736</v>
       </c>
       <c r="B11" t="n">
-        <v>83158</v>
+        <v>92026</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,26 +1696,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1723,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504090</v>
+        <v>504081</v>
       </c>
       <c r="R11" t="n">
-        <v>7021787</v>
+        <v>7021794</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,41 +1795,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130222705</v>
+        <v>130222701</v>
       </c>
       <c r="B12" t="n">
-        <v>91692</v>
+        <v>83158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504210</v>
+        <v>504090</v>
       </c>
       <c r="R12" t="n">
-        <v>7022007</v>
+        <v>7021787</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,32 +1901,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130222736</v>
+        <v>130222705</v>
       </c>
       <c r="B13" t="n">
-        <v>92026</v>
+        <v>91692</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504081</v>
+        <v>504210</v>
       </c>
       <c r="R13" t="n">
-        <v>7021794</v>
+        <v>7022007</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,32 +2011,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130222702</v>
+        <v>130222730</v>
       </c>
       <c r="B14" t="n">
-        <v>83158</v>
+        <v>80189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504100</v>
+        <v>504166</v>
       </c>
       <c r="R14" t="n">
-        <v>7021801</v>
+        <v>7021800</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,32 +2117,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222730</v>
+        <v>130222702</v>
       </c>
       <c r="B15" t="n">
-        <v>80189</v>
+        <v>83158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504166</v>
+        <v>504100</v>
       </c>
       <c r="R15" t="n">
-        <v>7021800</v>
+        <v>7021801</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130222724</v>
+        <v>130222711</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,29 +2234,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2266,10 +2265,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504139</v>
+        <v>504154</v>
       </c>
       <c r="R16" t="n">
-        <v>7021798</v>
+        <v>7021848</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,17 +2303,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2338,7 +2333,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130222711</v>
+        <v>130222713</v>
       </c>
       <c r="B17" t="n">
         <v>91728</v>
@@ -2380,10 +2375,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>504154</v>
+        <v>504135</v>
       </c>
       <c r="R17" t="n">
-        <v>7021848</v>
+        <v>7021768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,10 +2443,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130222713</v>
+        <v>130222724</v>
       </c>
       <c r="B18" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2459,28 +2454,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2490,10 +2486,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504135</v>
+        <v>504139</v>
       </c>
       <c r="R18" t="n">
-        <v>7021768</v>
+        <v>7021798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2528,13 +2524,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2558,32 +2558,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130222706</v>
+        <v>130222727</v>
       </c>
       <c r="B19" t="n">
-        <v>91692</v>
+        <v>92451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>67</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504083</v>
+        <v>504089</v>
       </c>
       <c r="R19" t="n">
-        <v>7021773</v>
+        <v>7021772</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2651,6 +2651,21 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2668,37 +2683,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130222700</v>
+        <v>130222706</v>
       </c>
       <c r="B20" t="n">
-        <v>83158</v>
+        <v>91692</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2706,10 +2725,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504099</v>
+        <v>504083</v>
       </c>
       <c r="R20" t="n">
-        <v>7021769</v>
+        <v>7021773</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,41 +2793,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130222727</v>
+        <v>130222700</v>
       </c>
       <c r="B21" t="n">
-        <v>92451</v>
+        <v>83158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>67</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2816,10 +2831,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>504089</v>
+        <v>504099</v>
       </c>
       <c r="R21" t="n">
-        <v>7021772</v>
+        <v>7021769</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2867,21 +2882,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130222720</v>
+        <v>130222725</v>
       </c>
       <c r="B24" t="n">
-        <v>57826</v>
+        <v>57985</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,42 +3122,50 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503952</v>
+        <v>504058</v>
       </c>
       <c r="R24" t="n">
-        <v>7022000</v>
+        <v>7021715</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3190,11 +3198,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3226,10 +3229,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130222725</v>
+        <v>130222720</v>
       </c>
       <c r="B25" t="n">
-        <v>57985</v>
+        <v>57826</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,50 +3240,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>504058</v>
+        <v>503952</v>
       </c>
       <c r="R25" t="n">
-        <v>7021715</v>
+        <v>7022000</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3313,6 +3308,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3787,40 +3787,39 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130222722</v>
+        <v>130222704</v>
       </c>
       <c r="B30" t="n">
-        <v>57826</v>
+        <v>91692</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3830,10 +3829,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503979</v>
+        <v>504208</v>
       </c>
       <c r="R30" t="n">
-        <v>7022007</v>
+        <v>7022015</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3868,17 +3867,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3902,37 +3897,41 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130222756</v>
+        <v>130222719</v>
       </c>
       <c r="B31" t="n">
-        <v>79180</v>
+        <v>92446</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3940,10 +3939,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504101</v>
+        <v>504219</v>
       </c>
       <c r="R31" t="n">
-        <v>7021774</v>
+        <v>7022014</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4008,10 +4007,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130222742</v>
+        <v>130222715</v>
       </c>
       <c r="B32" t="n">
-        <v>91724</v>
+        <v>91728</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4019,21 +4018,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4050,10 +4049,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504227</v>
+        <v>504083</v>
       </c>
       <c r="R32" t="n">
-        <v>7022001</v>
+        <v>7021787</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4243,32 +4242,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130222704</v>
+        <v>130222742</v>
       </c>
       <c r="B34" t="n">
-        <v>91692</v>
+        <v>91724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4285,10 +4284,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504208</v>
+        <v>504227</v>
       </c>
       <c r="R34" t="n">
-        <v>7022015</v>
+        <v>7022001</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4478,41 +4477,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130222719</v>
+        <v>130222756</v>
       </c>
       <c r="B36" t="n">
-        <v>92446</v>
+        <v>79180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4520,10 +4515,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504219</v>
+        <v>504101</v>
       </c>
       <c r="R36" t="n">
-        <v>7022014</v>
+        <v>7021774</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4588,10 +4583,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130222715</v>
+        <v>130222722</v>
       </c>
       <c r="B37" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4599,28 +4594,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4630,10 +4626,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504083</v>
+        <v>503979</v>
       </c>
       <c r="R37" t="n">
-        <v>7021787</v>
+        <v>7022007</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4668,13 +4664,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5130,10 +5130,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130222735</v>
+        <v>130222708</v>
       </c>
       <c r="B42" t="n">
-        <v>92026</v>
+        <v>91728</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504166</v>
+        <v>504191</v>
       </c>
       <c r="R42" t="n">
-        <v>7021986</v>
+        <v>7022006</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5223,21 +5223,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5255,10 +5240,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130222708</v>
+        <v>130222735</v>
       </c>
       <c r="B43" t="n">
-        <v>91728</v>
+        <v>92026</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5266,21 +5251,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5297,10 +5282,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504191</v>
+        <v>504166</v>
       </c>
       <c r="R43" t="n">
-        <v>7022006</v>
+        <v>7021986</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5348,6 +5333,21 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5365,37 +5365,41 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130222726</v>
+        <v>130222745</v>
       </c>
       <c r="B44" t="n">
-        <v>80314</v>
+        <v>91724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5403,10 +5407,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504106</v>
+        <v>504130</v>
       </c>
       <c r="R44" t="n">
-        <v>7021741</v>
+        <v>7021754</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5454,6 +5458,21 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5471,10 +5490,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130222699</v>
+        <v>130222744</v>
       </c>
       <c r="B45" t="n">
-        <v>83158</v>
+        <v>91724</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5482,26 +5501,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5509,10 +5532,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504118</v>
+        <v>504178</v>
       </c>
       <c r="R45" t="n">
-        <v>7021776</v>
+        <v>7021976</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5560,6 +5583,21 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5702,10 +5740,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130222744</v>
+        <v>130222699</v>
       </c>
       <c r="B47" t="n">
-        <v>91724</v>
+        <v>83158</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5713,30 +5751,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5744,10 +5778,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504178</v>
+        <v>504118</v>
       </c>
       <c r="R47" t="n">
-        <v>7021976</v>
+        <v>7021776</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5795,21 +5829,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5827,41 +5846,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130222745</v>
+        <v>130222726</v>
       </c>
       <c r="B48" t="n">
-        <v>91724</v>
+        <v>80314</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5869,10 +5884,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504130</v>
+        <v>504106</v>
       </c>
       <c r="R48" t="n">
-        <v>7021754</v>
+        <v>7021741</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5920,21 +5935,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6168,10 +6168,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130222703</v>
+        <v>130222738</v>
       </c>
       <c r="B51" t="n">
-        <v>83158</v>
+        <v>78192</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6179,21 +6179,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6206,10 +6206,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504170</v>
+        <v>504087</v>
       </c>
       <c r="R51" t="n">
-        <v>7021803</v>
+        <v>7021791</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6274,10 +6274,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130222738</v>
+        <v>130222703</v>
       </c>
       <c r="B52" t="n">
-        <v>78192</v>
+        <v>83158</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504087</v>
+        <v>504170</v>
       </c>
       <c r="R52" t="n">
-        <v>7021791</v>
+        <v>7021803</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6486,42 +6486,46 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130222723</v>
+        <v>130222739</v>
       </c>
       <c r="B54" t="n">
-        <v>57826</v>
+        <v>98920</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6529,7 +6533,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504117</v>
+        <v>504054</v>
       </c>
       <c r="R54" t="n">
         <v>7021735</v>
@@ -6569,7 +6573,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Minst 3 plantor finns på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6578,6 +6582,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6711,46 +6716,37 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130222739</v>
+        <v>130222754</v>
       </c>
       <c r="B56" t="n">
-        <v>98920</v>
+        <v>79180</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6758,10 +6754,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504054</v>
+        <v>504081</v>
       </c>
       <c r="R56" t="n">
-        <v>7021735</v>
+        <v>7021796</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6794,11 +6790,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Minst 3 plantor finns på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6831,10 +6822,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130222754</v>
+        <v>130222723</v>
       </c>
       <c r="B57" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6842,26 +6833,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6869,10 +6865,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504081</v>
+        <v>504117</v>
       </c>
       <c r="R57" t="n">
-        <v>7021796</v>
+        <v>7021735</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6907,13 +6903,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7058,41 +7058,46 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130222748</v>
+        <v>130222740</v>
       </c>
       <c r="B59" t="n">
-        <v>91742</v>
+        <v>98920</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7100,10 +7105,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504123</v>
+        <v>504087</v>
       </c>
       <c r="R59" t="n">
-        <v>7021748</v>
+        <v>7021765</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7136,6 +7141,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Minst 8 plantor på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7168,10 +7178,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130222721</v>
+        <v>130222741</v>
       </c>
       <c r="B60" t="n">
-        <v>57826</v>
+        <v>91724</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7179,29 +7189,28 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7211,10 +7220,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503954</v>
+        <v>504078</v>
       </c>
       <c r="R60" t="n">
-        <v>7021984</v>
+        <v>7022057</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7249,23 +7258,34 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7283,46 +7303,41 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130222740</v>
+        <v>130222748</v>
       </c>
       <c r="B61" t="n">
-        <v>98920</v>
+        <v>91742</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7330,10 +7345,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504087</v>
+        <v>504123</v>
       </c>
       <c r="R61" t="n">
-        <v>7021765</v>
+        <v>7021748</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7366,11 +7381,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Minst 8 plantor på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7403,10 +7413,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130222741</v>
+        <v>130222721</v>
       </c>
       <c r="B62" t="n">
-        <v>91724</v>
+        <v>57826</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7414,28 +7424,29 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7445,10 +7456,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>504078</v>
+        <v>503954</v>
       </c>
       <c r="R62" t="n">
-        <v>7022057</v>
+        <v>7021984</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7483,34 +7494,23 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130222714</v>
+        <v>130222710</v>
       </c>
       <c r="B5" t="n">
         <v>91728</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504091</v>
+        <v>504160</v>
       </c>
       <c r="R5" t="n">
-        <v>7021759</v>
+        <v>7021867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130222710</v>
+        <v>130222749</v>
       </c>
       <c r="B6" t="n">
-        <v>91728</v>
+        <v>91742</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504160</v>
+        <v>504067</v>
       </c>
       <c r="R6" t="n">
-        <v>7021867</v>
+        <v>7021774</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130222749</v>
+        <v>130222714</v>
       </c>
       <c r="B7" t="n">
-        <v>91742</v>
+        <v>91728</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504067</v>
+        <v>504091</v>
       </c>
       <c r="R7" t="n">
-        <v>7021774</v>
+        <v>7021759</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130222716</v>
+        <v>130222712</v>
       </c>
       <c r="B9" t="n">
         <v>91728</v>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504095</v>
+        <v>504057</v>
       </c>
       <c r="R9" t="n">
-        <v>7021805</v>
+        <v>7021765</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130222712</v>
+        <v>130222716</v>
       </c>
       <c r="B10" t="n">
         <v>91728</v>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504057</v>
+        <v>504095</v>
       </c>
       <c r="R10" t="n">
-        <v>7021765</v>
+        <v>7021805</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2011,37 +2011,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130222730</v>
+        <v>130222713</v>
       </c>
       <c r="B14" t="n">
-        <v>80189</v>
+        <v>91728</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2049,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504166</v>
+        <v>504135</v>
       </c>
       <c r="R14" t="n">
-        <v>7021800</v>
+        <v>7021768</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222702</v>
+        <v>130222711</v>
       </c>
       <c r="B15" t="n">
-        <v>83158</v>
+        <v>91728</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2128,26 +2132,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2155,10 +2163,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504100</v>
+        <v>504154</v>
       </c>
       <c r="R15" t="n">
-        <v>7021801</v>
+        <v>7021848</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130222711</v>
+        <v>130222702</v>
       </c>
       <c r="B16" t="n">
-        <v>91728</v>
+        <v>83158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,30 +2242,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2265,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504154</v>
+        <v>504100</v>
       </c>
       <c r="R16" t="n">
-        <v>7021848</v>
+        <v>7021801</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2333,41 +2337,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130222713</v>
+        <v>130222730</v>
       </c>
       <c r="B17" t="n">
-        <v>91728</v>
+        <v>80189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>504135</v>
+        <v>504166</v>
       </c>
       <c r="R17" t="n">
-        <v>7021768</v>
+        <v>7021800</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2558,41 +2558,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130222727</v>
+        <v>130222700</v>
       </c>
       <c r="B19" t="n">
-        <v>92451</v>
+        <v>83158</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>67</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2600,10 +2596,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504089</v>
+        <v>504099</v>
       </c>
       <c r="R19" t="n">
-        <v>7021772</v>
+        <v>7021769</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2651,21 +2647,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2683,32 +2664,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130222706</v>
+        <v>130222727</v>
       </c>
       <c r="B20" t="n">
-        <v>91692</v>
+        <v>92451</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>67</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2725,10 +2706,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504083</v>
+        <v>504089</v>
       </c>
       <c r="R20" t="n">
-        <v>7021773</v>
+        <v>7021772</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,6 +2757,21 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2793,37 +2789,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130222700</v>
+        <v>130222706</v>
       </c>
       <c r="B21" t="n">
-        <v>83158</v>
+        <v>91692</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>504099</v>
+        <v>504083</v>
       </c>
       <c r="R21" t="n">
-        <v>7021769</v>
+        <v>7021773</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130222725</v>
+        <v>130222720</v>
       </c>
       <c r="B24" t="n">
-        <v>57985</v>
+        <v>57826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,50 +3122,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504058</v>
+        <v>503952</v>
       </c>
       <c r="R24" t="n">
-        <v>7021715</v>
+        <v>7022000</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3198,6 +3190,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3229,10 +3226,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130222720</v>
+        <v>130222725</v>
       </c>
       <c r="B25" t="n">
-        <v>57826</v>
+        <v>57985</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,42 +3237,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503952</v>
+        <v>504058</v>
       </c>
       <c r="R25" t="n">
-        <v>7022000</v>
+        <v>7021715</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3308,11 +3313,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130222743</v>
+        <v>130222755</v>
       </c>
       <c r="B26" t="n">
-        <v>91724</v>
+        <v>79180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,30 +3355,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3386,10 +3382,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504223</v>
+        <v>504177</v>
       </c>
       <c r="R26" t="n">
-        <v>7022010</v>
+        <v>7021847</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3437,21 +3433,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3469,10 +3450,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130222755</v>
+        <v>130222743</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>91724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,26 +3461,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3507,10 +3492,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504177</v>
+        <v>504223</v>
       </c>
       <c r="R27" t="n">
-        <v>7021847</v>
+        <v>7022010</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3558,6 +3543,21 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3575,10 +3575,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130222752</v>
+        <v>130222750</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>91748</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3586,26 +3586,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504097</v>
+        <v>504216</v>
       </c>
       <c r="R28" t="n">
-        <v>7021762</v>
+        <v>7022005</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3681,10 +3681,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130222750</v>
+        <v>130222752</v>
       </c>
       <c r="B29" t="n">
-        <v>91748</v>
+        <v>79180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3692,26 +3692,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504216</v>
+        <v>504097</v>
       </c>
       <c r="R29" t="n">
-        <v>7022005</v>
+        <v>7021762</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3787,32 +3787,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130222704</v>
+        <v>130222742</v>
       </c>
       <c r="B30" t="n">
-        <v>91692</v>
+        <v>91724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504208</v>
+        <v>504227</v>
       </c>
       <c r="R30" t="n">
-        <v>7022015</v>
+        <v>7022001</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130222719</v>
+        <v>130222746</v>
       </c>
       <c r="B31" t="n">
-        <v>92446</v>
+        <v>91724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504219</v>
+        <v>503973</v>
       </c>
       <c r="R31" t="n">
-        <v>7022014</v>
+        <v>7021998</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3990,6 +3990,21 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4117,32 +4132,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130222746</v>
+        <v>130222719</v>
       </c>
       <c r="B33" t="n">
-        <v>91724</v>
+        <v>92446</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4159,10 +4174,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503973</v>
+        <v>504219</v>
       </c>
       <c r="R33" t="n">
-        <v>7021998</v>
+        <v>7022014</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4210,21 +4225,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4242,10 +4242,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130222742</v>
+        <v>130222734</v>
       </c>
       <c r="B34" t="n">
-        <v>91724</v>
+        <v>92026</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,21 +4253,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504227</v>
+        <v>504221</v>
       </c>
       <c r="R34" t="n">
-        <v>7022001</v>
+        <v>7022011</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4335,6 +4335,21 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4352,10 +4367,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130222734</v>
+        <v>130222756</v>
       </c>
       <c r="B35" t="n">
-        <v>92026</v>
+        <v>79180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,30 +4378,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4394,10 +4405,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504221</v>
+        <v>504101</v>
       </c>
       <c r="R35" t="n">
-        <v>7022011</v>
+        <v>7021774</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4445,21 +4456,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4477,37 +4473,41 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130222756</v>
+        <v>130222704</v>
       </c>
       <c r="B36" t="n">
-        <v>79180</v>
+        <v>91692</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504101</v>
+        <v>504208</v>
       </c>
       <c r="R36" t="n">
-        <v>7021774</v>
+        <v>7022015</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4914,41 +4914,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130222709</v>
+        <v>130222729</v>
       </c>
       <c r="B40" t="n">
-        <v>91728</v>
+        <v>80189</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4956,10 +4952,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504104</v>
+        <v>504173</v>
       </c>
       <c r="R40" t="n">
-        <v>7021877</v>
+        <v>7021803</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5024,37 +5020,41 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130222729</v>
+        <v>130222709</v>
       </c>
       <c r="B41" t="n">
-        <v>80189</v>
+        <v>91728</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504173</v>
+        <v>504104</v>
       </c>
       <c r="R41" t="n">
-        <v>7021803</v>
+        <v>7021877</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5130,10 +5130,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130222708</v>
+        <v>130222735</v>
       </c>
       <c r="B42" t="n">
-        <v>91728</v>
+        <v>92026</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504191</v>
+        <v>504166</v>
       </c>
       <c r="R42" t="n">
-        <v>7022006</v>
+        <v>7021986</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5223,6 +5223,21 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5240,10 +5255,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130222735</v>
+        <v>130222708</v>
       </c>
       <c r="B43" t="n">
-        <v>92026</v>
+        <v>91728</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5251,21 +5266,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5282,10 +5297,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504166</v>
+        <v>504191</v>
       </c>
       <c r="R43" t="n">
-        <v>7021986</v>
+        <v>7022006</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5333,21 +5348,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5365,32 +5365,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130222745</v>
+        <v>130222733</v>
       </c>
       <c r="B44" t="n">
-        <v>91724</v>
+        <v>92181</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504130</v>
+        <v>504161</v>
       </c>
       <c r="R44" t="n">
-        <v>7021754</v>
+        <v>7021869</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5615,32 +5615,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130222733</v>
+        <v>130222745</v>
       </c>
       <c r="B46" t="n">
-        <v>92181</v>
+        <v>91724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5657,10 +5657,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504161</v>
+        <v>504130</v>
       </c>
       <c r="R46" t="n">
-        <v>7021869</v>
+        <v>7021754</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6168,10 +6168,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130222738</v>
+        <v>130222703</v>
       </c>
       <c r="B51" t="n">
-        <v>78192</v>
+        <v>83158</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6179,21 +6179,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6206,10 +6206,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504087</v>
+        <v>504170</v>
       </c>
       <c r="R51" t="n">
-        <v>7021791</v>
+        <v>7021803</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6274,10 +6274,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130222703</v>
+        <v>130222738</v>
       </c>
       <c r="B52" t="n">
-        <v>83158</v>
+        <v>78192</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504170</v>
+        <v>504087</v>
       </c>
       <c r="R52" t="n">
-        <v>7021803</v>
+        <v>7021791</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6937,37 +6937,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130222751</v>
+        <v>130222740</v>
       </c>
       <c r="B58" t="n">
-        <v>91748</v>
+        <v>98920</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6975,10 +6984,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504218</v>
+        <v>504087</v>
       </c>
       <c r="R58" t="n">
-        <v>7022019</v>
+        <v>7021765</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7013,6 +7022,11 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Minst 8 plantor på fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7026,21 +7040,6 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7058,46 +7057,37 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130222740</v>
+        <v>130222751</v>
       </c>
       <c r="B59" t="n">
-        <v>98920</v>
+        <v>91748</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7105,10 +7095,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504087</v>
+        <v>504218</v>
       </c>
       <c r="R59" t="n">
-        <v>7021765</v>
+        <v>7022019</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7143,11 +7133,6 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Minst 8 plantor på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7161,6 +7146,21 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7178,10 +7178,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130222741</v>
+        <v>130222748</v>
       </c>
       <c r="B60" t="n">
-        <v>91724</v>
+        <v>91742</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7189,21 +7189,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7220,10 +7220,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504078</v>
+        <v>504123</v>
       </c>
       <c r="R60" t="n">
-        <v>7022057</v>
+        <v>7021748</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7271,21 +7271,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7303,10 +7288,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130222748</v>
+        <v>130222741</v>
       </c>
       <c r="B61" t="n">
-        <v>91742</v>
+        <v>91724</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7314,21 +7299,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7345,10 +7330,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504123</v>
+        <v>504078</v>
       </c>
       <c r="R61" t="n">
-        <v>7021748</v>
+        <v>7022057</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7396,6 +7381,21 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130222749</v>
+        <v>130222714</v>
       </c>
       <c r="B6" t="n">
-        <v>91742</v>
+        <v>91728</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504067</v>
+        <v>504091</v>
       </c>
       <c r="R6" t="n">
-        <v>7021774</v>
+        <v>7021759</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130222714</v>
+        <v>130222749</v>
       </c>
       <c r="B7" t="n">
-        <v>91728</v>
+        <v>91742</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504091</v>
+        <v>504067</v>
       </c>
       <c r="R7" t="n">
-        <v>7021759</v>
+        <v>7021774</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,32 +1340,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130222732</v>
+        <v>130222712</v>
       </c>
       <c r="B8" t="n">
-        <v>92181</v>
+        <v>91728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504202</v>
+        <v>504057</v>
       </c>
       <c r="R8" t="n">
-        <v>7022015</v>
+        <v>7021765</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,21 +1433,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1465,7 +1450,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130222712</v>
+        <v>130222716</v>
       </c>
       <c r="B9" t="n">
         <v>91728</v>
@@ -1507,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504057</v>
+        <v>504095</v>
       </c>
       <c r="R9" t="n">
-        <v>7021765</v>
+        <v>7021805</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,32 +1560,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130222716</v>
+        <v>130222732</v>
       </c>
       <c r="B10" t="n">
-        <v>91728</v>
+        <v>92181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1617,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504095</v>
+        <v>504202</v>
       </c>
       <c r="R10" t="n">
-        <v>7021805</v>
+        <v>7022015</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,6 +1653,21 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130222753</v>
+        <v>130222725</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>57985</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,37 +2910,50 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>504059</v>
+        <v>504058</v>
       </c>
       <c r="R22" t="n">
-        <v>7021781</v>
+        <v>7021715</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2981,7 +2994,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3005,7 +3017,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130222757</v>
+        <v>130222753</v>
       </c>
       <c r="B23" t="n">
         <v>79180</v>
@@ -3043,10 +3055,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504170</v>
+        <v>504059</v>
       </c>
       <c r="R23" t="n">
-        <v>7021800</v>
+        <v>7021781</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3111,10 +3123,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130222720</v>
+        <v>130222757</v>
       </c>
       <c r="B24" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,31 +3134,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3154,10 +3161,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503952</v>
+        <v>504170</v>
       </c>
       <c r="R24" t="n">
-        <v>7022000</v>
+        <v>7021800</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3192,17 +3199,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3226,10 +3229,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130222725</v>
+        <v>130222720</v>
       </c>
       <c r="B25" t="n">
-        <v>57985</v>
+        <v>57826</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,50 +3240,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>504058</v>
+        <v>503952</v>
       </c>
       <c r="R25" t="n">
-        <v>7021715</v>
+        <v>7022000</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3313,6 +3308,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3344,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130222755</v>
+        <v>130222743</v>
       </c>
       <c r="B26" t="n">
-        <v>79180</v>
+        <v>91724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,26 +3355,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3382,10 +3386,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504177</v>
+        <v>504223</v>
       </c>
       <c r="R26" t="n">
-        <v>7021847</v>
+        <v>7022010</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3433,6 +3437,21 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3450,10 +3469,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130222743</v>
+        <v>130222755</v>
       </c>
       <c r="B27" t="n">
-        <v>91724</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3461,30 +3480,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3492,10 +3507,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504223</v>
+        <v>504177</v>
       </c>
       <c r="R27" t="n">
-        <v>7022010</v>
+        <v>7021847</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3543,21 +3558,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3575,10 +3575,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130222750</v>
+        <v>130222752</v>
       </c>
       <c r="B28" t="n">
-        <v>91748</v>
+        <v>79180</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3586,26 +3586,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504216</v>
+        <v>504097</v>
       </c>
       <c r="R28" t="n">
-        <v>7022005</v>
+        <v>7021762</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3681,10 +3681,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130222752</v>
+        <v>130222750</v>
       </c>
       <c r="B29" t="n">
-        <v>79180</v>
+        <v>91748</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3692,26 +3692,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504097</v>
+        <v>504216</v>
       </c>
       <c r="R29" t="n">
-        <v>7021762</v>
+        <v>7022005</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3787,10 +3787,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130222742</v>
+        <v>130222756</v>
       </c>
       <c r="B30" t="n">
-        <v>91724</v>
+        <v>79180</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3798,30 +3798,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3829,10 +3825,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504227</v>
+        <v>504101</v>
       </c>
       <c r="R30" t="n">
-        <v>7022001</v>
+        <v>7021774</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3897,7 +3893,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130222746</v>
+        <v>130222742</v>
       </c>
       <c r="B31" t="n">
         <v>91724</v>
@@ -3939,10 +3935,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503973</v>
+        <v>504227</v>
       </c>
       <c r="R31" t="n">
-        <v>7021998</v>
+        <v>7022001</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3990,21 +3986,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4022,10 +4003,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130222715</v>
+        <v>130222746</v>
       </c>
       <c r="B32" t="n">
-        <v>91728</v>
+        <v>91724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4033,21 +4014,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4064,10 +4045,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504083</v>
+        <v>503973</v>
       </c>
       <c r="R32" t="n">
-        <v>7021787</v>
+        <v>7021998</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4115,6 +4096,21 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4132,32 +4128,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130222719</v>
+        <v>130222734</v>
       </c>
       <c r="B33" t="n">
-        <v>92446</v>
+        <v>92026</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4174,10 +4170,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504219</v>
+        <v>504221</v>
       </c>
       <c r="R33" t="n">
-        <v>7022014</v>
+        <v>7022011</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4225,6 +4221,21 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4242,10 +4253,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130222734</v>
+        <v>130222715</v>
       </c>
       <c r="B34" t="n">
-        <v>92026</v>
+        <v>91728</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4253,21 +4264,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4284,10 +4295,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504221</v>
+        <v>504083</v>
       </c>
       <c r="R34" t="n">
-        <v>7022011</v>
+        <v>7021787</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4335,21 +4346,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4367,37 +4363,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130222756</v>
+        <v>130222704</v>
       </c>
       <c r="B35" t="n">
-        <v>79180</v>
+        <v>91692</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504101</v>
+        <v>504208</v>
       </c>
       <c r="R35" t="n">
-        <v>7021774</v>
+        <v>7022015</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130222704</v>
+        <v>130222719</v>
       </c>
       <c r="B36" t="n">
-        <v>91692</v>
+        <v>92446</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504208</v>
+        <v>504219</v>
       </c>
       <c r="R36" t="n">
-        <v>7022015</v>
+        <v>7022014</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4698,10 +4698,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130222718</v>
+        <v>130222728</v>
       </c>
       <c r="B38" t="n">
-        <v>92446</v>
+        <v>80189</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4709,30 +4709,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3298</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4740,10 +4736,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504098</v>
+        <v>504090</v>
       </c>
       <c r="R38" t="n">
-        <v>7022064</v>
+        <v>7021781</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4808,10 +4804,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130222728</v>
+        <v>130222718</v>
       </c>
       <c r="B39" t="n">
-        <v>80189</v>
+        <v>92446</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4819,26 +4815,30 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504090</v>
+        <v>504098</v>
       </c>
       <c r="R39" t="n">
-        <v>7021781</v>
+        <v>7022064</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4914,37 +4914,41 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130222729</v>
+        <v>130222709</v>
       </c>
       <c r="B40" t="n">
-        <v>80189</v>
+        <v>91728</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4952,10 +4956,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504173</v>
+        <v>504104</v>
       </c>
       <c r="R40" t="n">
-        <v>7021803</v>
+        <v>7021877</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5020,41 +5024,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130222709</v>
+        <v>130222729</v>
       </c>
       <c r="B41" t="n">
-        <v>91728</v>
+        <v>80189</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504104</v>
+        <v>504173</v>
       </c>
       <c r="R41" t="n">
-        <v>7021877</v>
+        <v>7021803</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5365,41 +5365,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130222733</v>
+        <v>130222699</v>
       </c>
       <c r="B44" t="n">
-        <v>92181</v>
+        <v>83158</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5407,10 +5403,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504161</v>
+        <v>504118</v>
       </c>
       <c r="R44" t="n">
-        <v>7021869</v>
+        <v>7021776</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5458,21 +5454,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5490,41 +5471,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130222744</v>
+        <v>130222726</v>
       </c>
       <c r="B45" t="n">
-        <v>91724</v>
+        <v>80314</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5532,10 +5509,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504178</v>
+        <v>504106</v>
       </c>
       <c r="R45" t="n">
-        <v>7021976</v>
+        <v>7021741</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5583,21 +5560,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5615,32 +5577,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130222745</v>
+        <v>130222733</v>
       </c>
       <c r="B46" t="n">
-        <v>91724</v>
+        <v>92181</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5657,10 +5619,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504130</v>
+        <v>504161</v>
       </c>
       <c r="R46" t="n">
-        <v>7021754</v>
+        <v>7021869</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5740,10 +5702,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130222699</v>
+        <v>130222744</v>
       </c>
       <c r="B47" t="n">
-        <v>83158</v>
+        <v>91724</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5751,26 +5713,30 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5778,10 +5744,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504118</v>
+        <v>504178</v>
       </c>
       <c r="R47" t="n">
-        <v>7021776</v>
+        <v>7021976</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5829,6 +5795,21 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5846,37 +5827,41 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130222726</v>
+        <v>130222745</v>
       </c>
       <c r="B48" t="n">
-        <v>80314</v>
+        <v>91724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5884,10 +5869,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504106</v>
+        <v>504130</v>
       </c>
       <c r="R48" t="n">
-        <v>7021741</v>
+        <v>7021754</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5935,6 +5920,21 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5952,41 +5952,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130222707</v>
+        <v>130222758</v>
       </c>
       <c r="B49" t="n">
-        <v>91692</v>
+        <v>79180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5994,10 +5990,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504161</v>
+        <v>504172</v>
       </c>
       <c r="R49" t="n">
-        <v>7021806</v>
+        <v>7021818</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6062,37 +6058,41 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130222758</v>
+        <v>130222707</v>
       </c>
       <c r="B50" t="n">
-        <v>79180</v>
+        <v>91692</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504172</v>
+        <v>504161</v>
       </c>
       <c r="R50" t="n">
-        <v>7021818</v>
+        <v>7021806</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6486,46 +6486,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130222739</v>
+        <v>130222754</v>
       </c>
       <c r="B54" t="n">
-        <v>98920</v>
+        <v>79180</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6533,10 +6524,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504054</v>
+        <v>504081</v>
       </c>
       <c r="R54" t="n">
-        <v>7021735</v>
+        <v>7021796</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6569,11 +6560,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Minst 3 plantor finns på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6716,10 +6702,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130222754</v>
+        <v>130222723</v>
       </c>
       <c r="B56" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6727,26 +6713,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6754,10 +6745,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504081</v>
+        <v>504117</v>
       </c>
       <c r="R56" t="n">
-        <v>7021796</v>
+        <v>7021735</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6792,13 +6783,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6822,42 +6817,46 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130222723</v>
+        <v>130222739</v>
       </c>
       <c r="B57" t="n">
-        <v>57826</v>
+        <v>98920</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6865,7 +6864,7 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504117</v>
+        <v>504054</v>
       </c>
       <c r="R57" t="n">
         <v>7021735</v>
@@ -6905,7 +6904,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Minst 3 plantor finns på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6914,6 +6913,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6937,46 +6937,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130222740</v>
+        <v>130222751</v>
       </c>
       <c r="B58" t="n">
-        <v>98920</v>
+        <v>91748</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6984,10 +6975,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504087</v>
+        <v>504218</v>
       </c>
       <c r="R58" t="n">
-        <v>7021765</v>
+        <v>7022019</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7022,11 +7013,6 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Minst 8 plantor på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7040,6 +7026,21 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7057,10 +7058,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130222751</v>
+        <v>130222721</v>
       </c>
       <c r="B59" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7068,24 +7069,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7095,10 +7101,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504218</v>
+        <v>503954</v>
       </c>
       <c r="R59" t="n">
-        <v>7022019</v>
+        <v>7021984</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7133,34 +7139,23 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7178,10 +7173,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130222748</v>
+        <v>130222741</v>
       </c>
       <c r="B60" t="n">
-        <v>91742</v>
+        <v>91724</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7189,21 +7184,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7220,10 +7215,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504123</v>
+        <v>504078</v>
       </c>
       <c r="R60" t="n">
-        <v>7021748</v>
+        <v>7022057</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7271,6 +7266,21 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7288,10 +7298,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130222741</v>
+        <v>130222748</v>
       </c>
       <c r="B61" t="n">
-        <v>91724</v>
+        <v>91742</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7299,21 +7309,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7330,10 +7340,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504078</v>
+        <v>504123</v>
       </c>
       <c r="R61" t="n">
-        <v>7022057</v>
+        <v>7021748</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7381,21 +7391,6 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7413,42 +7408,46 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130222721</v>
+        <v>130222740</v>
       </c>
       <c r="B62" t="n">
-        <v>57826</v>
+        <v>98920</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7456,10 +7455,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503954</v>
+        <v>504087</v>
       </c>
       <c r="R62" t="n">
-        <v>7021984</v>
+        <v>7021765</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7496,7 +7495,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Minst 8 plantor på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7505,6 +7504,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -1795,37 +1795,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130222701</v>
+        <v>130222705</v>
       </c>
       <c r="B12" t="n">
-        <v>83158</v>
+        <v>91692</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1833,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504090</v>
+        <v>504210</v>
       </c>
       <c r="R12" t="n">
-        <v>7021787</v>
+        <v>7022007</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,41 +1905,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130222705</v>
+        <v>130222701</v>
       </c>
       <c r="B13" t="n">
-        <v>91692</v>
+        <v>83158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504210</v>
+        <v>504090</v>
       </c>
       <c r="R13" t="n">
-        <v>7022007</v>
+        <v>7021787</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2117,37 +2117,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222730</v>
+        <v>130222713</v>
       </c>
       <c r="B15" t="n">
-        <v>80189</v>
+        <v>91728</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2155,10 +2159,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504166</v>
+        <v>504135</v>
       </c>
       <c r="R15" t="n">
-        <v>7021800</v>
+        <v>7021768</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,10 +2227,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130222724</v>
+        <v>130222711</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,29 +2238,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2266,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504139</v>
+        <v>504154</v>
       </c>
       <c r="R16" t="n">
-        <v>7021798</v>
+        <v>7021848</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,17 +2307,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2338,41 +2337,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130222713</v>
+        <v>130222730</v>
       </c>
       <c r="B17" t="n">
-        <v>91728</v>
+        <v>80189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2380,10 +2375,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>504135</v>
+        <v>504166</v>
       </c>
       <c r="R17" t="n">
-        <v>7021768</v>
+        <v>7021800</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,10 +2443,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130222711</v>
+        <v>130222724</v>
       </c>
       <c r="B18" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2459,28 +2454,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2490,10 +2486,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504154</v>
+        <v>504139</v>
       </c>
       <c r="R18" t="n">
-        <v>7021848</v>
+        <v>7021798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2528,13 +2524,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -4367,37 +4367,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130222756</v>
+        <v>130222704</v>
       </c>
       <c r="B35" t="n">
-        <v>79180</v>
+        <v>91692</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4405,10 +4409,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504101</v>
+        <v>504208</v>
       </c>
       <c r="R35" t="n">
-        <v>7021774</v>
+        <v>7022015</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4473,10 +4477,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130222722</v>
+        <v>130222756</v>
       </c>
       <c r="B36" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4484,31 +4488,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4516,10 +4515,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503979</v>
+        <v>504101</v>
       </c>
       <c r="R36" t="n">
-        <v>7022007</v>
+        <v>7021774</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4554,17 +4553,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4588,39 +4583,40 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130222704</v>
+        <v>130222722</v>
       </c>
       <c r="B37" t="n">
-        <v>91692</v>
+        <v>57826</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4630,10 +4626,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504208</v>
+        <v>503979</v>
       </c>
       <c r="R37" t="n">
-        <v>7022015</v>
+        <v>7022007</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4668,13 +4664,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -6168,10 +6168,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130222738</v>
+        <v>130222703</v>
       </c>
       <c r="B51" t="n">
-        <v>78192</v>
+        <v>83158</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6179,21 +6179,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6206,10 +6206,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504087</v>
+        <v>504170</v>
       </c>
       <c r="R51" t="n">
-        <v>7021791</v>
+        <v>7021803</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6274,10 +6274,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130222703</v>
+        <v>130222738</v>
       </c>
       <c r="B52" t="n">
-        <v>83158</v>
+        <v>78192</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504170</v>
+        <v>504087</v>
       </c>
       <c r="R52" t="n">
-        <v>7021803</v>
+        <v>7021791</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -2558,37 +2558,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130222700</v>
+        <v>130222727</v>
       </c>
       <c r="B19" t="n">
-        <v>83158</v>
+        <v>92451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>67</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2596,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504099</v>
+        <v>504089</v>
       </c>
       <c r="R19" t="n">
-        <v>7021769</v>
+        <v>7021772</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2647,6 +2651,21 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2664,32 +2683,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130222727</v>
+        <v>130222706</v>
       </c>
       <c r="B20" t="n">
-        <v>92451</v>
+        <v>91692</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>67</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2706,10 +2725,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504089</v>
+        <v>504083</v>
       </c>
       <c r="R20" t="n">
-        <v>7021772</v>
+        <v>7021773</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2757,21 +2776,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2789,41 +2793,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130222706</v>
+        <v>130222700</v>
       </c>
       <c r="B21" t="n">
-        <v>91692</v>
+        <v>83158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>504083</v>
+        <v>504099</v>
       </c>
       <c r="R21" t="n">
-        <v>7021773</v>
+        <v>7021769</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130222720</v>
+        <v>130222725</v>
       </c>
       <c r="B24" t="n">
-        <v>57826</v>
+        <v>57985</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,42 +3122,50 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503952</v>
+        <v>504058</v>
       </c>
       <c r="R24" t="n">
-        <v>7022000</v>
+        <v>7021715</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3190,11 +3198,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3226,10 +3229,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130222725</v>
+        <v>130222720</v>
       </c>
       <c r="B25" t="n">
-        <v>57985</v>
+        <v>57826</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,50 +3240,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>504058</v>
+        <v>503952</v>
       </c>
       <c r="R25" t="n">
-        <v>7021715</v>
+        <v>7022000</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3313,6 +3308,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4367,41 +4367,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130222704</v>
+        <v>130222756</v>
       </c>
       <c r="B35" t="n">
-        <v>91692</v>
+        <v>79180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4409,10 +4405,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504208</v>
+        <v>504101</v>
       </c>
       <c r="R35" t="n">
-        <v>7022015</v>
+        <v>7021774</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4477,10 +4473,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130222756</v>
+        <v>130222722</v>
       </c>
       <c r="B36" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4488,26 +4484,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4515,10 +4516,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504101</v>
+        <v>503979</v>
       </c>
       <c r="R36" t="n">
-        <v>7021774</v>
+        <v>7022007</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4553,13 +4554,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4583,40 +4588,39 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130222722</v>
+        <v>130222704</v>
       </c>
       <c r="B37" t="n">
-        <v>57826</v>
+        <v>91692</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4626,10 +4630,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503979</v>
+        <v>504208</v>
       </c>
       <c r="R37" t="n">
-        <v>7022007</v>
+        <v>7022015</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4664,17 +4668,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -1795,41 +1795,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130222705</v>
+        <v>130222701</v>
       </c>
       <c r="B12" t="n">
-        <v>91692</v>
+        <v>83158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1837,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504210</v>
+        <v>504090</v>
       </c>
       <c r="R12" t="n">
-        <v>7022007</v>
+        <v>7021787</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,37 +1901,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130222701</v>
+        <v>130222705</v>
       </c>
       <c r="B13" t="n">
-        <v>83158</v>
+        <v>91692</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504090</v>
+        <v>504210</v>
       </c>
       <c r="R13" t="n">
-        <v>7021787</v>
+        <v>7022007</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2117,41 +2117,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222713</v>
+        <v>130222730</v>
       </c>
       <c r="B15" t="n">
-        <v>91728</v>
+        <v>80189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2159,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504135</v>
+        <v>504166</v>
       </c>
       <c r="R15" t="n">
-        <v>7021768</v>
+        <v>7021800</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130222711</v>
+        <v>130222724</v>
       </c>
       <c r="B16" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,28 +2234,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2269,10 +2266,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504154</v>
+        <v>504139</v>
       </c>
       <c r="R16" t="n">
-        <v>7021848</v>
+        <v>7021798</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2307,13 +2304,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2337,37 +2338,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130222730</v>
+        <v>130222713</v>
       </c>
       <c r="B17" t="n">
-        <v>80189</v>
+        <v>91728</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2375,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>504166</v>
+        <v>504135</v>
       </c>
       <c r="R17" t="n">
-        <v>7021800</v>
+        <v>7021768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2443,10 +2448,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130222724</v>
+        <v>130222711</v>
       </c>
       <c r="B18" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,29 +2459,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2486,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504139</v>
+        <v>504154</v>
       </c>
       <c r="R18" t="n">
-        <v>7021798</v>
+        <v>7021848</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2524,17 +2528,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2558,41 +2558,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130222727</v>
+        <v>130222700</v>
       </c>
       <c r="B19" t="n">
-        <v>92451</v>
+        <v>83158</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>67</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2600,10 +2596,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504089</v>
+        <v>504099</v>
       </c>
       <c r="R19" t="n">
-        <v>7021772</v>
+        <v>7021769</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2651,21 +2647,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2683,32 +2664,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130222706</v>
+        <v>130222727</v>
       </c>
       <c r="B20" t="n">
-        <v>91692</v>
+        <v>92451</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>67</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2725,10 +2706,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504083</v>
+        <v>504089</v>
       </c>
       <c r="R20" t="n">
-        <v>7021773</v>
+        <v>7021772</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,6 +2757,21 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2793,37 +2789,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130222700</v>
+        <v>130222706</v>
       </c>
       <c r="B21" t="n">
-        <v>83158</v>
+        <v>91692</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>504099</v>
+        <v>504083</v>
       </c>
       <c r="R21" t="n">
-        <v>7021769</v>
+        <v>7021773</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130222725</v>
+        <v>130222720</v>
       </c>
       <c r="B24" t="n">
-        <v>57985</v>
+        <v>57826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,50 +3122,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504058</v>
+        <v>503952</v>
       </c>
       <c r="R24" t="n">
-        <v>7021715</v>
+        <v>7022000</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3198,6 +3190,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3229,10 +3226,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130222720</v>
+        <v>130222725</v>
       </c>
       <c r="B25" t="n">
-        <v>57826</v>
+        <v>57985</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,42 +3237,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503952</v>
+        <v>504058</v>
       </c>
       <c r="R25" t="n">
-        <v>7022000</v>
+        <v>7021715</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3308,11 +3313,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -6168,10 +6168,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130222703</v>
+        <v>130222738</v>
       </c>
       <c r="B51" t="n">
-        <v>83158</v>
+        <v>78192</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6179,21 +6179,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6206,10 +6206,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504170</v>
+        <v>504087</v>
       </c>
       <c r="R51" t="n">
-        <v>7021803</v>
+        <v>7021791</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6274,10 +6274,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130222738</v>
+        <v>130222703</v>
       </c>
       <c r="B52" t="n">
-        <v>78192</v>
+        <v>83158</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504087</v>
+        <v>504170</v>
       </c>
       <c r="R52" t="n">
-        <v>7021791</v>
+        <v>7021803</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130222754</v>
+        <v>130222723</v>
       </c>
       <c r="B55" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6607,26 +6607,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6634,10 +6639,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504081</v>
+        <v>504117</v>
       </c>
       <c r="R55" t="n">
-        <v>7021796</v>
+        <v>7021735</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6672,13 +6677,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6702,10 +6711,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130222723</v>
+        <v>130222754</v>
       </c>
       <c r="B56" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6713,31 +6722,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6745,10 +6749,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504117</v>
+        <v>504081</v>
       </c>
       <c r="R56" t="n">
-        <v>7021735</v>
+        <v>7021796</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6783,17 +6787,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,7 +888,7 @@
         <v>130222731</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>130222710</v>
       </c>
       <c r="B5" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>130222749</v>
       </c>
       <c r="B6" t="n">
-        <v>91742</v>
+        <v>91745</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>130222714</v>
       </c>
       <c r="B7" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>130222732</v>
       </c>
       <c r="B8" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>130222712</v>
       </c>
       <c r="B9" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>130222716</v>
       </c>
       <c r="B10" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130222736</v>
+        <v>130222701</v>
       </c>
       <c r="B11" t="n">
-        <v>92026</v>
+        <v>83161</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,30 +1696,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1727,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504081</v>
+        <v>504090</v>
       </c>
       <c r="R11" t="n">
-        <v>7021794</v>
+        <v>7021787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,37 +1791,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130222701</v>
+        <v>130222705</v>
       </c>
       <c r="B12" t="n">
-        <v>83158</v>
+        <v>91695</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504090</v>
+        <v>504210</v>
       </c>
       <c r="R12" t="n">
-        <v>7021787</v>
+        <v>7022007</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,32 +1901,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130222705</v>
+        <v>130222736</v>
       </c>
       <c r="B13" t="n">
-        <v>91692</v>
+        <v>92029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504210</v>
+        <v>504081</v>
       </c>
       <c r="R13" t="n">
-        <v>7022007</v>
+        <v>7021794</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130222702</v>
+        <v>130222713</v>
       </c>
       <c r="B14" t="n">
-        <v>83158</v>
+        <v>91731</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,26 +2022,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2049,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504100</v>
+        <v>504135</v>
       </c>
       <c r="R14" t="n">
-        <v>7021801</v>
+        <v>7021768</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,37 +2121,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222730</v>
+        <v>130222711</v>
       </c>
       <c r="B15" t="n">
-        <v>80189</v>
+        <v>91731</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2155,10 +2163,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504166</v>
+        <v>504154</v>
       </c>
       <c r="R15" t="n">
-        <v>7021800</v>
+        <v>7021848</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130222724</v>
+        <v>130222702</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>83161</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,31 +2242,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2266,10 +2269,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504139</v>
+        <v>504100</v>
       </c>
       <c r="R16" t="n">
-        <v>7021798</v>
+        <v>7021801</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,17 +2307,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2338,41 +2337,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130222713</v>
+        <v>130222730</v>
       </c>
       <c r="B17" t="n">
-        <v>91728</v>
+        <v>80192</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2380,10 +2375,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>504135</v>
+        <v>504166</v>
       </c>
       <c r="R17" t="n">
-        <v>7021768</v>
+        <v>7021800</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,10 +2443,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130222711</v>
+        <v>130222724</v>
       </c>
       <c r="B18" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2459,28 +2454,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2490,10 +2486,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504154</v>
+        <v>504139</v>
       </c>
       <c r="R18" t="n">
-        <v>7021848</v>
+        <v>7021798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2528,13 +2524,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2558,37 +2558,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130222700</v>
+        <v>130222727</v>
       </c>
       <c r="B19" t="n">
-        <v>83158</v>
+        <v>92454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>67</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2596,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504099</v>
+        <v>504089</v>
       </c>
       <c r="R19" t="n">
-        <v>7021769</v>
+        <v>7021772</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2647,6 +2651,21 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2664,32 +2683,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130222727</v>
+        <v>130222706</v>
       </c>
       <c r="B20" t="n">
-        <v>92451</v>
+        <v>91695</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>67</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2706,10 +2725,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504089</v>
+        <v>504083</v>
       </c>
       <c r="R20" t="n">
-        <v>7021772</v>
+        <v>7021773</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2757,21 +2776,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2789,41 +2793,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130222706</v>
+        <v>130222700</v>
       </c>
       <c r="B21" t="n">
-        <v>91692</v>
+        <v>83161</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>504083</v>
+        <v>504099</v>
       </c>
       <c r="R21" t="n">
-        <v>7021773</v>
+        <v>7021769</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130222753</v>
+        <v>130222720</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,26 +2910,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2937,10 +2942,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>504059</v>
+        <v>503952</v>
       </c>
       <c r="R22" t="n">
-        <v>7021781</v>
+        <v>7022000</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2975,13 +2980,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3005,10 +3014,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130222757</v>
+        <v>130222753</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3043,10 +3052,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504170</v>
+        <v>504059</v>
       </c>
       <c r="R23" t="n">
-        <v>7021800</v>
+        <v>7021781</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3111,10 +3120,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130222720</v>
+        <v>130222757</v>
       </c>
       <c r="B24" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,31 +3131,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3154,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503952</v>
+        <v>504170</v>
       </c>
       <c r="R24" t="n">
-        <v>7022000</v>
+        <v>7021800</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3192,17 +3196,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>130222743</v>
       </c>
       <c r="B26" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>130222755</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3575,10 +3575,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130222750</v>
+        <v>130222752</v>
       </c>
       <c r="B28" t="n">
-        <v>91748</v>
+        <v>79183</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3586,26 +3586,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504216</v>
+        <v>504097</v>
       </c>
       <c r="R28" t="n">
-        <v>7022005</v>
+        <v>7021762</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3681,10 +3681,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130222752</v>
+        <v>130222750</v>
       </c>
       <c r="B29" t="n">
-        <v>79180</v>
+        <v>91751</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3692,26 +3692,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504097</v>
+        <v>504216</v>
       </c>
       <c r="R29" t="n">
-        <v>7021762</v>
+        <v>7022005</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3790,7 +3790,7 @@
         <v>130222742</v>
       </c>
       <c r="B30" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>130222746</v>
       </c>
       <c r="B31" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4022,10 +4022,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130222715</v>
+        <v>130222734</v>
       </c>
       <c r="B32" t="n">
-        <v>91728</v>
+        <v>92029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4033,21 +4033,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504083</v>
+        <v>504221</v>
       </c>
       <c r="R32" t="n">
-        <v>7021787</v>
+        <v>7022011</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4115,6 +4115,21 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4132,10 +4147,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130222734</v>
+        <v>130222715</v>
       </c>
       <c r="B33" t="n">
-        <v>92026</v>
+        <v>91731</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4143,21 +4158,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4174,10 +4189,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504221</v>
+        <v>504083</v>
       </c>
       <c r="R33" t="n">
-        <v>7022011</v>
+        <v>7021787</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4225,21 +4240,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4257,41 +4257,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130222719</v>
+        <v>130222756</v>
       </c>
       <c r="B34" t="n">
-        <v>92446</v>
+        <v>79183</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4299,10 +4295,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504219</v>
+        <v>504101</v>
       </c>
       <c r="R34" t="n">
-        <v>7022014</v>
+        <v>7021774</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4367,37 +4363,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130222756</v>
+        <v>130222704</v>
       </c>
       <c r="B35" t="n">
-        <v>79180</v>
+        <v>91695</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504101</v>
+        <v>504208</v>
       </c>
       <c r="R35" t="n">
-        <v>7021774</v>
+        <v>7022015</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4473,40 +4473,39 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130222722</v>
+        <v>130222719</v>
       </c>
       <c r="B36" t="n">
-        <v>57826</v>
+        <v>92449</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4516,10 +4515,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503979</v>
+        <v>504219</v>
       </c>
       <c r="R36" t="n">
-        <v>7022007</v>
+        <v>7022014</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4554,17 +4553,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4588,39 +4583,40 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130222704</v>
+        <v>130222722</v>
       </c>
       <c r="B37" t="n">
-        <v>91692</v>
+        <v>57826</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4630,10 +4626,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504208</v>
+        <v>503979</v>
       </c>
       <c r="R37" t="n">
-        <v>7022015</v>
+        <v>7022007</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4668,13 +4664,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4698,10 +4698,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130222718</v>
+        <v>130222728</v>
       </c>
       <c r="B38" t="n">
-        <v>92446</v>
+        <v>80192</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4709,30 +4709,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3298</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4740,10 +4736,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504098</v>
+        <v>504090</v>
       </c>
       <c r="R38" t="n">
-        <v>7022064</v>
+        <v>7021781</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4808,10 +4804,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130222728</v>
+        <v>130222718</v>
       </c>
       <c r="B39" t="n">
-        <v>80189</v>
+        <v>92449</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4819,26 +4815,30 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504090</v>
+        <v>504098</v>
       </c>
       <c r="R39" t="n">
-        <v>7021781</v>
+        <v>7022064</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4917,7 +4917,7 @@
         <v>130222709</v>
       </c>
       <c r="B40" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>130222729</v>
       </c>
       <c r="B41" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5130,10 +5130,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130222708</v>
+        <v>130222735</v>
       </c>
       <c r="B42" t="n">
-        <v>91728</v>
+        <v>92029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504191</v>
+        <v>504166</v>
       </c>
       <c r="R42" t="n">
-        <v>7022006</v>
+        <v>7021986</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5223,6 +5223,21 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5240,10 +5255,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130222735</v>
+        <v>130222708</v>
       </c>
       <c r="B43" t="n">
-        <v>92026</v>
+        <v>91731</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5251,21 +5266,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5282,10 +5297,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504166</v>
+        <v>504191</v>
       </c>
       <c r="R43" t="n">
-        <v>7021986</v>
+        <v>7022006</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5333,21 +5348,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5365,37 +5365,41 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130222726</v>
+        <v>130222744</v>
       </c>
       <c r="B44" t="n">
-        <v>80314</v>
+        <v>91727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5403,10 +5407,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504106</v>
+        <v>504178</v>
       </c>
       <c r="R44" t="n">
-        <v>7021741</v>
+        <v>7021976</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5454,6 +5458,21 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5471,32 +5490,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130222733</v>
+        <v>130222745</v>
       </c>
       <c r="B45" t="n">
-        <v>92181</v>
+        <v>91727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5513,10 +5532,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504161</v>
+        <v>504130</v>
       </c>
       <c r="R45" t="n">
-        <v>7021869</v>
+        <v>7021754</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5596,41 +5615,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130222744</v>
+        <v>130222726</v>
       </c>
       <c r="B46" t="n">
-        <v>91724</v>
+        <v>80317</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5638,10 +5653,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504178</v>
+        <v>504106</v>
       </c>
       <c r="R46" t="n">
-        <v>7021976</v>
+        <v>7021741</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5689,21 +5704,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5721,32 +5721,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130222745</v>
+        <v>130222733</v>
       </c>
       <c r="B47" t="n">
-        <v>91724</v>
+        <v>92184</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5763,10 +5763,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504130</v>
+        <v>504161</v>
       </c>
       <c r="R47" t="n">
-        <v>7021754</v>
+        <v>7021869</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5849,7 +5849,7 @@
         <v>130222699</v>
       </c>
       <c r="B48" t="n">
-        <v>83158</v>
+        <v>83161</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>130222707</v>
       </c>
       <c r="B49" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>130222758</v>
       </c>
       <c r="B50" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6168,10 +6168,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130222738</v>
+        <v>130222703</v>
       </c>
       <c r="B51" t="n">
-        <v>78192</v>
+        <v>83161</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6179,21 +6179,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6206,10 +6206,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504087</v>
+        <v>504170</v>
       </c>
       <c r="R51" t="n">
-        <v>7021791</v>
+        <v>7021803</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6274,10 +6274,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130222703</v>
+        <v>130222738</v>
       </c>
       <c r="B52" t="n">
-        <v>83158</v>
+        <v>78195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504170</v>
+        <v>504087</v>
       </c>
       <c r="R52" t="n">
-        <v>7021803</v>
+        <v>7021791</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6383,7 +6383,7 @@
         <v>130222737</v>
       </c>
       <c r="B53" t="n">
-        <v>78192</v>
+        <v>78195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6486,10 +6486,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130222747</v>
+        <v>130222754</v>
       </c>
       <c r="B54" t="n">
-        <v>91742</v>
+        <v>79183</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6497,30 +6497,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6528,10 +6524,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504210</v>
+        <v>504081</v>
       </c>
       <c r="R54" t="n">
-        <v>7022007</v>
+        <v>7021796</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6596,42 +6592,46 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130222723</v>
+        <v>130222739</v>
       </c>
       <c r="B55" t="n">
-        <v>57826</v>
+        <v>98923</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504117</v>
+        <v>504054</v>
       </c>
       <c r="R55" t="n">
         <v>7021735</v>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Minst 3 plantor finns på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6688,6 +6688,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6711,10 +6712,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130222754</v>
+        <v>130222747</v>
       </c>
       <c r="B56" t="n">
-        <v>79180</v>
+        <v>91745</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6722,26 +6723,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6749,10 +6754,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504081</v>
+        <v>504210</v>
       </c>
       <c r="R56" t="n">
-        <v>7021796</v>
+        <v>7022007</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6817,46 +6822,42 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130222739</v>
+        <v>130222723</v>
       </c>
       <c r="B57" t="n">
-        <v>98920</v>
+        <v>57826</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6864,7 +6865,7 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504054</v>
+        <v>504117</v>
       </c>
       <c r="R57" t="n">
         <v>7021735</v>
@@ -6904,7 +6905,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 3 plantor finns på fyndplatsen.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6913,7 +6914,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6937,10 +6937,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130222748</v>
+        <v>130222741</v>
       </c>
       <c r="B58" t="n">
-        <v>91742</v>
+        <v>91727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6948,21 +6948,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6979,10 +6979,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504123</v>
+        <v>504078</v>
       </c>
       <c r="R58" t="n">
-        <v>7021748</v>
+        <v>7022057</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7030,6 +7030,21 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7047,10 +7062,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130222741</v>
+        <v>130222751</v>
       </c>
       <c r="B59" t="n">
-        <v>91724</v>
+        <v>91751</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7058,23 +7073,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
@@ -7089,10 +7100,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504078</v>
+        <v>504218</v>
       </c>
       <c r="R59" t="n">
-        <v>7022057</v>
+        <v>7022019</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7172,10 +7183,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130222751</v>
+        <v>130222721</v>
       </c>
       <c r="B60" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7183,24 +7194,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7210,10 +7226,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504218</v>
+        <v>503954</v>
       </c>
       <c r="R60" t="n">
-        <v>7022019</v>
+        <v>7021984</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7248,34 +7264,23 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7293,46 +7298,41 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130222740</v>
+        <v>130222748</v>
       </c>
       <c r="B61" t="n">
-        <v>98920</v>
+        <v>91745</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504087</v>
+        <v>504123</v>
       </c>
       <c r="R61" t="n">
-        <v>7021765</v>
+        <v>7021748</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7376,11 +7376,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Minst 8 plantor på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7413,42 +7408,46 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130222721</v>
+        <v>130222740</v>
       </c>
       <c r="B62" t="n">
-        <v>57826</v>
+        <v>98923</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7456,10 +7455,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503954</v>
+        <v>504087</v>
       </c>
       <c r="R62" t="n">
-        <v>7021984</v>
+        <v>7021765</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7496,7 +7495,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Minst 8 plantor på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7505,6 +7504,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7525,6 +7525,1246 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>130619758</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79209</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>504047</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7021752</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>130619765</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57852</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>503938</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7021990</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>130619759</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79209</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>504159</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7021846</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>130619766</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57852</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>503958</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7021988</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>130619760</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80314</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>504274</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7021941</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På döende eller död sälg</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>130619762</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79209</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>504212</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7021967</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>130619764</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57033</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>504059</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7022053</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>130619769</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91753</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>504228</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7021996</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På grov torraka av gran, bhd 45 cm</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>130619761</v>
+      </c>
+      <c r="B71" t="n">
+        <v>92475</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>504231</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7021975</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På död gran</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>130619768</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79209</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>504172</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7022030</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På torraka av gran</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>130619767</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79209</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Eliasbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>504062</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7022023</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Elin Albrechtsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>130222731</v>
       </c>
       <c r="B4" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>130222710</v>
       </c>
       <c r="B5" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130222749</v>
+        <v>130222714</v>
       </c>
       <c r="B6" t="n">
-        <v>91745</v>
+        <v>91757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504067</v>
+        <v>504091</v>
       </c>
       <c r="R6" t="n">
-        <v>7021774</v>
+        <v>7021759</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130222714</v>
+        <v>130222749</v>
       </c>
       <c r="B7" t="n">
-        <v>91731</v>
+        <v>91771</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504091</v>
+        <v>504067</v>
       </c>
       <c r="R7" t="n">
-        <v>7021759</v>
+        <v>7021774</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,32 +1340,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130222732</v>
+        <v>130222712</v>
       </c>
       <c r="B8" t="n">
-        <v>92184</v>
+        <v>91757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504202</v>
+        <v>504057</v>
       </c>
       <c r="R8" t="n">
-        <v>7022015</v>
+        <v>7021765</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,21 +1433,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1465,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130222712</v>
+        <v>130222716</v>
       </c>
       <c r="B9" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504057</v>
+        <v>504095</v>
       </c>
       <c r="R9" t="n">
-        <v>7021765</v>
+        <v>7021805</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,32 +1560,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130222716</v>
+        <v>130222732</v>
       </c>
       <c r="B10" t="n">
-        <v>91731</v>
+        <v>92210</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1617,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504095</v>
+        <v>504202</v>
       </c>
       <c r="R10" t="n">
-        <v>7021805</v>
+        <v>7022015</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,6 +1653,21 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130222701</v>
+        <v>130222736</v>
       </c>
       <c r="B11" t="n">
-        <v>83161</v>
+        <v>92055</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,26 +1696,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1723,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504090</v>
+        <v>504081</v>
       </c>
       <c r="R11" t="n">
-        <v>7021787</v>
+        <v>7021794</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,41 +1795,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130222705</v>
+        <v>130222701</v>
       </c>
       <c r="B12" t="n">
-        <v>91695</v>
+        <v>83187</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504210</v>
+        <v>504090</v>
       </c>
       <c r="R12" t="n">
-        <v>7022007</v>
+        <v>7021787</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,32 +1901,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130222736</v>
+        <v>130222705</v>
       </c>
       <c r="B13" t="n">
-        <v>92029</v>
+        <v>91721</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504081</v>
+        <v>504210</v>
       </c>
       <c r="R13" t="n">
-        <v>7021794</v>
+        <v>7022007</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
         <v>130222713</v>
       </c>
       <c r="B14" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>130222711</v>
       </c>
       <c r="B15" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>130222702</v>
       </c>
       <c r="B16" t="n">
-        <v>83161</v>
+        <v>83187</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>130222730</v>
       </c>
       <c r="B17" t="n">
-        <v>80192</v>
+        <v>80218</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>130222724</v>
       </c>
       <c r="B18" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,32 +2558,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130222727</v>
+        <v>130222706</v>
       </c>
       <c r="B19" t="n">
-        <v>92454</v>
+        <v>91721</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>67</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504089</v>
+        <v>504083</v>
       </c>
       <c r="R19" t="n">
-        <v>7021772</v>
+        <v>7021773</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2651,21 +2651,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2683,32 +2668,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130222706</v>
+        <v>130222727</v>
       </c>
       <c r="B20" t="n">
-        <v>91695</v>
+        <v>92480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>67</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2725,10 +2710,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504083</v>
+        <v>504089</v>
       </c>
       <c r="R20" t="n">
-        <v>7021773</v>
+        <v>7021772</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2776,6 +2761,21 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2796,7 +2796,7 @@
         <v>130222700</v>
       </c>
       <c r="B21" t="n">
-        <v>83161</v>
+        <v>83187</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130222720</v>
+        <v>130222725</v>
       </c>
       <c r="B22" t="n">
-        <v>57826</v>
+        <v>58011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,42 +2910,50 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503952</v>
+        <v>504058</v>
       </c>
       <c r="R22" t="n">
-        <v>7022000</v>
+        <v>7021715</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2978,11 +2986,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3017,7 +3020,7 @@
         <v>130222753</v>
       </c>
       <c r="B23" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3126,7 @@
         <v>130222757</v>
       </c>
       <c r="B24" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3226,10 +3229,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130222725</v>
+        <v>130222720</v>
       </c>
       <c r="B25" t="n">
-        <v>57985</v>
+        <v>57852</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,50 +3240,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>504058</v>
+        <v>503952</v>
       </c>
       <c r="R25" t="n">
-        <v>7021715</v>
+        <v>7022000</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3313,6 +3308,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,7 +3347,7 @@
         <v>130222743</v>
       </c>
       <c r="B26" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>130222755</v>
       </c>
       <c r="B27" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>130222752</v>
       </c>
       <c r="B28" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>130222750</v>
       </c>
       <c r="B29" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3787,10 +3787,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130222742</v>
+        <v>130222756</v>
       </c>
       <c r="B30" t="n">
-        <v>91727</v>
+        <v>79209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3798,30 +3798,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3829,10 +3825,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504227</v>
+        <v>504101</v>
       </c>
       <c r="R30" t="n">
-        <v>7022001</v>
+        <v>7021774</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3897,32 +3893,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130222746</v>
+        <v>130222704</v>
       </c>
       <c r="B31" t="n">
-        <v>91727</v>
+        <v>91721</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3939,10 +3935,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503973</v>
+        <v>504208</v>
       </c>
       <c r="R31" t="n">
-        <v>7021998</v>
+        <v>7022015</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3990,21 +3986,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4022,32 +4003,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130222734</v>
+        <v>130222719</v>
       </c>
       <c r="B32" t="n">
-        <v>92029</v>
+        <v>92475</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4064,10 +4045,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504221</v>
+        <v>504219</v>
       </c>
       <c r="R32" t="n">
-        <v>7022011</v>
+        <v>7022014</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4115,21 +4096,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4147,10 +4113,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130222715</v>
+        <v>130222742</v>
       </c>
       <c r="B33" t="n">
-        <v>91731</v>
+        <v>91753</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4158,21 +4124,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4189,10 +4155,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504083</v>
+        <v>504227</v>
       </c>
       <c r="R33" t="n">
-        <v>7021787</v>
+        <v>7022001</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4257,10 +4223,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130222756</v>
+        <v>130222746</v>
       </c>
       <c r="B34" t="n">
-        <v>79183</v>
+        <v>91753</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4268,26 +4234,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4295,10 +4265,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504101</v>
+        <v>503973</v>
       </c>
       <c r="R34" t="n">
-        <v>7021774</v>
+        <v>7021998</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4346,6 +4316,21 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4363,32 +4348,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130222704</v>
+        <v>130222734</v>
       </c>
       <c r="B35" t="n">
-        <v>91695</v>
+        <v>92055</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4405,10 +4390,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504208</v>
+        <v>504221</v>
       </c>
       <c r="R35" t="n">
-        <v>7022015</v>
+        <v>7022011</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4456,6 +4441,21 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4473,32 +4473,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130222719</v>
+        <v>130222715</v>
       </c>
       <c r="B36" t="n">
-        <v>92449</v>
+        <v>91757</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504219</v>
+        <v>504083</v>
       </c>
       <c r="R36" t="n">
-        <v>7022014</v>
+        <v>7021787</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4586,7 +4586,7 @@
         <v>130222722</v>
       </c>
       <c r="B37" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>130222728</v>
       </c>
       <c r="B38" t="n">
-        <v>80192</v>
+        <v>80218</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>130222718</v>
       </c>
       <c r="B39" t="n">
-        <v>92449</v>
+        <v>92475</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>130222709</v>
       </c>
       <c r="B40" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>130222729</v>
       </c>
       <c r="B41" t="n">
-        <v>80192</v>
+        <v>80218</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>130222735</v>
       </c>
       <c r="B42" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>130222708</v>
       </c>
       <c r="B43" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5365,32 +5365,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130222744</v>
+        <v>130222733</v>
       </c>
       <c r="B44" t="n">
-        <v>91727</v>
+        <v>92210</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504178</v>
+        <v>504161</v>
       </c>
       <c r="R44" t="n">
-        <v>7021976</v>
+        <v>7021869</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5490,41 +5490,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130222745</v>
+        <v>130222726</v>
       </c>
       <c r="B45" t="n">
-        <v>91727</v>
+        <v>80343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5532,10 +5528,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504130</v>
+        <v>504106</v>
       </c>
       <c r="R45" t="n">
-        <v>7021754</v>
+        <v>7021741</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5583,21 +5579,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5615,32 +5596,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130222726</v>
+        <v>130222699</v>
       </c>
       <c r="B46" t="n">
-        <v>80317</v>
+        <v>83187</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5653,10 +5634,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504106</v>
+        <v>504118</v>
       </c>
       <c r="R46" t="n">
-        <v>7021741</v>
+        <v>7021776</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5721,32 +5702,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130222733</v>
+        <v>130222744</v>
       </c>
       <c r="B47" t="n">
-        <v>92184</v>
+        <v>91753</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5763,10 +5744,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504161</v>
+        <v>504178</v>
       </c>
       <c r="R47" t="n">
-        <v>7021869</v>
+        <v>7021976</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5846,10 +5827,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130222699</v>
+        <v>130222745</v>
       </c>
       <c r="B48" t="n">
-        <v>83161</v>
+        <v>91753</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5857,26 +5838,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5884,10 +5869,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504118</v>
+        <v>504130</v>
       </c>
       <c r="R48" t="n">
-        <v>7021776</v>
+        <v>7021754</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5935,6 +5920,21 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5952,41 +5952,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130222707</v>
+        <v>130222758</v>
       </c>
       <c r="B49" t="n">
-        <v>91695</v>
+        <v>79209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5994,10 +5990,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504161</v>
+        <v>504172</v>
       </c>
       <c r="R49" t="n">
-        <v>7021806</v>
+        <v>7021818</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6062,37 +6058,41 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130222758</v>
+        <v>130222707</v>
       </c>
       <c r="B50" t="n">
-        <v>79183</v>
+        <v>91721</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504172</v>
+        <v>504161</v>
       </c>
       <c r="R50" t="n">
-        <v>7021818</v>
+        <v>7021806</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6171,7 +6171,7 @@
         <v>130222703</v>
       </c>
       <c r="B51" t="n">
-        <v>83161</v>
+        <v>83187</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>130222738</v>
       </c>
       <c r="B52" t="n">
-        <v>78195</v>
+        <v>78221</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>130222737</v>
       </c>
       <c r="B53" t="n">
-        <v>78195</v>
+        <v>78221</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6486,10 +6486,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130222754</v>
+        <v>130222723</v>
       </c>
       <c r="B54" t="n">
-        <v>79183</v>
+        <v>57852</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6497,26 +6497,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6524,10 +6529,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504081</v>
+        <v>504117</v>
       </c>
       <c r="R54" t="n">
-        <v>7021796</v>
+        <v>7021735</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6562,13 +6567,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6595,7 +6604,7 @@
         <v>130222739</v>
       </c>
       <c r="B55" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6715,7 +6724,7 @@
         <v>130222747</v>
       </c>
       <c r="B56" t="n">
-        <v>91745</v>
+        <v>91771</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6822,10 +6831,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130222723</v>
+        <v>130222754</v>
       </c>
       <c r="B57" t="n">
-        <v>57826</v>
+        <v>79209</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6833,31 +6842,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6865,10 +6869,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504117</v>
+        <v>504081</v>
       </c>
       <c r="R57" t="n">
-        <v>7021735</v>
+        <v>7021796</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6903,17 +6907,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6940,7 +6940,7 @@
         <v>130222741</v>
       </c>
       <c r="B58" t="n">
-        <v>91727</v>
+        <v>91753</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130222751</v>
+        <v>130222748</v>
       </c>
       <c r="B59" t="n">
-        <v>91751</v>
+        <v>91771</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7073,19 +7073,23 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
@@ -7100,10 +7104,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504218</v>
+        <v>504123</v>
       </c>
       <c r="R59" t="n">
-        <v>7022019</v>
+        <v>7021748</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7151,21 +7155,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7183,10 +7172,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130222721</v>
+        <v>130222751</v>
       </c>
       <c r="B60" t="n">
-        <v>57826</v>
+        <v>91777</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7194,29 +7183,24 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7226,10 +7210,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503954</v>
+        <v>504218</v>
       </c>
       <c r="R60" t="n">
-        <v>7021984</v>
+        <v>7022019</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7264,23 +7248,34 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7298,10 +7293,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130222748</v>
+        <v>130222721</v>
       </c>
       <c r="B61" t="n">
-        <v>91745</v>
+        <v>57852</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7309,28 +7304,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7340,10 +7336,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504123</v>
+        <v>503954</v>
       </c>
       <c r="R61" t="n">
-        <v>7021748</v>
+        <v>7021984</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7378,13 +7374,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7411,7 +7411,7 @@
         <v>130222740</v>
       </c>
       <c r="B62" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8200,10 +8200,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130619764</v>
+        <v>130619769</v>
       </c>
       <c r="B69" t="n">
-        <v>57033</v>
+        <v>91753</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8211,42 +8211,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504059</v>
+        <v>504228</v>
       </c>
       <c r="R69" t="n">
-        <v>7022053</v>
+        <v>7021996</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8278,7 +8270,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8288,12 +8280,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
+          <t>På grov torraka av gran, bhd 45 cm</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8320,10 +8312,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130619769</v>
+        <v>130619764</v>
       </c>
       <c r="B70" t="n">
-        <v>91753</v>
+        <v>57033</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8331,34 +8323,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504228</v>
+        <v>504059</v>
       </c>
       <c r="R70" t="n">
-        <v>7021996</v>
+        <v>7022053</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På grov torraka av gran, bhd 45 cm</t>
+          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -1795,37 +1795,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130222701</v>
+        <v>130222705</v>
       </c>
       <c r="B12" t="n">
-        <v>83187</v>
+        <v>91721</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1833,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504090</v>
+        <v>504210</v>
       </c>
       <c r="R12" t="n">
-        <v>7021787</v>
+        <v>7022007</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,41 +1905,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130222705</v>
+        <v>130222701</v>
       </c>
       <c r="B13" t="n">
-        <v>91721</v>
+        <v>83187</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504210</v>
+        <v>504090</v>
       </c>
       <c r="R13" t="n">
-        <v>7022007</v>
+        <v>7021787</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130222725</v>
+        <v>130222753</v>
       </c>
       <c r="B22" t="n">
-        <v>58011</v>
+        <v>79209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,50 +2910,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>504058</v>
+        <v>504059</v>
       </c>
       <c r="R22" t="n">
-        <v>7021715</v>
+        <v>7021781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2994,6 +2981,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3017,7 +3005,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130222753</v>
+        <v>130222757</v>
       </c>
       <c r="B23" t="n">
         <v>79209</v>
@@ -3055,10 +3043,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504059</v>
+        <v>504170</v>
       </c>
       <c r="R23" t="n">
-        <v>7021781</v>
+        <v>7021800</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3123,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130222757</v>
+        <v>130222720</v>
       </c>
       <c r="B24" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3134,26 +3122,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3161,10 +3154,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504170</v>
+        <v>503952</v>
       </c>
       <c r="R24" t="n">
-        <v>7021800</v>
+        <v>7022000</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3199,13 +3192,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3229,10 +3226,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130222720</v>
+        <v>130222725</v>
       </c>
       <c r="B25" t="n">
-        <v>57852</v>
+        <v>58011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,42 +3237,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503952</v>
+        <v>504058</v>
       </c>
       <c r="R25" t="n">
-        <v>7022000</v>
+        <v>7021715</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3308,11 +3313,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3787,10 +3787,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130222756</v>
+        <v>130222742</v>
       </c>
       <c r="B30" t="n">
-        <v>79209</v>
+        <v>91753</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3798,26 +3798,30 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3825,10 +3829,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504101</v>
+        <v>504227</v>
       </c>
       <c r="R30" t="n">
-        <v>7021774</v>
+        <v>7022001</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3893,32 +3897,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130222704</v>
+        <v>130222746</v>
       </c>
       <c r="B31" t="n">
-        <v>91721</v>
+        <v>91753</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3935,10 +3939,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504208</v>
+        <v>503973</v>
       </c>
       <c r="R31" t="n">
-        <v>7022015</v>
+        <v>7021998</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3986,6 +3990,21 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4003,32 +4022,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130222719</v>
+        <v>130222734</v>
       </c>
       <c r="B32" t="n">
-        <v>92475</v>
+        <v>92055</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4045,10 +4064,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504219</v>
+        <v>504221</v>
       </c>
       <c r="R32" t="n">
-        <v>7022014</v>
+        <v>7022011</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4096,6 +4115,21 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4113,10 +4147,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130222742</v>
+        <v>130222715</v>
       </c>
       <c r="B33" t="n">
-        <v>91753</v>
+        <v>91757</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,21 +4158,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4155,10 +4189,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504227</v>
+        <v>504083</v>
       </c>
       <c r="R33" t="n">
-        <v>7022001</v>
+        <v>7021787</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4223,10 +4257,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130222746</v>
+        <v>130222756</v>
       </c>
       <c r="B34" t="n">
-        <v>91753</v>
+        <v>79209</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4234,30 +4268,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4265,10 +4295,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503973</v>
+        <v>504101</v>
       </c>
       <c r="R34" t="n">
-        <v>7021998</v>
+        <v>7021774</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4316,21 +4346,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4348,32 +4363,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130222734</v>
+        <v>130222704</v>
       </c>
       <c r="B35" t="n">
-        <v>92055</v>
+        <v>91721</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4390,10 +4405,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504221</v>
+        <v>504208</v>
       </c>
       <c r="R35" t="n">
-        <v>7022011</v>
+        <v>7022015</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4441,21 +4456,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4473,32 +4473,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130222715</v>
+        <v>130222719</v>
       </c>
       <c r="B36" t="n">
-        <v>91757</v>
+        <v>92475</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4515,10 +4515,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504083</v>
+        <v>504219</v>
       </c>
       <c r="R36" t="n">
-        <v>7021787</v>
+        <v>7022014</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4914,41 +4914,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130222709</v>
+        <v>130222729</v>
       </c>
       <c r="B40" t="n">
-        <v>91757</v>
+        <v>80218</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4956,10 +4952,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504104</v>
+        <v>504173</v>
       </c>
       <c r="R40" t="n">
-        <v>7021877</v>
+        <v>7021803</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5024,37 +5020,41 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130222729</v>
+        <v>130222709</v>
       </c>
       <c r="B41" t="n">
-        <v>80218</v>
+        <v>91757</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504173</v>
+        <v>504104</v>
       </c>
       <c r="R41" t="n">
-        <v>7021803</v>
+        <v>7021877</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>130222731</v>
       </c>
       <c r="B4" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130222710</v>
+        <v>130222714</v>
       </c>
       <c r="B5" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504160</v>
+        <v>504091</v>
       </c>
       <c r="R5" t="n">
-        <v>7021867</v>
+        <v>7021759</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130222714</v>
+        <v>130222710</v>
       </c>
       <c r="B6" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504091</v>
+        <v>504160</v>
       </c>
       <c r="R6" t="n">
-        <v>7021759</v>
+        <v>7021867</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
         <v>130222749</v>
       </c>
       <c r="B7" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130222712</v>
+        <v>130222716</v>
       </c>
       <c r="B8" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504057</v>
+        <v>504095</v>
       </c>
       <c r="R8" t="n">
-        <v>7021765</v>
+        <v>7021805</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130222716</v>
+        <v>130222712</v>
       </c>
       <c r="B9" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504095</v>
+        <v>504057</v>
       </c>
       <c r="R9" t="n">
-        <v>7021805</v>
+        <v>7021765</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
         <v>130222732</v>
       </c>
       <c r="B10" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130222736</v>
+        <v>130222701</v>
       </c>
       <c r="B11" t="n">
-        <v>92055</v>
+        <v>83188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,30 +1696,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1727,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504081</v>
+        <v>504090</v>
       </c>
       <c r="R11" t="n">
-        <v>7021794</v>
+        <v>7021787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1798,7 +1794,7 @@
         <v>130222705</v>
       </c>
       <c r="B12" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,10 +1901,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130222701</v>
+        <v>130222736</v>
       </c>
       <c r="B13" t="n">
-        <v>83187</v>
+        <v>92056</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,26 +1912,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504090</v>
+        <v>504081</v>
       </c>
       <c r="R13" t="n">
-        <v>7021787</v>
+        <v>7021794</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,41 +2011,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130222713</v>
+        <v>130222730</v>
       </c>
       <c r="B14" t="n">
-        <v>91757</v>
+        <v>80218</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2053,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504135</v>
+        <v>504166</v>
       </c>
       <c r="R14" t="n">
-        <v>7021768</v>
+        <v>7021800</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,10 +2117,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222711</v>
+        <v>130222702</v>
       </c>
       <c r="B15" t="n">
-        <v>91757</v>
+        <v>83188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,30 +2128,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2163,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504154</v>
+        <v>504100</v>
       </c>
       <c r="R15" t="n">
-        <v>7021848</v>
+        <v>7021801</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2231,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130222702</v>
+        <v>130222711</v>
       </c>
       <c r="B16" t="n">
-        <v>83187</v>
+        <v>91758</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2242,26 +2234,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2269,10 +2265,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504100</v>
+        <v>504154</v>
       </c>
       <c r="R16" t="n">
-        <v>7021801</v>
+        <v>7021848</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2337,37 +2333,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130222730</v>
+        <v>130222713</v>
       </c>
       <c r="B17" t="n">
-        <v>80218</v>
+        <v>91758</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>504166</v>
+        <v>504135</v>
       </c>
       <c r="R17" t="n">
-        <v>7021800</v>
+        <v>7021768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2558,41 +2558,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130222706</v>
+        <v>130222700</v>
       </c>
       <c r="B19" t="n">
-        <v>91721</v>
+        <v>83188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2600,10 +2596,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504083</v>
+        <v>504099</v>
       </c>
       <c r="R19" t="n">
-        <v>7021773</v>
+        <v>7021769</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2671,7 +2667,7 @@
         <v>130222727</v>
       </c>
       <c r="B20" t="n">
-        <v>92480</v>
+        <v>92481</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2793,37 +2789,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130222700</v>
+        <v>130222706</v>
       </c>
       <c r="B21" t="n">
-        <v>83187</v>
+        <v>91722</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>504099</v>
+        <v>504083</v>
       </c>
       <c r="R21" t="n">
-        <v>7021769</v>
+        <v>7021773</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130222753</v>
+        <v>130222725</v>
       </c>
       <c r="B22" t="n">
-        <v>79209</v>
+        <v>58011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,37 +2910,50 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>504059</v>
+        <v>504058</v>
       </c>
       <c r="R22" t="n">
-        <v>7021781</v>
+        <v>7021715</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2981,7 +2994,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3005,7 +3017,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130222757</v>
+        <v>130222753</v>
       </c>
       <c r="B23" t="n">
         <v>79209</v>
@@ -3043,10 +3055,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504170</v>
+        <v>504059</v>
       </c>
       <c r="R23" t="n">
-        <v>7021800</v>
+        <v>7021781</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3111,10 +3123,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130222720</v>
+        <v>130222757</v>
       </c>
       <c r="B24" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,31 +3134,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3154,10 +3161,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503952</v>
+        <v>504170</v>
       </c>
       <c r="R24" t="n">
-        <v>7022000</v>
+        <v>7021800</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3192,17 +3199,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3226,10 +3229,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130222725</v>
+        <v>130222720</v>
       </c>
       <c r="B25" t="n">
-        <v>58011</v>
+        <v>57852</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,50 +3240,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>504058</v>
+        <v>503952</v>
       </c>
       <c r="R25" t="n">
-        <v>7021715</v>
+        <v>7022000</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3313,6 +3308,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,7 +3347,7 @@
         <v>130222743</v>
       </c>
       <c r="B26" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>130222750</v>
       </c>
       <c r="B29" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>130222742</v>
       </c>
       <c r="B30" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130222746</v>
+        <v>130222704</v>
       </c>
       <c r="B31" t="n">
-        <v>91753</v>
+        <v>91722</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503973</v>
+        <v>504208</v>
       </c>
       <c r="R31" t="n">
-        <v>7021998</v>
+        <v>7022015</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3990,21 +3990,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4022,10 +4007,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130222734</v>
+        <v>130222715</v>
       </c>
       <c r="B32" t="n">
-        <v>92055</v>
+        <v>91758</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4033,21 +4018,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4064,10 +4049,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504221</v>
+        <v>504083</v>
       </c>
       <c r="R32" t="n">
-        <v>7022011</v>
+        <v>7021787</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4115,21 +4100,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4147,10 +4117,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130222715</v>
+        <v>130222746</v>
       </c>
       <c r="B33" t="n">
-        <v>91757</v>
+        <v>91754</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4158,21 +4128,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4189,10 +4159,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504083</v>
+        <v>503973</v>
       </c>
       <c r="R33" t="n">
-        <v>7021787</v>
+        <v>7021998</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4240,6 +4210,21 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4257,37 +4242,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130222756</v>
+        <v>130222719</v>
       </c>
       <c r="B34" t="n">
-        <v>79209</v>
+        <v>92476</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4295,10 +4284,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504101</v>
+        <v>504219</v>
       </c>
       <c r="R34" t="n">
-        <v>7021774</v>
+        <v>7022014</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4363,41 +4352,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130222704</v>
+        <v>130222756</v>
       </c>
       <c r="B35" t="n">
-        <v>91721</v>
+        <v>79209</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4405,10 +4390,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504208</v>
+        <v>504101</v>
       </c>
       <c r="R35" t="n">
-        <v>7022015</v>
+        <v>7021774</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4473,39 +4458,40 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130222719</v>
+        <v>130222722</v>
       </c>
       <c r="B36" t="n">
-        <v>92475</v>
+        <v>57852</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4515,10 +4501,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504219</v>
+        <v>503979</v>
       </c>
       <c r="R36" t="n">
-        <v>7022014</v>
+        <v>7022007</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4553,13 +4539,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4583,10 +4573,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130222722</v>
+        <v>130222734</v>
       </c>
       <c r="B37" t="n">
-        <v>57852</v>
+        <v>92056</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4594,29 +4584,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4626,10 +4615,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503979</v>
+        <v>504221</v>
       </c>
       <c r="R37" t="n">
-        <v>7022007</v>
+        <v>7022011</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4664,23 +4653,34 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130222728</v>
+        <v>130222718</v>
       </c>
       <c r="B38" t="n">
-        <v>80218</v>
+        <v>92476</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4709,26 +4709,30 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>3298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4736,10 +4740,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504090</v>
+        <v>504098</v>
       </c>
       <c r="R38" t="n">
-        <v>7021781</v>
+        <v>7022064</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4804,10 +4808,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130222718</v>
+        <v>130222728</v>
       </c>
       <c r="B39" t="n">
-        <v>92475</v>
+        <v>80218</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4815,30 +4819,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3298</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504098</v>
+        <v>504090</v>
       </c>
       <c r="R39" t="n">
-        <v>7022064</v>
+        <v>7021781</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5023,7 +5023,7 @@
         <v>130222709</v>
       </c>
       <c r="B41" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>130222735</v>
       </c>
       <c r="B42" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>130222708</v>
       </c>
       <c r="B43" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>130222733</v>
       </c>
       <c r="B44" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5490,32 +5490,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130222726</v>
+        <v>130222699</v>
       </c>
       <c r="B45" t="n">
-        <v>80343</v>
+        <v>83188</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504106</v>
+        <v>504118</v>
       </c>
       <c r="R45" t="n">
-        <v>7021741</v>
+        <v>7021776</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5596,32 +5596,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130222699</v>
+        <v>130222726</v>
       </c>
       <c r="B46" t="n">
-        <v>83187</v>
+        <v>80343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5634,10 +5634,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504118</v>
+        <v>504106</v>
       </c>
       <c r="R46" t="n">
-        <v>7021776</v>
+        <v>7021741</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5702,10 +5702,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130222744</v>
+        <v>130222745</v>
       </c>
       <c r="B47" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504178</v>
+        <v>504130</v>
       </c>
       <c r="R47" t="n">
-        <v>7021976</v>
+        <v>7021754</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5827,10 +5827,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130222745</v>
+        <v>130222744</v>
       </c>
       <c r="B48" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504130</v>
+        <v>504178</v>
       </c>
       <c r="R48" t="n">
-        <v>7021754</v>
+        <v>7021976</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6061,7 +6061,7 @@
         <v>130222707</v>
       </c>
       <c r="B50" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6168,10 +6168,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130222703</v>
+        <v>130222738</v>
       </c>
       <c r="B51" t="n">
-        <v>83187</v>
+        <v>78221</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6179,21 +6179,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6206,10 +6206,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504170</v>
+        <v>504087</v>
       </c>
       <c r="R51" t="n">
-        <v>7021803</v>
+        <v>7021791</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6274,10 +6274,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130222738</v>
+        <v>130222703</v>
       </c>
       <c r="B52" t="n">
-        <v>78221</v>
+        <v>83188</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504087</v>
+        <v>504170</v>
       </c>
       <c r="R52" t="n">
-        <v>7021791</v>
+        <v>7021803</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6486,10 +6486,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130222723</v>
+        <v>130222747</v>
       </c>
       <c r="B54" t="n">
-        <v>57852</v>
+        <v>91772</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6497,29 +6497,28 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6529,10 +6528,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504117</v>
+        <v>504210</v>
       </c>
       <c r="R54" t="n">
-        <v>7021735</v>
+        <v>7022007</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6567,17 +6566,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6601,46 +6596,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130222739</v>
+        <v>130222754</v>
       </c>
       <c r="B55" t="n">
-        <v>98949</v>
+        <v>79209</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6648,10 +6634,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504054</v>
+        <v>504081</v>
       </c>
       <c r="R55" t="n">
-        <v>7021735</v>
+        <v>7021796</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6684,11 +6670,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Minst 3 plantor finns på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6721,10 +6702,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130222747</v>
+        <v>130222723</v>
       </c>
       <c r="B56" t="n">
-        <v>91771</v>
+        <v>57852</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6732,28 +6713,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6763,10 +6745,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504210</v>
+        <v>504117</v>
       </c>
       <c r="R56" t="n">
-        <v>7022007</v>
+        <v>7021735</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6801,13 +6783,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6831,37 +6817,46 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130222754</v>
+        <v>130222739</v>
       </c>
       <c r="B57" t="n">
-        <v>79209</v>
+        <v>98950</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6869,10 +6864,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504081</v>
+        <v>504054</v>
       </c>
       <c r="R57" t="n">
-        <v>7021796</v>
+        <v>7021735</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6905,6 +6900,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor finns på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6940,7 +6940,7 @@
         <v>130222741</v>
       </c>
       <c r="B58" t="n">
-        <v>91753</v>
+        <v>91754</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>130222748</v>
       </c>
       <c r="B59" t="n">
-        <v>91771</v>
+        <v>91772</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>130222751</v>
       </c>
       <c r="B60" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>130222740</v>
       </c>
       <c r="B62" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8200,10 +8200,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130619769</v>
+        <v>130619764</v>
       </c>
       <c r="B69" t="n">
-        <v>91753</v>
+        <v>57033</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8211,34 +8211,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504228</v>
+        <v>504059</v>
       </c>
       <c r="R69" t="n">
-        <v>7021996</v>
+        <v>7022053</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8270,7 +8278,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8280,12 +8288,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På grov torraka av gran, bhd 45 cm</t>
+          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8312,10 +8320,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130619764</v>
+        <v>130619769</v>
       </c>
       <c r="B70" t="n">
-        <v>57033</v>
+        <v>91754</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8323,42 +8331,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504059</v>
+        <v>504228</v>
       </c>
       <c r="R70" t="n">
-        <v>7022053</v>
+        <v>7021996</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
+          <t>På grov torraka av gran, bhd 45 cm</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8435,7 +8435,7 @@
         <v>130619761</v>
       </c>
       <c r="B71" t="n">
-        <v>92475</v>
+        <v>92476</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>130222731</v>
       </c>
       <c r="B4" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>130222714</v>
       </c>
       <c r="B5" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>130222710</v>
       </c>
       <c r="B6" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>130222749</v>
       </c>
       <c r="B7" t="n">
-        <v>91772</v>
+        <v>91773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,32 +1340,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130222716</v>
+        <v>130222732</v>
       </c>
       <c r="B8" t="n">
-        <v>91758</v>
+        <v>92212</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504095</v>
+        <v>504202</v>
       </c>
       <c r="R8" t="n">
-        <v>7021805</v>
+        <v>7022015</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,6 +1433,21 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1450,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130222712</v>
+        <v>130222716</v>
       </c>
       <c r="B9" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504057</v>
+        <v>504095</v>
       </c>
       <c r="R9" t="n">
-        <v>7021765</v>
+        <v>7021805</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,32 +1575,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130222732</v>
+        <v>130222712</v>
       </c>
       <c r="B10" t="n">
-        <v>92211</v>
+        <v>91759</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504202</v>
+        <v>504057</v>
       </c>
       <c r="R10" t="n">
-        <v>7022015</v>
+        <v>7021765</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,21 +1668,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130222701</v>
+        <v>130222736</v>
       </c>
       <c r="B11" t="n">
-        <v>83188</v>
+        <v>92057</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,26 +1696,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1723,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504090</v>
+        <v>504081</v>
       </c>
       <c r="R11" t="n">
-        <v>7021787</v>
+        <v>7021794</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,7 +1798,7 @@
         <v>130222705</v>
       </c>
       <c r="B12" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1901,10 +1905,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130222736</v>
+        <v>130222701</v>
       </c>
       <c r="B13" t="n">
-        <v>92056</v>
+        <v>83189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1912,30 +1916,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504081</v>
+        <v>504090</v>
       </c>
       <c r="R13" t="n">
-        <v>7021794</v>
+        <v>7021787</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,37 +2011,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130222730</v>
+        <v>130222711</v>
       </c>
       <c r="B14" t="n">
-        <v>80218</v>
+        <v>91759</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2049,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504166</v>
+        <v>504154</v>
       </c>
       <c r="R14" t="n">
-        <v>7021800</v>
+        <v>7021848</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222702</v>
+        <v>130222713</v>
       </c>
       <c r="B15" t="n">
-        <v>83188</v>
+        <v>91759</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2128,26 +2132,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2155,10 +2163,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504100</v>
+        <v>504135</v>
       </c>
       <c r="R15" t="n">
-        <v>7021801</v>
+        <v>7021768</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,10 +2231,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130222711</v>
+        <v>130222724</v>
       </c>
       <c r="B16" t="n">
-        <v>91758</v>
+        <v>57852</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,28 +2242,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2265,10 +2274,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504154</v>
+        <v>504139</v>
       </c>
       <c r="R16" t="n">
-        <v>7021848</v>
+        <v>7021798</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,13 +2312,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2333,10 +2346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130222713</v>
+        <v>130222702</v>
       </c>
       <c r="B17" t="n">
-        <v>91758</v>
+        <v>83189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2344,30 +2357,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2375,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>504135</v>
+        <v>504100</v>
       </c>
       <c r="R17" t="n">
-        <v>7021768</v>
+        <v>7021801</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2443,42 +2452,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130222724</v>
+        <v>130222730</v>
       </c>
       <c r="B18" t="n">
-        <v>57852</v>
+        <v>80218</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2486,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504139</v>
+        <v>504166</v>
       </c>
       <c r="R18" t="n">
-        <v>7021798</v>
+        <v>7021800</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2524,17 +2528,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2558,37 +2558,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130222700</v>
+        <v>130222727</v>
       </c>
       <c r="B19" t="n">
-        <v>83188</v>
+        <v>92482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>67</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2596,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504099</v>
+        <v>504089</v>
       </c>
       <c r="R19" t="n">
-        <v>7021769</v>
+        <v>7021772</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2647,6 +2651,21 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2664,32 +2683,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130222727</v>
+        <v>130222706</v>
       </c>
       <c r="B20" t="n">
-        <v>92481</v>
+        <v>91723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>67</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2706,10 +2725,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504089</v>
+        <v>504083</v>
       </c>
       <c r="R20" t="n">
-        <v>7021772</v>
+        <v>7021773</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2757,21 +2776,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2789,41 +2793,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130222706</v>
+        <v>130222700</v>
       </c>
       <c r="B21" t="n">
-        <v>91722</v>
+        <v>83189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>504083</v>
+        <v>504099</v>
       </c>
       <c r="R21" t="n">
-        <v>7021773</v>
+        <v>7021769</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130222725</v>
+        <v>130222720</v>
       </c>
       <c r="B22" t="n">
-        <v>58011</v>
+        <v>57852</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,50 +2910,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>504058</v>
+        <v>503952</v>
       </c>
       <c r="R22" t="n">
-        <v>7021715</v>
+        <v>7022000</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2986,6 +2978,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3017,10 +3014,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130222753</v>
+        <v>130222725</v>
       </c>
       <c r="B23" t="n">
-        <v>79209</v>
+        <v>58011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3028,37 +3025,50 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504059</v>
+        <v>504058</v>
       </c>
       <c r="R23" t="n">
-        <v>7021781</v>
+        <v>7021715</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3099,7 +3109,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3123,7 +3132,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130222757</v>
+        <v>130222753</v>
       </c>
       <c r="B24" t="n">
         <v>79209</v>
@@ -3161,10 +3170,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504170</v>
+        <v>504059</v>
       </c>
       <c r="R24" t="n">
-        <v>7021800</v>
+        <v>7021781</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3229,10 +3238,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130222720</v>
+        <v>130222757</v>
       </c>
       <c r="B25" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,31 +3249,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3272,10 +3276,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503952</v>
+        <v>504170</v>
       </c>
       <c r="R25" t="n">
-        <v>7022000</v>
+        <v>7021800</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,17 +3314,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>130222743</v>
       </c>
       <c r="B26" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3575,10 +3575,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130222752</v>
+        <v>130222750</v>
       </c>
       <c r="B28" t="n">
-        <v>79209</v>
+        <v>91779</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3586,26 +3586,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504097</v>
+        <v>504216</v>
       </c>
       <c r="R28" t="n">
-        <v>7021762</v>
+        <v>7022005</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3681,10 +3681,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130222750</v>
+        <v>130222752</v>
       </c>
       <c r="B29" t="n">
-        <v>91778</v>
+        <v>79209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3692,26 +3692,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504216</v>
+        <v>504097</v>
       </c>
       <c r="R29" t="n">
-        <v>7022005</v>
+        <v>7021762</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3787,10 +3787,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130222742</v>
+        <v>130222756</v>
       </c>
       <c r="B30" t="n">
-        <v>91754</v>
+        <v>79209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3798,30 +3798,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3829,10 +3825,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504227</v>
+        <v>504101</v>
       </c>
       <c r="R30" t="n">
-        <v>7022001</v>
+        <v>7021774</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3897,10 +3893,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130222704</v>
+        <v>130222719</v>
       </c>
       <c r="B31" t="n">
-        <v>91722</v>
+        <v>92477</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3908,21 +3904,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3939,10 +3935,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504208</v>
+        <v>504219</v>
       </c>
       <c r="R31" t="n">
-        <v>7022015</v>
+        <v>7022014</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4007,32 +4003,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130222715</v>
+        <v>130222704</v>
       </c>
       <c r="B32" t="n">
-        <v>91758</v>
+        <v>91723</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4049,10 +4045,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504083</v>
+        <v>504208</v>
       </c>
       <c r="R32" t="n">
-        <v>7021787</v>
+        <v>7022015</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4117,10 +4113,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130222746</v>
+        <v>130222722</v>
       </c>
       <c r="B33" t="n">
-        <v>91754</v>
+        <v>57852</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4128,28 +4124,29 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4159,10 +4156,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503973</v>
+        <v>503979</v>
       </c>
       <c r="R33" t="n">
-        <v>7021998</v>
+        <v>7022007</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4197,34 +4194,23 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4242,32 +4228,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130222719</v>
+        <v>130222734</v>
       </c>
       <c r="B34" t="n">
-        <v>92476</v>
+        <v>92057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4284,10 +4270,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504219</v>
+        <v>504221</v>
       </c>
       <c r="R34" t="n">
-        <v>7022014</v>
+        <v>7022011</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4335,6 +4321,21 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4352,10 +4353,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130222756</v>
+        <v>130222715</v>
       </c>
       <c r="B35" t="n">
-        <v>79209</v>
+        <v>91759</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,26 +4364,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4390,10 +4395,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504101</v>
+        <v>504083</v>
       </c>
       <c r="R35" t="n">
-        <v>7021774</v>
+        <v>7021787</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4458,10 +4463,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130222722</v>
+        <v>130222746</v>
       </c>
       <c r="B36" t="n">
-        <v>57852</v>
+        <v>91755</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4469,29 +4474,28 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4501,10 +4505,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503979</v>
+        <v>503973</v>
       </c>
       <c r="R36" t="n">
-        <v>7022007</v>
+        <v>7021998</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4539,23 +4543,34 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4573,10 +4588,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130222734</v>
+        <v>130222742</v>
       </c>
       <c r="B37" t="n">
-        <v>92056</v>
+        <v>91755</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4584,21 +4599,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4615,10 +4630,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504221</v>
+        <v>504227</v>
       </c>
       <c r="R37" t="n">
-        <v>7022011</v>
+        <v>7022001</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4666,21 +4681,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
         <v>130222718</v>
       </c>
       <c r="B38" t="n">
-        <v>92476</v>
+        <v>92477</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4914,37 +4914,41 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130222729</v>
+        <v>130222709</v>
       </c>
       <c r="B40" t="n">
-        <v>80218</v>
+        <v>91759</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4952,10 +4956,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504173</v>
+        <v>504104</v>
       </c>
       <c r="R40" t="n">
-        <v>7021803</v>
+        <v>7021877</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5020,41 +5024,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130222709</v>
+        <v>130222729</v>
       </c>
       <c r="B41" t="n">
-        <v>91758</v>
+        <v>80218</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504104</v>
+        <v>504173</v>
       </c>
       <c r="R41" t="n">
-        <v>7021877</v>
+        <v>7021803</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5133,7 +5133,7 @@
         <v>130222735</v>
       </c>
       <c r="B42" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>130222708</v>
       </c>
       <c r="B43" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5365,32 +5365,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130222733</v>
+        <v>130222745</v>
       </c>
       <c r="B44" t="n">
-        <v>92211</v>
+        <v>91755</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504161</v>
+        <v>504130</v>
       </c>
       <c r="R44" t="n">
-        <v>7021869</v>
+        <v>7021754</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5490,10 +5490,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130222699</v>
+        <v>130222744</v>
       </c>
       <c r="B45" t="n">
-        <v>83188</v>
+        <v>91755</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5501,26 +5501,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5528,10 +5532,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504118</v>
+        <v>504178</v>
       </c>
       <c r="R45" t="n">
-        <v>7021776</v>
+        <v>7021976</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5579,6 +5583,21 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5702,10 +5721,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130222745</v>
+        <v>130222699</v>
       </c>
       <c r="B47" t="n">
-        <v>91754</v>
+        <v>83189</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5713,30 +5732,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5744,10 +5759,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504130</v>
+        <v>504118</v>
       </c>
       <c r="R47" t="n">
-        <v>7021754</v>
+        <v>7021776</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5795,21 +5810,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5827,32 +5827,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130222744</v>
+        <v>130222733</v>
       </c>
       <c r="B48" t="n">
-        <v>91754</v>
+        <v>92212</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504178</v>
+        <v>504161</v>
       </c>
       <c r="R48" t="n">
-        <v>7021976</v>
+        <v>7021869</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6061,7 +6061,7 @@
         <v>130222707</v>
       </c>
       <c r="B50" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6168,10 +6168,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130222738</v>
+        <v>130222703</v>
       </c>
       <c r="B51" t="n">
-        <v>78221</v>
+        <v>83189</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6179,21 +6179,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6206,10 +6206,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>504087</v>
+        <v>504170</v>
       </c>
       <c r="R51" t="n">
-        <v>7021791</v>
+        <v>7021803</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6274,10 +6274,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130222703</v>
+        <v>130222738</v>
       </c>
       <c r="B52" t="n">
-        <v>83188</v>
+        <v>78221</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504170</v>
+        <v>504087</v>
       </c>
       <c r="R52" t="n">
-        <v>7021803</v>
+        <v>7021791</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6489,7 +6489,7 @@
         <v>130222747</v>
       </c>
       <c r="B54" t="n">
-        <v>91772</v>
+        <v>91773</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130222754</v>
+        <v>130222723</v>
       </c>
       <c r="B55" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6607,26 +6607,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6634,10 +6639,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504081</v>
+        <v>504117</v>
       </c>
       <c r="R55" t="n">
-        <v>7021796</v>
+        <v>7021735</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6672,13 +6677,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6702,10 +6711,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130222723</v>
+        <v>130222754</v>
       </c>
       <c r="B56" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6713,31 +6722,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6745,10 +6749,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504117</v>
+        <v>504081</v>
       </c>
       <c r="R56" t="n">
-        <v>7021735</v>
+        <v>7021796</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6783,17 +6787,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6820,7 +6820,7 @@
         <v>130222739</v>
       </c>
       <c r="B57" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>130222741</v>
       </c>
       <c r="B58" t="n">
-        <v>91754</v>
+        <v>91755</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>130222748</v>
       </c>
       <c r="B59" t="n">
-        <v>91772</v>
+        <v>91773</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>130222751</v>
       </c>
       <c r="B60" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>130222740</v>
       </c>
       <c r="B62" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8200,10 +8200,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130619764</v>
+        <v>130619769</v>
       </c>
       <c r="B69" t="n">
-        <v>57033</v>
+        <v>91755</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8211,42 +8211,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504059</v>
+        <v>504228</v>
       </c>
       <c r="R69" t="n">
-        <v>7022053</v>
+        <v>7021996</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8278,7 +8270,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8288,12 +8280,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
+          <t>På grov torraka av gran, bhd 45 cm</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8320,32 +8312,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130619769</v>
+        <v>130619761</v>
       </c>
       <c r="B70" t="n">
-        <v>91754</v>
+        <v>92477</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8355,10 +8347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504228</v>
+        <v>504231</v>
       </c>
       <c r="R70" t="n">
-        <v>7021996</v>
+        <v>7021975</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8390,7 +8382,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8400,12 +8392,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På grov torraka av gran, bhd 45 cm</t>
+          <t>På död gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8432,45 +8424,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130619761</v>
+        <v>130619764</v>
       </c>
       <c r="B71" t="n">
-        <v>92476</v>
+        <v>57033</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3298</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504231</v>
+        <v>504059</v>
       </c>
       <c r="R71" t="n">
-        <v>7021975</v>
+        <v>7022053</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På död gran</t>
+          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>130222731</v>
       </c>
       <c r="B4" t="n">
-        <v>92212</v>
+        <v>92214</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130222714</v>
+        <v>130222710</v>
       </c>
       <c r="B5" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504091</v>
+        <v>504160</v>
       </c>
       <c r="R5" t="n">
-        <v>7021759</v>
+        <v>7021867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130222710</v>
+        <v>130222749</v>
       </c>
       <c r="B6" t="n">
-        <v>91759</v>
+        <v>91775</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504160</v>
+        <v>504067</v>
       </c>
       <c r="R6" t="n">
-        <v>7021867</v>
+        <v>7021774</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130222749</v>
+        <v>130222714</v>
       </c>
       <c r="B7" t="n">
-        <v>91773</v>
+        <v>91761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504067</v>
+        <v>504091</v>
       </c>
       <c r="R7" t="n">
-        <v>7021774</v>
+        <v>7021759</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1343,7 @@
         <v>130222732</v>
       </c>
       <c r="B8" t="n">
-        <v>92212</v>
+        <v>92214</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130222716</v>
+        <v>130222712</v>
       </c>
       <c r="B9" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504095</v>
+        <v>504057</v>
       </c>
       <c r="R9" t="n">
-        <v>7021805</v>
+        <v>7021765</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130222712</v>
+        <v>130222716</v>
       </c>
       <c r="B10" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504057</v>
+        <v>504095</v>
       </c>
       <c r="R10" t="n">
-        <v>7021765</v>
+        <v>7021805</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,7 +1688,7 @@
         <v>130222736</v>
       </c>
       <c r="B11" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,41 +1795,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130222705</v>
+        <v>130222701</v>
       </c>
       <c r="B12" t="n">
-        <v>91723</v>
+        <v>83191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1837,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504210</v>
+        <v>504090</v>
       </c>
       <c r="R12" t="n">
-        <v>7022007</v>
+        <v>7021787</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,37 +1901,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130222701</v>
+        <v>130222705</v>
       </c>
       <c r="B13" t="n">
-        <v>83189</v>
+        <v>91725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504090</v>
+        <v>504210</v>
       </c>
       <c r="R13" t="n">
-        <v>7021787</v>
+        <v>7022007</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130222711</v>
+        <v>130222724</v>
       </c>
       <c r="B14" t="n">
-        <v>91759</v>
+        <v>57854</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,28 +2022,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2053,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504154</v>
+        <v>504139</v>
       </c>
       <c r="R14" t="n">
-        <v>7021848</v>
+        <v>7021798</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2091,13 +2092,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2121,41 +2126,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222713</v>
+        <v>130222730</v>
       </c>
       <c r="B15" t="n">
-        <v>91759</v>
+        <v>80220</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2163,10 +2164,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504135</v>
+        <v>504166</v>
       </c>
       <c r="R15" t="n">
-        <v>7021768</v>
+        <v>7021800</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2231,10 +2232,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130222724</v>
+        <v>130222713</v>
       </c>
       <c r="B16" t="n">
-        <v>57852</v>
+        <v>91761</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2242,29 +2243,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504139</v>
+        <v>504135</v>
       </c>
       <c r="R16" t="n">
-        <v>7021798</v>
+        <v>7021768</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2312,17 +2312,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2346,10 +2342,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130222702</v>
+        <v>130222711</v>
       </c>
       <c r="B17" t="n">
-        <v>83189</v>
+        <v>91761</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,26 +2353,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>504100</v>
+        <v>504154</v>
       </c>
       <c r="R17" t="n">
-        <v>7021801</v>
+        <v>7021848</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,32 +2452,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130222730</v>
+        <v>130222702</v>
       </c>
       <c r="B18" t="n">
-        <v>80218</v>
+        <v>83191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504166</v>
+        <v>504100</v>
       </c>
       <c r="R18" t="n">
-        <v>7021800</v>
+        <v>7021801</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2561,7 +2561,7 @@
         <v>130222727</v>
       </c>
       <c r="B19" t="n">
-        <v>92482</v>
+        <v>92484</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>130222706</v>
       </c>
       <c r="B20" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>130222700</v>
       </c>
       <c r="B21" t="n">
-        <v>83189</v>
+        <v>83191</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130222720</v>
+        <v>130222753</v>
       </c>
       <c r="B22" t="n">
-        <v>57852</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,31 +2910,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2942,10 +2937,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503952</v>
+        <v>504059</v>
       </c>
       <c r="R22" t="n">
-        <v>7022000</v>
+        <v>7021781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2980,17 +2975,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3014,10 +3005,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130222725</v>
+        <v>130222757</v>
       </c>
       <c r="B23" t="n">
-        <v>58011</v>
+        <v>79211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3025,50 +3016,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504058</v>
+        <v>504170</v>
       </c>
       <c r="R23" t="n">
-        <v>7021715</v>
+        <v>7021800</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3109,6 +3087,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3132,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130222753</v>
+        <v>130222720</v>
       </c>
       <c r="B24" t="n">
-        <v>79209</v>
+        <v>57854</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3143,26 +3122,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3170,10 +3154,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504059</v>
+        <v>503952</v>
       </c>
       <c r="R24" t="n">
-        <v>7021781</v>
+        <v>7022000</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3208,13 +3192,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3238,10 +3226,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130222757</v>
+        <v>130222725</v>
       </c>
       <c r="B25" t="n">
-        <v>79209</v>
+        <v>58013</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3249,37 +3237,50 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>504170</v>
+        <v>504058</v>
       </c>
       <c r="R25" t="n">
-        <v>7021800</v>
+        <v>7021715</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3320,7 +3321,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3344,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130222743</v>
+        <v>130222755</v>
       </c>
       <c r="B26" t="n">
-        <v>91755</v>
+        <v>79211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,30 +3355,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3386,10 +3382,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504223</v>
+        <v>504177</v>
       </c>
       <c r="R26" t="n">
-        <v>7022010</v>
+        <v>7021847</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3437,21 +3433,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3469,10 +3450,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130222755</v>
+        <v>130222743</v>
       </c>
       <c r="B27" t="n">
-        <v>79209</v>
+        <v>91757</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,26 +3461,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3507,10 +3492,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504177</v>
+        <v>504223</v>
       </c>
       <c r="R27" t="n">
-        <v>7021847</v>
+        <v>7022010</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3558,6 +3543,21 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3578,7 +3578,7 @@
         <v>130222750</v>
       </c>
       <c r="B28" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>130222752</v>
       </c>
       <c r="B29" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3787,37 +3787,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130222756</v>
+        <v>130222719</v>
       </c>
       <c r="B30" t="n">
-        <v>79209</v>
+        <v>92479</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3825,10 +3829,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504101</v>
+        <v>504219</v>
       </c>
       <c r="R30" t="n">
-        <v>7021774</v>
+        <v>7022014</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3893,32 +3897,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130222719</v>
+        <v>130222734</v>
       </c>
       <c r="B31" t="n">
-        <v>92477</v>
+        <v>92059</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3935,10 +3939,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504219</v>
+        <v>504221</v>
       </c>
       <c r="R31" t="n">
-        <v>7022014</v>
+        <v>7022011</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3986,6 +3990,21 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4003,32 +4022,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130222704</v>
+        <v>130222742</v>
       </c>
       <c r="B32" t="n">
-        <v>91723</v>
+        <v>91757</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4045,10 +4064,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504208</v>
+        <v>504227</v>
       </c>
       <c r="R32" t="n">
-        <v>7022015</v>
+        <v>7022001</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4113,10 +4132,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130222722</v>
+        <v>130222746</v>
       </c>
       <c r="B33" t="n">
-        <v>57852</v>
+        <v>91757</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4124,29 +4143,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4156,10 +4174,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503979</v>
+        <v>503973</v>
       </c>
       <c r="R33" t="n">
-        <v>7022007</v>
+        <v>7021998</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4194,23 +4212,34 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4228,10 +4257,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130222734</v>
+        <v>130222715</v>
       </c>
       <c r="B34" t="n">
-        <v>92057</v>
+        <v>91761</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4239,21 +4268,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4270,10 +4299,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504221</v>
+        <v>504083</v>
       </c>
       <c r="R34" t="n">
-        <v>7022011</v>
+        <v>7021787</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4321,21 +4350,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4353,10 +4367,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130222715</v>
+        <v>130222756</v>
       </c>
       <c r="B35" t="n">
-        <v>91759</v>
+        <v>79211</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4364,30 +4378,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4395,10 +4405,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504083</v>
+        <v>504101</v>
       </c>
       <c r="R35" t="n">
-        <v>7021787</v>
+        <v>7021774</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4463,32 +4473,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130222746</v>
+        <v>130222704</v>
       </c>
       <c r="B36" t="n">
-        <v>91755</v>
+        <v>91725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4505,10 +4515,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503973</v>
+        <v>504208</v>
       </c>
       <c r="R36" t="n">
-        <v>7021998</v>
+        <v>7022015</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4556,21 +4566,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4588,10 +4583,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130222742</v>
+        <v>130222722</v>
       </c>
       <c r="B37" t="n">
-        <v>91755</v>
+        <v>57854</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4599,28 +4594,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4630,10 +4626,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>504227</v>
+        <v>503979</v>
       </c>
       <c r="R37" t="n">
-        <v>7022001</v>
+        <v>7022007</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4668,13 +4664,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>130222718</v>
       </c>
       <c r="B38" t="n">
-        <v>92477</v>
+        <v>92479</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>130222728</v>
       </c>
       <c r="B39" t="n">
-        <v>80218</v>
+        <v>80220</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>130222709</v>
       </c>
       <c r="B40" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>130222729</v>
       </c>
       <c r="B41" t="n">
-        <v>80218</v>
+        <v>80220</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>130222735</v>
       </c>
       <c r="B42" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>130222708</v>
       </c>
       <c r="B43" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5365,32 +5365,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130222745</v>
+        <v>130222733</v>
       </c>
       <c r="B44" t="n">
-        <v>91755</v>
+        <v>92214</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504130</v>
+        <v>504161</v>
       </c>
       <c r="R44" t="n">
-        <v>7021754</v>
+        <v>7021869</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5493,7 +5493,7 @@
         <v>130222744</v>
       </c>
       <c r="B45" t="n">
-        <v>91755</v>
+        <v>91757</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5615,37 +5615,41 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130222726</v>
+        <v>130222745</v>
       </c>
       <c r="B46" t="n">
-        <v>80343</v>
+        <v>91757</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5653,10 +5657,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504106</v>
+        <v>504130</v>
       </c>
       <c r="R46" t="n">
-        <v>7021741</v>
+        <v>7021754</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5704,6 +5708,21 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5724,7 +5743,7 @@
         <v>130222699</v>
       </c>
       <c r="B47" t="n">
-        <v>83189</v>
+        <v>83191</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5827,41 +5846,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130222733</v>
+        <v>130222726</v>
       </c>
       <c r="B48" t="n">
-        <v>92212</v>
+        <v>80345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5869,10 +5884,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504161</v>
+        <v>504106</v>
       </c>
       <c r="R48" t="n">
-        <v>7021869</v>
+        <v>7021741</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5920,21 +5935,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5952,37 +5952,41 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130222758</v>
+        <v>130222707</v>
       </c>
       <c r="B49" t="n">
-        <v>79209</v>
+        <v>91725</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5990,10 +5994,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504172</v>
+        <v>504161</v>
       </c>
       <c r="R49" t="n">
-        <v>7021818</v>
+        <v>7021806</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6058,41 +6062,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130222707</v>
+        <v>130222758</v>
       </c>
       <c r="B50" t="n">
-        <v>91723</v>
+        <v>79211</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504161</v>
+        <v>504172</v>
       </c>
       <c r="R50" t="n">
-        <v>7021806</v>
+        <v>7021818</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6171,7 +6171,7 @@
         <v>130222703</v>
       </c>
       <c r="B51" t="n">
-        <v>83189</v>
+        <v>83191</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         <v>130222738</v>
       </c>
       <c r="B52" t="n">
-        <v>78221</v>
+        <v>78223</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>130222737</v>
       </c>
       <c r="B53" t="n">
-        <v>78221</v>
+        <v>78223</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>130222747</v>
       </c>
       <c r="B54" t="n">
-        <v>91773</v>
+        <v>91775</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6596,10 +6596,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130222723</v>
+        <v>130222754</v>
       </c>
       <c r="B55" t="n">
-        <v>57852</v>
+        <v>79211</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6607,31 +6607,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6639,10 +6634,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504117</v>
+        <v>504081</v>
       </c>
       <c r="R55" t="n">
-        <v>7021735</v>
+        <v>7021796</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6677,17 +6672,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6711,10 +6702,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130222754</v>
+        <v>130222723</v>
       </c>
       <c r="B56" t="n">
-        <v>79209</v>
+        <v>57854</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6722,26 +6713,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6749,10 +6745,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504081</v>
+        <v>504117</v>
       </c>
       <c r="R56" t="n">
-        <v>7021796</v>
+        <v>7021735</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6787,13 +6783,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6820,7 +6820,7 @@
         <v>130222739</v>
       </c>
       <c r="B57" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6937,10 +6937,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130222741</v>
+        <v>130222751</v>
       </c>
       <c r="B58" t="n">
-        <v>91755</v>
+        <v>91781</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6948,23 +6948,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
@@ -6979,10 +6975,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504078</v>
+        <v>504218</v>
       </c>
       <c r="R58" t="n">
-        <v>7022057</v>
+        <v>7022019</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7065,7 +7061,7 @@
         <v>130222748</v>
       </c>
       <c r="B59" t="n">
-        <v>91773</v>
+        <v>91775</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7172,10 +7168,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130222751</v>
+        <v>130222741</v>
       </c>
       <c r="B60" t="n">
-        <v>91779</v>
+        <v>91757</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7183,19 +7179,23 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
@@ -7210,10 +7210,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504218</v>
+        <v>504078</v>
       </c>
       <c r="R60" t="n">
-        <v>7022019</v>
+        <v>7022057</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7296,7 +7296,7 @@
         <v>130222721</v>
       </c>
       <c r="B61" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>130222740</v>
       </c>
       <c r="B62" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>130619758</v>
       </c>
       <c r="B63" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>130619765</v>
       </c>
       <c r="B64" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>130619759</v>
       </c>
       <c r="B65" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>130619766</v>
       </c>
       <c r="B66" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>130619760</v>
       </c>
       <c r="B67" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>130619762</v>
       </c>
       <c r="B68" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8200,10 +8200,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130619769</v>
+        <v>130619764</v>
       </c>
       <c r="B69" t="n">
-        <v>91755</v>
+        <v>57035</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8211,34 +8211,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504228</v>
+        <v>504059</v>
       </c>
       <c r="R69" t="n">
-        <v>7021996</v>
+        <v>7022053</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8270,7 +8278,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8280,12 +8288,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På grov torraka av gran, bhd 45 cm</t>
+          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8312,32 +8320,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130619761</v>
+        <v>130619769</v>
       </c>
       <c r="B70" t="n">
-        <v>92477</v>
+        <v>91757</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8347,10 +8355,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504231</v>
+        <v>504228</v>
       </c>
       <c r="R70" t="n">
-        <v>7021975</v>
+        <v>7021996</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8382,7 +8390,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8392,12 +8400,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På död gran</t>
+          <t>På grov torraka av gran, bhd 45 cm</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8424,53 +8432,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130619764</v>
+        <v>130619761</v>
       </c>
       <c r="B71" t="n">
-        <v>57033</v>
+        <v>92479</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>3298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504059</v>
+        <v>504231</v>
       </c>
       <c r="R71" t="n">
-        <v>7022053</v>
+        <v>7021975</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
+          <t>På död gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8547,7 +8547,7 @@
         <v>130619768</v>
       </c>
       <c r="B72" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>130619767</v>
       </c>
       <c r="B73" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>130222731</v>
       </c>
       <c r="B4" t="n">
-        <v>92214</v>
+        <v>92220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130222710</v>
+        <v>130222714</v>
       </c>
       <c r="B5" t="n">
         <v>91761</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504160</v>
+        <v>504091</v>
       </c>
       <c r="R5" t="n">
-        <v>7021867</v>
+        <v>7021759</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130222749</v>
+        <v>130222710</v>
       </c>
       <c r="B6" t="n">
-        <v>91775</v>
+        <v>91761</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504067</v>
+        <v>504160</v>
       </c>
       <c r="R6" t="n">
-        <v>7021774</v>
+        <v>7021867</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130222714</v>
+        <v>130222749</v>
       </c>
       <c r="B7" t="n">
-        <v>91761</v>
+        <v>91775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504091</v>
+        <v>504067</v>
       </c>
       <c r="R7" t="n">
-        <v>7021759</v>
+        <v>7021774</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1343,7 @@
         <v>130222732</v>
       </c>
       <c r="B8" t="n">
-        <v>92214</v>
+        <v>92220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130222712</v>
+        <v>130222716</v>
       </c>
       <c r="B9" t="n">
         <v>91761</v>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504057</v>
+        <v>504095</v>
       </c>
       <c r="R9" t="n">
-        <v>7021765</v>
+        <v>7021805</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,7 +1575,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130222716</v>
+        <v>130222712</v>
       </c>
       <c r="B10" t="n">
         <v>91761</v>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504095</v>
+        <v>504057</v>
       </c>
       <c r="R10" t="n">
-        <v>7021805</v>
+        <v>7021765</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1795,37 +1795,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130222701</v>
+        <v>130222705</v>
       </c>
       <c r="B12" t="n">
-        <v>83191</v>
+        <v>91725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1833,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504090</v>
+        <v>504210</v>
       </c>
       <c r="R12" t="n">
-        <v>7021787</v>
+        <v>7022007</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,41 +1905,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130222705</v>
+        <v>130222701</v>
       </c>
       <c r="B13" t="n">
-        <v>91725</v>
+        <v>83191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504210</v>
+        <v>504090</v>
       </c>
       <c r="R13" t="n">
-        <v>7022007</v>
+        <v>7021787</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130222713</v>
+        <v>130222711</v>
       </c>
       <c r="B16" t="n">
         <v>91761</v>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504135</v>
+        <v>504154</v>
       </c>
       <c r="R16" t="n">
-        <v>7021768</v>
+        <v>7021848</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2342,7 +2342,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130222711</v>
+        <v>130222713</v>
       </c>
       <c r="B17" t="n">
         <v>91761</v>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>504154</v>
+        <v>504135</v>
       </c>
       <c r="R17" t="n">
-        <v>7021848</v>
+        <v>7021768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2558,32 +2558,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130222727</v>
+        <v>130222706</v>
       </c>
       <c r="B19" t="n">
-        <v>92484</v>
+        <v>91725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>67</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504089</v>
+        <v>504083</v>
       </c>
       <c r="R19" t="n">
-        <v>7021772</v>
+        <v>7021773</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2651,21 +2651,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2683,41 +2668,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130222706</v>
+        <v>130222700</v>
       </c>
       <c r="B20" t="n">
-        <v>91725</v>
+        <v>83191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2725,10 +2706,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504083</v>
+        <v>504099</v>
       </c>
       <c r="R20" t="n">
-        <v>7021773</v>
+        <v>7021769</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2793,37 +2774,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130222700</v>
+        <v>130222727</v>
       </c>
       <c r="B21" t="n">
-        <v>83191</v>
+        <v>92488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>67</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2831,10 +2816,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>504099</v>
+        <v>504089</v>
       </c>
       <c r="R21" t="n">
-        <v>7021769</v>
+        <v>7021772</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2882,6 +2867,21 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130222753</v>
+        <v>130222720</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,26 +2910,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2937,10 +2942,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>504059</v>
+        <v>503952</v>
       </c>
       <c r="R22" t="n">
-        <v>7021781</v>
+        <v>7022000</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2975,13 +2980,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3005,7 +3014,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130222757</v>
+        <v>130222753</v>
       </c>
       <c r="B23" t="n">
         <v>79211</v>
@@ -3043,10 +3052,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504170</v>
+        <v>504059</v>
       </c>
       <c r="R23" t="n">
-        <v>7021800</v>
+        <v>7021781</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3111,10 +3120,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130222720</v>
+        <v>130222757</v>
       </c>
       <c r="B24" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,31 +3131,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3154,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503952</v>
+        <v>504170</v>
       </c>
       <c r="R24" t="n">
-        <v>7022000</v>
+        <v>7021800</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3192,17 +3196,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3787,10 +3787,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130222719</v>
+        <v>130222704</v>
       </c>
       <c r="B30" t="n">
-        <v>92479</v>
+        <v>91725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3798,21 +3798,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504219</v>
+        <v>504208</v>
       </c>
       <c r="R30" t="n">
-        <v>7022014</v>
+        <v>7022015</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3897,10 +3897,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130222734</v>
+        <v>130222756</v>
       </c>
       <c r="B31" t="n">
-        <v>92059</v>
+        <v>79211</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3908,30 +3908,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3939,10 +3935,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504221</v>
+        <v>504101</v>
       </c>
       <c r="R31" t="n">
-        <v>7022011</v>
+        <v>7021774</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3990,21 +3986,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4022,32 +4003,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130222742</v>
+        <v>130222719</v>
       </c>
       <c r="B32" t="n">
-        <v>91757</v>
+        <v>92483</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4064,10 +4045,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504227</v>
+        <v>504219</v>
       </c>
       <c r="R32" t="n">
-        <v>7022001</v>
+        <v>7022014</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4132,10 +4113,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130222746</v>
+        <v>130222715</v>
       </c>
       <c r="B33" t="n">
-        <v>91757</v>
+        <v>91761</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4143,21 +4124,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4174,10 +4155,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503973</v>
+        <v>504083</v>
       </c>
       <c r="R33" t="n">
-        <v>7021998</v>
+        <v>7021787</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4225,21 +4206,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4257,10 +4223,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130222715</v>
+        <v>130222746</v>
       </c>
       <c r="B34" t="n">
-        <v>91761</v>
+        <v>91757</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4268,21 +4234,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4299,10 +4265,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504083</v>
+        <v>503973</v>
       </c>
       <c r="R34" t="n">
-        <v>7021787</v>
+        <v>7021998</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4350,6 +4316,21 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4367,10 +4348,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130222756</v>
+        <v>130222742</v>
       </c>
       <c r="B35" t="n">
-        <v>79211</v>
+        <v>91757</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4378,26 +4359,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4405,10 +4390,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504101</v>
+        <v>504227</v>
       </c>
       <c r="R35" t="n">
-        <v>7021774</v>
+        <v>7022001</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4473,32 +4458,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130222704</v>
+        <v>130222734</v>
       </c>
       <c r="B36" t="n">
-        <v>91725</v>
+        <v>92059</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4515,10 +4500,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504208</v>
+        <v>504221</v>
       </c>
       <c r="R36" t="n">
-        <v>7022015</v>
+        <v>7022011</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4566,6 +4551,21 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
         <v>130222718</v>
       </c>
       <c r="B38" t="n">
-        <v>92479</v>
+        <v>92483</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5130,10 +5130,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130222735</v>
+        <v>130222708</v>
       </c>
       <c r="B42" t="n">
-        <v>92059</v>
+        <v>91761</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5141,21 +5141,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504166</v>
+        <v>504191</v>
       </c>
       <c r="R42" t="n">
-        <v>7021986</v>
+        <v>7022006</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5223,21 +5223,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5255,10 +5240,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130222708</v>
+        <v>130222735</v>
       </c>
       <c r="B43" t="n">
-        <v>91761</v>
+        <v>92059</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5266,21 +5251,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5297,10 +5282,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504191</v>
+        <v>504166</v>
       </c>
       <c r="R43" t="n">
-        <v>7022006</v>
+        <v>7021986</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5348,6 +5333,21 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5365,32 +5365,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130222733</v>
+        <v>130222745</v>
       </c>
       <c r="B44" t="n">
-        <v>92214</v>
+        <v>91757</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504161</v>
+        <v>504130</v>
       </c>
       <c r="R44" t="n">
-        <v>7021869</v>
+        <v>7021754</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5615,32 +5615,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130222745</v>
+        <v>130222733</v>
       </c>
       <c r="B46" t="n">
-        <v>91757</v>
+        <v>92220</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5657,10 +5657,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504130</v>
+        <v>504161</v>
       </c>
       <c r="R46" t="n">
-        <v>7021754</v>
+        <v>7021869</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5740,32 +5740,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130222699</v>
+        <v>130222726</v>
       </c>
       <c r="B47" t="n">
-        <v>83191</v>
+        <v>80345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5778,10 +5778,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504118</v>
+        <v>504106</v>
       </c>
       <c r="R47" t="n">
-        <v>7021776</v>
+        <v>7021741</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5846,32 +5846,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130222726</v>
+        <v>130222699</v>
       </c>
       <c r="B48" t="n">
-        <v>80345</v>
+        <v>83191</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5884,10 +5884,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504106</v>
+        <v>504118</v>
       </c>
       <c r="R48" t="n">
-        <v>7021741</v>
+        <v>7021776</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6486,10 +6486,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130222747</v>
+        <v>130222754</v>
       </c>
       <c r="B54" t="n">
-        <v>91775</v>
+        <v>79211</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6497,30 +6497,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6528,10 +6524,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504210</v>
+        <v>504081</v>
       </c>
       <c r="R54" t="n">
-        <v>7022007</v>
+        <v>7021796</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6596,37 +6592,46 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130222754</v>
+        <v>130222739</v>
       </c>
       <c r="B55" t="n">
-        <v>79211</v>
+        <v>98957</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6634,10 +6639,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504081</v>
+        <v>504054</v>
       </c>
       <c r="R55" t="n">
-        <v>7021796</v>
+        <v>7021735</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6670,6 +6675,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor finns på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6702,10 +6712,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130222723</v>
+        <v>130222747</v>
       </c>
       <c r="B56" t="n">
-        <v>57854</v>
+        <v>91775</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6713,29 +6723,28 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6745,10 +6754,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504117</v>
+        <v>504210</v>
       </c>
       <c r="R56" t="n">
-        <v>7021735</v>
+        <v>7022007</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6783,17 +6792,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6817,46 +6822,42 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130222739</v>
+        <v>130222723</v>
       </c>
       <c r="B57" t="n">
-        <v>98953</v>
+        <v>57854</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6864,7 +6865,7 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504054</v>
+        <v>504117</v>
       </c>
       <c r="R57" t="n">
         <v>7021735</v>
@@ -6904,7 +6905,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 3 plantor finns på fyndplatsen.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6913,7 +6914,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7058,10 +7058,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130222748</v>
+        <v>130222721</v>
       </c>
       <c r="B59" t="n">
-        <v>91775</v>
+        <v>57854</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7069,28 +7069,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7100,10 +7101,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504123</v>
+        <v>503954</v>
       </c>
       <c r="R59" t="n">
-        <v>7021748</v>
+        <v>7021984</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7138,13 +7139,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7293,10 +7298,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130222721</v>
+        <v>130222748</v>
       </c>
       <c r="B61" t="n">
-        <v>57854</v>
+        <v>91775</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7304,29 +7309,28 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7336,10 +7340,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503954</v>
+        <v>504123</v>
       </c>
       <c r="R61" t="n">
-        <v>7021984</v>
+        <v>7021748</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7374,17 +7378,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7411,7 +7411,7 @@
         <v>130222740</v>
       </c>
       <c r="B62" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8200,10 +8200,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130619764</v>
+        <v>130619769</v>
       </c>
       <c r="B69" t="n">
-        <v>57035</v>
+        <v>91757</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8211,42 +8211,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504059</v>
+        <v>504228</v>
       </c>
       <c r="R69" t="n">
-        <v>7022053</v>
+        <v>7021996</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8278,7 +8270,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8288,12 +8280,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
+          <t>På grov torraka av gran, bhd 45 cm</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8320,10 +8312,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130619769</v>
+        <v>130619764</v>
       </c>
       <c r="B70" t="n">
-        <v>91757</v>
+        <v>57035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8331,34 +8323,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504228</v>
+        <v>504059</v>
       </c>
       <c r="R70" t="n">
-        <v>7021996</v>
+        <v>7022053</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På grov torraka av gran, bhd 45 cm</t>
+          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8435,7 +8435,7 @@
         <v>130619761</v>
       </c>
       <c r="B71" t="n">
-        <v>92479</v>
+        <v>92483</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130222714</v>
+        <v>130222710</v>
       </c>
       <c r="B5" t="n">
         <v>91761</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504091</v>
+        <v>504160</v>
       </c>
       <c r="R5" t="n">
-        <v>7021759</v>
+        <v>7021867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130222710</v>
+        <v>130222749</v>
       </c>
       <c r="B6" t="n">
-        <v>91761</v>
+        <v>91775</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504160</v>
+        <v>504067</v>
       </c>
       <c r="R6" t="n">
-        <v>7021867</v>
+        <v>7021774</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130222749</v>
+        <v>130222714</v>
       </c>
       <c r="B7" t="n">
-        <v>91775</v>
+        <v>91761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504067</v>
+        <v>504091</v>
       </c>
       <c r="R7" t="n">
-        <v>7021774</v>
+        <v>7021759</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,32 +1340,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130222732</v>
+        <v>130222712</v>
       </c>
       <c r="B8" t="n">
-        <v>92220</v>
+        <v>91761</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504202</v>
+        <v>504057</v>
       </c>
       <c r="R8" t="n">
-        <v>7022015</v>
+        <v>7021765</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,21 +1433,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1465,32 +1450,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130222716</v>
+        <v>130222732</v>
       </c>
       <c r="B9" t="n">
-        <v>91761</v>
+        <v>92220</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504095</v>
+        <v>504202</v>
       </c>
       <c r="R9" t="n">
-        <v>7021805</v>
+        <v>7022015</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,6 +1543,21 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1575,7 +1575,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130222712</v>
+        <v>130222716</v>
       </c>
       <c r="B10" t="n">
         <v>91761</v>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504057</v>
+        <v>504095</v>
       </c>
       <c r="R10" t="n">
-        <v>7021765</v>
+        <v>7021805</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1795,41 +1795,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130222705</v>
+        <v>130222701</v>
       </c>
       <c r="B12" t="n">
-        <v>91725</v>
+        <v>83191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1837,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504210</v>
+        <v>504090</v>
       </c>
       <c r="R12" t="n">
-        <v>7022007</v>
+        <v>7021787</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,37 +1901,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130222701</v>
+        <v>130222705</v>
       </c>
       <c r="B13" t="n">
-        <v>83191</v>
+        <v>91725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504090</v>
+        <v>504210</v>
       </c>
       <c r="R13" t="n">
-        <v>7021787</v>
+        <v>7022007</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2126,37 +2126,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222730</v>
+        <v>130222713</v>
       </c>
       <c r="B15" t="n">
-        <v>80220</v>
+        <v>91761</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2164,10 +2168,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504166</v>
+        <v>504135</v>
       </c>
       <c r="R15" t="n">
-        <v>7021800</v>
+        <v>7021768</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2342,10 +2346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130222713</v>
+        <v>130222702</v>
       </c>
       <c r="B17" t="n">
-        <v>91761</v>
+        <v>83191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2353,30 +2357,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>504135</v>
+        <v>504100</v>
       </c>
       <c r="R17" t="n">
-        <v>7021768</v>
+        <v>7021801</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,32 +2452,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130222702</v>
+        <v>130222730</v>
       </c>
       <c r="B18" t="n">
-        <v>83191</v>
+        <v>80220</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504100</v>
+        <v>504166</v>
       </c>
       <c r="R18" t="n">
-        <v>7021801</v>
+        <v>7021800</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,32 +2558,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130222706</v>
+        <v>130222727</v>
       </c>
       <c r="B19" t="n">
-        <v>91725</v>
+        <v>92488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>67</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504083</v>
+        <v>504089</v>
       </c>
       <c r="R19" t="n">
-        <v>7021773</v>
+        <v>7021772</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2651,6 +2651,21 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2668,37 +2683,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130222700</v>
+        <v>130222706</v>
       </c>
       <c r="B20" t="n">
-        <v>83191</v>
+        <v>91725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2706,10 +2725,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504099</v>
+        <v>504083</v>
       </c>
       <c r="R20" t="n">
-        <v>7021769</v>
+        <v>7021773</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,41 +2793,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130222727</v>
+        <v>130222700</v>
       </c>
       <c r="B21" t="n">
-        <v>92488</v>
+        <v>83191</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>67</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2816,10 +2831,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>504089</v>
+        <v>504099</v>
       </c>
       <c r="R21" t="n">
-        <v>7021772</v>
+        <v>7021769</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2867,21 +2882,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130222720</v>
+        <v>130222753</v>
       </c>
       <c r="B22" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,31 +2910,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2942,10 +2937,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503952</v>
+        <v>504059</v>
       </c>
       <c r="R22" t="n">
-        <v>7022000</v>
+        <v>7021781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2980,17 +2975,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3014,7 +3005,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130222753</v>
+        <v>130222757</v>
       </c>
       <c r="B23" t="n">
         <v>79211</v>
@@ -3052,10 +3043,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504059</v>
+        <v>504170</v>
       </c>
       <c r="R23" t="n">
-        <v>7021781</v>
+        <v>7021800</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3120,10 +3111,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130222757</v>
+        <v>130222720</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,26 +3122,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3158,10 +3154,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504170</v>
+        <v>503952</v>
       </c>
       <c r="R24" t="n">
-        <v>7021800</v>
+        <v>7022000</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3196,13 +3192,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3575,10 +3575,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130222750</v>
+        <v>130222752</v>
       </c>
       <c r="B28" t="n">
-        <v>91781</v>
+        <v>79211</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3586,26 +3586,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504216</v>
+        <v>504097</v>
       </c>
       <c r="R28" t="n">
-        <v>7022005</v>
+        <v>7021762</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3681,10 +3681,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130222752</v>
+        <v>130222750</v>
       </c>
       <c r="B29" t="n">
-        <v>79211</v>
+        <v>91781</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3692,26 +3692,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504097</v>
+        <v>504216</v>
       </c>
       <c r="R29" t="n">
-        <v>7021762</v>
+        <v>7022005</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3787,32 +3787,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130222704</v>
+        <v>130222715</v>
       </c>
       <c r="B30" t="n">
-        <v>91725</v>
+        <v>91761</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504208</v>
+        <v>504083</v>
       </c>
       <c r="R30" t="n">
-        <v>7022015</v>
+        <v>7021787</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3897,37 +3897,41 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130222756</v>
+        <v>130222719</v>
       </c>
       <c r="B31" t="n">
-        <v>79211</v>
+        <v>92483</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3935,10 +3939,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504101</v>
+        <v>504219</v>
       </c>
       <c r="R31" t="n">
-        <v>7021774</v>
+        <v>7022014</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4003,41 +4007,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130222719</v>
+        <v>130222756</v>
       </c>
       <c r="B32" t="n">
-        <v>92483</v>
+        <v>79211</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504219</v>
+        <v>504101</v>
       </c>
       <c r="R32" t="n">
-        <v>7022014</v>
+        <v>7021774</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4113,32 +4113,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130222715</v>
+        <v>130222704</v>
       </c>
       <c r="B33" t="n">
-        <v>91761</v>
+        <v>91725</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4155,10 +4155,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504083</v>
+        <v>504208</v>
       </c>
       <c r="R33" t="n">
-        <v>7021787</v>
+        <v>7022015</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4223,7 +4223,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130222746</v>
+        <v>130222742</v>
       </c>
       <c r="B34" t="n">
         <v>91757</v>
@@ -4265,10 +4265,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503973</v>
+        <v>504227</v>
       </c>
       <c r="R34" t="n">
-        <v>7021998</v>
+        <v>7022001</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4316,21 +4316,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4348,7 +4333,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130222742</v>
+        <v>130222746</v>
       </c>
       <c r="B35" t="n">
         <v>91757</v>
@@ -4390,10 +4375,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504227</v>
+        <v>503973</v>
       </c>
       <c r="R35" t="n">
-        <v>7022001</v>
+        <v>7021998</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4441,6 +4426,21 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4914,41 +4914,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130222709</v>
+        <v>130222729</v>
       </c>
       <c r="B40" t="n">
-        <v>91761</v>
+        <v>80220</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4956,10 +4952,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504104</v>
+        <v>504173</v>
       </c>
       <c r="R40" t="n">
-        <v>7021877</v>
+        <v>7021803</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5024,37 +5020,41 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130222729</v>
+        <v>130222709</v>
       </c>
       <c r="B41" t="n">
-        <v>80220</v>
+        <v>91761</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504173</v>
+        <v>504104</v>
       </c>
       <c r="R41" t="n">
-        <v>7021803</v>
+        <v>7021877</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5365,7 +5365,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130222745</v>
+        <v>130222744</v>
       </c>
       <c r="B44" t="n">
         <v>91757</v>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504130</v>
+        <v>504178</v>
       </c>
       <c r="R44" t="n">
-        <v>7021754</v>
+        <v>7021976</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130222744</v>
+        <v>130222745</v>
       </c>
       <c r="B45" t="n">
         <v>91757</v>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504178</v>
+        <v>504130</v>
       </c>
       <c r="R45" t="n">
-        <v>7021976</v>
+        <v>7021754</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5615,41 +5615,37 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130222733</v>
+        <v>130222726</v>
       </c>
       <c r="B46" t="n">
-        <v>92220</v>
+        <v>80345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5657,10 +5653,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504161</v>
+        <v>504106</v>
       </c>
       <c r="R46" t="n">
-        <v>7021869</v>
+        <v>7021741</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5708,21 +5704,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5740,37 +5721,41 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130222726</v>
+        <v>130222733</v>
       </c>
       <c r="B47" t="n">
-        <v>80345</v>
+        <v>92220</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5778,10 +5763,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504106</v>
+        <v>504161</v>
       </c>
       <c r="R47" t="n">
-        <v>7021741</v>
+        <v>7021869</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5829,6 +5814,21 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6486,37 +6486,46 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130222754</v>
+        <v>130222739</v>
       </c>
       <c r="B54" t="n">
-        <v>79211</v>
+        <v>98957</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6524,10 +6533,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504081</v>
+        <v>504054</v>
       </c>
       <c r="R54" t="n">
-        <v>7021796</v>
+        <v>7021735</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6560,6 +6569,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor finns på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6592,46 +6606,41 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130222739</v>
+        <v>130222747</v>
       </c>
       <c r="B55" t="n">
-        <v>98957</v>
+        <v>91775</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6639,10 +6648,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504054</v>
+        <v>504210</v>
       </c>
       <c r="R55" t="n">
-        <v>7021735</v>
+        <v>7022007</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6675,11 +6684,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Minst 3 plantor finns på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6712,10 +6716,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130222747</v>
+        <v>130222754</v>
       </c>
       <c r="B56" t="n">
-        <v>91775</v>
+        <v>79211</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6723,30 +6727,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504210</v>
+        <v>504081</v>
       </c>
       <c r="R56" t="n">
-        <v>7022007</v>
+        <v>7021796</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6937,10 +6937,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130222751</v>
+        <v>130222748</v>
       </c>
       <c r="B58" t="n">
-        <v>91781</v>
+        <v>91775</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6948,19 +6948,23 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
@@ -6975,10 +6979,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504218</v>
+        <v>504123</v>
       </c>
       <c r="R58" t="n">
-        <v>7022019</v>
+        <v>7021748</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7026,21 +7030,6 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7058,10 +7047,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130222721</v>
+        <v>130222741</v>
       </c>
       <c r="B59" t="n">
-        <v>57854</v>
+        <v>91757</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7069,29 +7058,28 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7101,10 +7089,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503954</v>
+        <v>504078</v>
       </c>
       <c r="R59" t="n">
-        <v>7021984</v>
+        <v>7022057</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7139,23 +7127,34 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7173,10 +7172,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130222741</v>
+        <v>130222751</v>
       </c>
       <c r="B60" t="n">
-        <v>91757</v>
+        <v>91781</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7184,23 +7183,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
@@ -7215,10 +7210,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504078</v>
+        <v>504218</v>
       </c>
       <c r="R60" t="n">
-        <v>7022057</v>
+        <v>7022019</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7298,10 +7293,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130222748</v>
+        <v>130222721</v>
       </c>
       <c r="B61" t="n">
-        <v>91775</v>
+        <v>57854</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7309,28 +7304,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7340,10 +7336,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504123</v>
+        <v>503954</v>
       </c>
       <c r="R61" t="n">
-        <v>7021748</v>
+        <v>7021984</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7378,13 +7374,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -8200,10 +8200,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130619769</v>
+        <v>130619764</v>
       </c>
       <c r="B69" t="n">
-        <v>91757</v>
+        <v>57035</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8211,34 +8211,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504228</v>
+        <v>504059</v>
       </c>
       <c r="R69" t="n">
-        <v>7021996</v>
+        <v>7022053</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8270,7 +8278,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8280,12 +8288,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På grov torraka av gran, bhd 45 cm</t>
+          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8312,53 +8320,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130619764</v>
+        <v>130619761</v>
       </c>
       <c r="B70" t="n">
-        <v>57035</v>
+        <v>92483</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102612</v>
+        <v>3298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504059</v>
+        <v>504231</v>
       </c>
       <c r="R70" t="n">
-        <v>7022053</v>
+        <v>7021975</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
+          <t>På död gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8432,32 +8432,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130619761</v>
+        <v>130619769</v>
       </c>
       <c r="B71" t="n">
-        <v>92483</v>
+        <v>91757</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8467,10 +8467,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504231</v>
+        <v>504228</v>
       </c>
       <c r="R71" t="n">
-        <v>7021975</v>
+        <v>7021996</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På död gran</t>
+          <t>På grov torraka av gran, bhd 45 cm</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130222710</v>
+        <v>130222714</v>
       </c>
       <c r="B5" t="n">
         <v>91761</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504160</v>
+        <v>504091</v>
       </c>
       <c r="R5" t="n">
-        <v>7021867</v>
+        <v>7021759</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130222749</v>
+        <v>130222710</v>
       </c>
       <c r="B6" t="n">
-        <v>91775</v>
+        <v>91761</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504067</v>
+        <v>504160</v>
       </c>
       <c r="R6" t="n">
-        <v>7021774</v>
+        <v>7021867</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130222714</v>
+        <v>130222749</v>
       </c>
       <c r="B7" t="n">
-        <v>91761</v>
+        <v>91775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504091</v>
+        <v>504067</v>
       </c>
       <c r="R7" t="n">
-        <v>7021759</v>
+        <v>7021774</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,32 +1340,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130222712</v>
+        <v>130222732</v>
       </c>
       <c r="B8" t="n">
-        <v>91761</v>
+        <v>92220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504057</v>
+        <v>504202</v>
       </c>
       <c r="R8" t="n">
-        <v>7021765</v>
+        <v>7022015</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,6 +1433,21 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1450,32 +1465,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130222732</v>
+        <v>130222716</v>
       </c>
       <c r="B9" t="n">
-        <v>92220</v>
+        <v>91761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504202</v>
+        <v>504095</v>
       </c>
       <c r="R9" t="n">
-        <v>7022015</v>
+        <v>7021805</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,21 +1558,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1575,7 +1575,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130222716</v>
+        <v>130222712</v>
       </c>
       <c r="B10" t="n">
         <v>91761</v>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504095</v>
+        <v>504057</v>
       </c>
       <c r="R10" t="n">
-        <v>7021805</v>
+        <v>7021765</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2011,10 +2011,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130222724</v>
+        <v>130222702</v>
       </c>
       <c r="B14" t="n">
-        <v>57854</v>
+        <v>83191</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,31 +2022,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2054,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504139</v>
+        <v>504100</v>
       </c>
       <c r="R14" t="n">
-        <v>7021798</v>
+        <v>7021801</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,17 +2087,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2126,41 +2117,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222713</v>
+        <v>130222730</v>
       </c>
       <c r="B15" t="n">
-        <v>91761</v>
+        <v>80220</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2168,10 +2155,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504135</v>
+        <v>504166</v>
       </c>
       <c r="R15" t="n">
-        <v>7021768</v>
+        <v>7021800</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,10 +2223,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130222711</v>
+        <v>130222724</v>
       </c>
       <c r="B16" t="n">
-        <v>91761</v>
+        <v>57854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,28 +2234,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2278,10 +2266,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504154</v>
+        <v>504139</v>
       </c>
       <c r="R16" t="n">
-        <v>7021848</v>
+        <v>7021798</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,13 +2304,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2346,10 +2338,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130222702</v>
+        <v>130222711</v>
       </c>
       <c r="B17" t="n">
-        <v>83191</v>
+        <v>91761</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,26 +2349,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2384,10 +2380,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>504100</v>
+        <v>504154</v>
       </c>
       <c r="R17" t="n">
-        <v>7021801</v>
+        <v>7021848</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,37 +2448,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130222730</v>
+        <v>130222713</v>
       </c>
       <c r="B18" t="n">
-        <v>80220</v>
+        <v>91761</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>504166</v>
+        <v>504135</v>
       </c>
       <c r="R18" t="n">
-        <v>7021800</v>
+        <v>7021768</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,32 +2558,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130222727</v>
+        <v>130222706</v>
       </c>
       <c r="B19" t="n">
-        <v>92488</v>
+        <v>91725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>67</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504089</v>
+        <v>504083</v>
       </c>
       <c r="R19" t="n">
-        <v>7021772</v>
+        <v>7021773</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2651,21 +2651,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2683,41 +2668,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130222706</v>
+        <v>130222700</v>
       </c>
       <c r="B20" t="n">
-        <v>91725</v>
+        <v>83191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2725,10 +2706,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504083</v>
+        <v>504099</v>
       </c>
       <c r="R20" t="n">
-        <v>7021773</v>
+        <v>7021769</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2793,37 +2774,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130222700</v>
+        <v>130222727</v>
       </c>
       <c r="B21" t="n">
-        <v>83191</v>
+        <v>92488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>67</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2831,10 +2816,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>504099</v>
+        <v>504089</v>
       </c>
       <c r="R21" t="n">
-        <v>7021769</v>
+        <v>7021772</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2882,6 +2867,21 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130222753</v>
+        <v>130222720</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,26 +2910,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2937,10 +2942,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>504059</v>
+        <v>503952</v>
       </c>
       <c r="R22" t="n">
-        <v>7021781</v>
+        <v>7022000</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2975,13 +2980,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3005,7 +3014,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130222757</v>
+        <v>130222753</v>
       </c>
       <c r="B23" t="n">
         <v>79211</v>
@@ -3043,10 +3052,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504170</v>
+        <v>504059</v>
       </c>
       <c r="R23" t="n">
-        <v>7021800</v>
+        <v>7021781</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3111,10 +3120,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130222720</v>
+        <v>130222757</v>
       </c>
       <c r="B24" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3122,31 +3131,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3154,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503952</v>
+        <v>504170</v>
       </c>
       <c r="R24" t="n">
-        <v>7022000</v>
+        <v>7021800</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3192,17 +3196,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3344,10 +3344,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130222755</v>
+        <v>130222743</v>
       </c>
       <c r="B26" t="n">
-        <v>79211</v>
+        <v>91757</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,26 +3355,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3382,10 +3386,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504177</v>
+        <v>504223</v>
       </c>
       <c r="R26" t="n">
-        <v>7021847</v>
+        <v>7022010</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3433,6 +3437,21 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3450,10 +3469,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130222743</v>
+        <v>130222755</v>
       </c>
       <c r="B27" t="n">
-        <v>91757</v>
+        <v>79211</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3461,30 +3480,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3492,10 +3507,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504223</v>
+        <v>504177</v>
       </c>
       <c r="R27" t="n">
-        <v>7022010</v>
+        <v>7021847</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3543,21 +3558,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130222719</v>
+        <v>130222746</v>
       </c>
       <c r="B31" t="n">
-        <v>92483</v>
+        <v>91757</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>504219</v>
+        <v>503973</v>
       </c>
       <c r="R31" t="n">
-        <v>7022014</v>
+        <v>7021998</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3990,6 +3990,21 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4007,10 +4022,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130222756</v>
+        <v>130222742</v>
       </c>
       <c r="B32" t="n">
-        <v>79211</v>
+        <v>91757</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4018,26 +4033,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4045,10 +4064,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504101</v>
+        <v>504227</v>
       </c>
       <c r="R32" t="n">
-        <v>7021774</v>
+        <v>7022001</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4113,32 +4132,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130222704</v>
+        <v>130222734</v>
       </c>
       <c r="B33" t="n">
-        <v>91725</v>
+        <v>92059</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4155,10 +4174,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504208</v>
+        <v>504221</v>
       </c>
       <c r="R33" t="n">
-        <v>7022015</v>
+        <v>7022011</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4206,6 +4225,21 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4223,10 +4257,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130222742</v>
+        <v>130222756</v>
       </c>
       <c r="B34" t="n">
-        <v>91757</v>
+        <v>79211</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4234,30 +4268,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4265,10 +4295,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504227</v>
+        <v>504101</v>
       </c>
       <c r="R34" t="n">
-        <v>7022001</v>
+        <v>7021774</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4333,32 +4363,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130222746</v>
+        <v>130222704</v>
       </c>
       <c r="B35" t="n">
-        <v>91757</v>
+        <v>91725</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4375,10 +4405,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503973</v>
+        <v>504208</v>
       </c>
       <c r="R35" t="n">
-        <v>7021998</v>
+        <v>7022015</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4426,21 +4456,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4458,32 +4473,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130222734</v>
+        <v>130222719</v>
       </c>
       <c r="B36" t="n">
-        <v>92059</v>
+        <v>92483</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4500,10 +4515,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504221</v>
+        <v>504219</v>
       </c>
       <c r="R36" t="n">
-        <v>7022011</v>
+        <v>7022014</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4551,21 +4566,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5365,7 +5365,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130222744</v>
+        <v>130222745</v>
       </c>
       <c r="B44" t="n">
         <v>91757</v>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504178</v>
+        <v>504130</v>
       </c>
       <c r="R44" t="n">
-        <v>7021976</v>
+        <v>7021754</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130222745</v>
+        <v>130222744</v>
       </c>
       <c r="B45" t="n">
         <v>91757</v>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504130</v>
+        <v>504178</v>
       </c>
       <c r="R45" t="n">
-        <v>7021754</v>
+        <v>7021976</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5615,37 +5615,41 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130222726</v>
+        <v>130222733</v>
       </c>
       <c r="B46" t="n">
-        <v>80345</v>
+        <v>92220</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5653,10 +5657,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504106</v>
+        <v>504161</v>
       </c>
       <c r="R46" t="n">
-        <v>7021741</v>
+        <v>7021869</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5704,6 +5708,21 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5721,41 +5740,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130222733</v>
+        <v>130222726</v>
       </c>
       <c r="B47" t="n">
-        <v>92220</v>
+        <v>80345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5763,10 +5778,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504161</v>
+        <v>504106</v>
       </c>
       <c r="R47" t="n">
-        <v>7021869</v>
+        <v>7021741</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5814,21 +5829,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6486,46 +6486,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130222739</v>
+        <v>130222723</v>
       </c>
       <c r="B54" t="n">
-        <v>98957</v>
+        <v>57854</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6533,7 +6529,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504054</v>
+        <v>504117</v>
       </c>
       <c r="R54" t="n">
         <v>7021735</v>
@@ -6573,7 +6569,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 3 plantor finns på fyndplatsen.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6582,7 +6578,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6606,41 +6601,46 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130222747</v>
+        <v>130222739</v>
       </c>
       <c r="B55" t="n">
-        <v>91775</v>
+        <v>98957</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504210</v>
+        <v>504054</v>
       </c>
       <c r="R55" t="n">
-        <v>7022007</v>
+        <v>7021735</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6684,6 +6684,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 3 plantor finns på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6716,10 +6721,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130222754</v>
+        <v>130222747</v>
       </c>
       <c r="B56" t="n">
-        <v>79211</v>
+        <v>91775</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6727,26 +6732,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6754,10 +6763,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504081</v>
+        <v>504210</v>
       </c>
       <c r="R56" t="n">
-        <v>7021796</v>
+        <v>7022007</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6822,10 +6831,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130222723</v>
+        <v>130222754</v>
       </c>
       <c r="B57" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6833,31 +6842,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6865,10 +6869,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504117</v>
+        <v>504081</v>
       </c>
       <c r="R57" t="n">
-        <v>7021735</v>
+        <v>7021796</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6903,17 +6907,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6937,41 +6937,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130222748</v>
+        <v>130222740</v>
       </c>
       <c r="B58" t="n">
-        <v>91775</v>
+        <v>98957</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6979,10 +6984,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504123</v>
+        <v>504087</v>
       </c>
       <c r="R58" t="n">
-        <v>7021748</v>
+        <v>7021765</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7015,6 +7020,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Minst 8 plantor på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7172,10 +7182,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130222751</v>
+        <v>130222748</v>
       </c>
       <c r="B60" t="n">
-        <v>91781</v>
+        <v>91775</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7183,19 +7193,23 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
@@ -7210,10 +7224,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504218</v>
+        <v>504123</v>
       </c>
       <c r="R60" t="n">
-        <v>7022019</v>
+        <v>7021748</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7261,21 +7275,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7293,10 +7292,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130222721</v>
+        <v>130222751</v>
       </c>
       <c r="B61" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7304,29 +7303,24 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7336,10 +7330,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503954</v>
+        <v>504218</v>
       </c>
       <c r="R61" t="n">
-        <v>7021984</v>
+        <v>7022019</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7374,23 +7368,34 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7408,46 +7413,42 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130222740</v>
+        <v>130222721</v>
       </c>
       <c r="B62" t="n">
-        <v>98957</v>
+        <v>57854</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7455,10 +7456,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>504087</v>
+        <v>503954</v>
       </c>
       <c r="R62" t="n">
-        <v>7021765</v>
+        <v>7021984</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7495,7 +7496,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Minst 8 plantor på fyndplatsen.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7504,7 +7505,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -8200,53 +8200,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130619764</v>
+        <v>130619761</v>
       </c>
       <c r="B69" t="n">
-        <v>57035</v>
+        <v>92483</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102612</v>
+        <v>3298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504059</v>
+        <v>504231</v>
       </c>
       <c r="R69" t="n">
-        <v>7022053</v>
+        <v>7021975</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8278,7 +8270,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8288,12 +8280,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
+          <t>På död gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8320,32 +8312,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130619761</v>
+        <v>130619769</v>
       </c>
       <c r="B70" t="n">
-        <v>92483</v>
+        <v>91757</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8355,10 +8347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504231</v>
+        <v>504228</v>
       </c>
       <c r="R70" t="n">
-        <v>7021975</v>
+        <v>7021996</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8390,7 +8382,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8400,12 +8392,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På död gran</t>
+          <t>På grov torraka av gran, bhd 45 cm</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8432,10 +8424,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130619769</v>
+        <v>130619764</v>
       </c>
       <c r="B71" t="n">
-        <v>91757</v>
+        <v>57035</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8443,34 +8435,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504228</v>
+        <v>504059</v>
       </c>
       <c r="R71" t="n">
-        <v>7021996</v>
+        <v>7022053</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På grov torraka av gran, bhd 45 cm</t>
+          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -8200,32 +8200,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130619761</v>
+        <v>130619769</v>
       </c>
       <c r="B69" t="n">
-        <v>92483</v>
+        <v>91757</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504231</v>
+        <v>504228</v>
       </c>
       <c r="R69" t="n">
-        <v>7021975</v>
+        <v>7021996</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På död gran</t>
+          <t>På grov torraka av gran, bhd 45 cm</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8312,32 +8312,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130619769</v>
+        <v>130619761</v>
       </c>
       <c r="B70" t="n">
-        <v>91757</v>
+        <v>92483</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504228</v>
+        <v>504231</v>
       </c>
       <c r="R70" t="n">
-        <v>7021996</v>
+        <v>7021975</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På grov torraka av gran, bhd 45 cm</t>
+          <t>På död gran</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -7531,7 +7531,7 @@
         <v>130619758</v>
       </c>
       <c r="B63" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>130619765</v>
       </c>
       <c r="B64" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>130619759</v>
       </c>
       <c r="B65" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>130619766</v>
       </c>
       <c r="B66" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>130619760</v>
       </c>
       <c r="B67" t="n">
-        <v>80316</v>
+        <v>80324</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>130619762</v>
       </c>
       <c r="B68" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8200,32 +8200,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130619769</v>
+        <v>130619761</v>
       </c>
       <c r="B69" t="n">
-        <v>91757</v>
+        <v>92496</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504228</v>
+        <v>504231</v>
       </c>
       <c r="R69" t="n">
-        <v>7021996</v>
+        <v>7021975</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På grov torraka av gran, bhd 45 cm</t>
+          <t>På död gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8312,32 +8312,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130619761</v>
+        <v>130619769</v>
       </c>
       <c r="B70" t="n">
-        <v>92483</v>
+        <v>91770</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504231</v>
+        <v>504228</v>
       </c>
       <c r="R70" t="n">
-        <v>7021975</v>
+        <v>7021996</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På död gran</t>
+          <t>På grov torraka av gran, bhd 45 cm</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8427,7 +8427,7 @@
         <v>130619764</v>
       </c>
       <c r="B71" t="n">
-        <v>57035</v>
+        <v>57043</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>130619768</v>
       </c>
       <c r="B72" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>130619767</v>
       </c>
       <c r="B73" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -7531,7 +7531,7 @@
         <v>130619758</v>
       </c>
       <c r="B63" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>130619765</v>
       </c>
       <c r="B64" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>130619759</v>
       </c>
       <c r="B65" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>130619766</v>
       </c>
       <c r="B66" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>130619760</v>
       </c>
       <c r="B67" t="n">
-        <v>80324</v>
+        <v>80325</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>130619762</v>
       </c>
       <c r="B68" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8200,32 +8200,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130619761</v>
+        <v>130619769</v>
       </c>
       <c r="B69" t="n">
-        <v>92496</v>
+        <v>91771</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504231</v>
+        <v>504228</v>
       </c>
       <c r="R69" t="n">
-        <v>7021975</v>
+        <v>7021996</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På död gran</t>
+          <t>På grov torraka av gran, bhd 45 cm</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8312,32 +8312,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130619769</v>
+        <v>130619761</v>
       </c>
       <c r="B70" t="n">
-        <v>91770</v>
+        <v>92497</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504228</v>
+        <v>504231</v>
       </c>
       <c r="R70" t="n">
-        <v>7021996</v>
+        <v>7021975</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På grov torraka av gran, bhd 45 cm</t>
+          <t>På död gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8427,7 +8427,7 @@
         <v>130619764</v>
       </c>
       <c r="B71" t="n">
-        <v>57043</v>
+        <v>57044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>130619768</v>
       </c>
       <c r="B72" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>130619767</v>
       </c>
       <c r="B73" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -7531,7 +7531,7 @@
         <v>130619758</v>
       </c>
       <c r="B63" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>130619765</v>
       </c>
       <c r="B64" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>130619759</v>
       </c>
       <c r="B65" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>130619766</v>
       </c>
       <c r="B66" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>130619760</v>
       </c>
       <c r="B67" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>130619762</v>
       </c>
       <c r="B68" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8200,10 +8200,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130619769</v>
+        <v>130619764</v>
       </c>
       <c r="B69" t="n">
-        <v>91771</v>
+        <v>57044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8211,34 +8211,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504228</v>
+        <v>504059</v>
       </c>
       <c r="R69" t="n">
-        <v>7021996</v>
+        <v>7022053</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8270,7 +8278,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8280,12 +8288,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På grov torraka av gran, bhd 45 cm</t>
+          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8312,32 +8320,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130619761</v>
+        <v>130619769</v>
       </c>
       <c r="B70" t="n">
-        <v>92497</v>
+        <v>91772</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8347,10 +8355,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504231</v>
+        <v>504228</v>
       </c>
       <c r="R70" t="n">
-        <v>7021975</v>
+        <v>7021996</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8382,7 +8390,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8392,12 +8400,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På död gran</t>
+          <t>På grov torraka av gran, bhd 45 cm</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8424,53 +8432,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130619764</v>
+        <v>130619761</v>
       </c>
       <c r="B71" t="n">
-        <v>57044</v>
+        <v>92498</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>3298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504059</v>
+        <v>504231</v>
       </c>
       <c r="R71" t="n">
-        <v>7022053</v>
+        <v>7021975</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
+          <t>På död gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8547,7 +8547,7 @@
         <v>130619768</v>
       </c>
       <c r="B72" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>130619767</v>
       </c>
       <c r="B73" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -8200,53 +8200,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130619764</v>
+        <v>130619761</v>
       </c>
       <c r="B69" t="n">
-        <v>57044</v>
+        <v>92498</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102612</v>
+        <v>3298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504059</v>
+        <v>504231</v>
       </c>
       <c r="R69" t="n">
-        <v>7022053</v>
+        <v>7021975</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8278,7 +8270,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8288,12 +8280,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
+          <t>På död gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8432,45 +8424,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130619761</v>
+        <v>130619764</v>
       </c>
       <c r="B71" t="n">
-        <v>92498</v>
+        <v>57044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3298</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504231</v>
+        <v>504059</v>
       </c>
       <c r="R71" t="n">
-        <v>7021975</v>
+        <v>7022053</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På död gran</t>
+          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -7864,10 +7864,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130619766</v>
+        <v>130619760</v>
       </c>
       <c r="B66" t="n">
-        <v>57864</v>
+        <v>80326</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7875,21 +7875,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7899,10 +7899,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503958</v>
+        <v>504274</v>
       </c>
       <c r="R66" t="n">
-        <v>7021988</v>
+        <v>7021941</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Äldre ringhack, gran</t>
+          <t>På döende eller död sälg</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7976,10 +7976,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130619760</v>
+        <v>130619762</v>
       </c>
       <c r="B67" t="n">
-        <v>80326</v>
+        <v>79221</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7987,21 +7987,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8011,10 +8011,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>504274</v>
+        <v>504212</v>
       </c>
       <c r="R67" t="n">
-        <v>7021941</v>
+        <v>7021967</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På döende eller död sälg</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8088,32 +8088,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130619762</v>
+        <v>130619761</v>
       </c>
       <c r="B68" t="n">
-        <v>79221</v>
+        <v>92498</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>504212</v>
+        <v>504231</v>
       </c>
       <c r="R68" t="n">
-        <v>7021967</v>
+        <v>7021975</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På död gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8200,32 +8200,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130619761</v>
+        <v>130619769</v>
       </c>
       <c r="B69" t="n">
-        <v>92498</v>
+        <v>91772</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504231</v>
+        <v>504228</v>
       </c>
       <c r="R69" t="n">
-        <v>7021975</v>
+        <v>7021996</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På död gran</t>
+          <t>På grov torraka av gran, bhd 45 cm</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8312,10 +8312,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130619769</v>
+        <v>130619764</v>
       </c>
       <c r="B70" t="n">
-        <v>91772</v>
+        <v>57044</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8323,34 +8323,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504228</v>
+        <v>504059</v>
       </c>
       <c r="R70" t="n">
-        <v>7021996</v>
+        <v>7022053</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8382,7 +8390,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8392,12 +8400,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På grov torraka av gran, bhd 45 cm</t>
+          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8424,10 +8432,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130619764</v>
+        <v>130619768</v>
       </c>
       <c r="B71" t="n">
-        <v>57044</v>
+        <v>79221</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8435,42 +8443,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504059</v>
+        <v>504172</v>
       </c>
       <c r="R71" t="n">
-        <v>7022053</v>
+        <v>7022030</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
+          <t>På torraka av gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8544,7 +8544,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130619768</v>
+        <v>130619767</v>
       </c>
       <c r="B72" t="n">
         <v>79221</v>
@@ -8579,10 +8579,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>504172</v>
+        <v>504062</v>
       </c>
       <c r="R72" t="n">
-        <v>7022030</v>
+        <v>7022023</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På torraka av gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8656,10 +8656,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130619767</v>
+        <v>130619766</v>
       </c>
       <c r="B73" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8667,21 +8667,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8691,10 +8691,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>504062</v>
+        <v>503958</v>
       </c>
       <c r="R73" t="n">
-        <v>7022023</v>
+        <v>7021988</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -8088,32 +8088,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130619761</v>
+        <v>130619769</v>
       </c>
       <c r="B68" t="n">
-        <v>92498</v>
+        <v>91772</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>504231</v>
+        <v>504228</v>
       </c>
       <c r="R68" t="n">
-        <v>7021975</v>
+        <v>7021996</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På död gran</t>
+          <t>På grov torraka av gran, bhd 45 cm</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8200,32 +8200,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130619769</v>
+        <v>130619761</v>
       </c>
       <c r="B69" t="n">
-        <v>91772</v>
+        <v>92498</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504228</v>
+        <v>504231</v>
       </c>
       <c r="R69" t="n">
-        <v>7021996</v>
+        <v>7021975</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På grov torraka av gran, bhd 45 cm</t>
+          <t>På död gran</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -8088,32 +8088,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130619769</v>
+        <v>130619761</v>
       </c>
       <c r="B68" t="n">
-        <v>91772</v>
+        <v>92498</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>504228</v>
+        <v>504231</v>
       </c>
       <c r="R68" t="n">
-        <v>7021996</v>
+        <v>7021975</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På grov torraka av gran, bhd 45 cm</t>
+          <t>På död gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8200,32 +8200,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130619761</v>
+        <v>130619769</v>
       </c>
       <c r="B69" t="n">
-        <v>92498</v>
+        <v>91772</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504231</v>
+        <v>504228</v>
       </c>
       <c r="R69" t="n">
-        <v>7021975</v>
+        <v>7021996</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På död gran</t>
+          <t>På grov torraka av gran, bhd 45 cm</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -8091,7 +8091,7 @@
         <v>130619761</v>
       </c>
       <c r="B68" t="n">
-        <v>92498</v>
+        <v>92506</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>130619769</v>
       </c>
       <c r="B69" t="n">
-        <v>91772</v>
+        <v>91780</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114916827</v>
+        <v>130222727</v>
       </c>
       <c r="B2" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Eliasbodarna (Eliasbodarna), Jmt</t>
+          <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>504089</v>
       </c>
       <c r="R2" t="n">
-        <v>7021788</v>
+        <v>7021772</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,12 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,69 +761,91 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114916764</v>
+        <v>130222734</v>
       </c>
       <c r="B3" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Eliasbodarna (Eliasbodarna), Jmt</t>
+          <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504111</v>
+        <v>504221</v>
       </c>
       <c r="R3" t="n">
-        <v>7021755</v>
+        <v>7022011</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,12 +872,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,50 +886,71 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130222731</v>
+        <v>130222735</v>
       </c>
       <c r="B4" t="n">
-        <v>92220</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504091</v>
+        <v>504166</v>
       </c>
       <c r="R4" t="n">
-        <v>7022065</v>
+        <v>7021986</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130222714</v>
+        <v>130222736</v>
       </c>
       <c r="B5" t="n">
-        <v>91761</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,21 +1061,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1092,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504091</v>
+        <v>504081</v>
       </c>
       <c r="R5" t="n">
-        <v>7021759</v>
+        <v>7021794</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130222710</v>
+        <v>130222741</v>
       </c>
       <c r="B6" t="n">
-        <v>91761</v>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,21 +1171,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504160</v>
+        <v>504078</v>
       </c>
       <c r="R6" t="n">
-        <v>7021867</v>
+        <v>7022057</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,6 +1253,21 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1230,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130222749</v>
+        <v>130222742</v>
       </c>
       <c r="B7" t="n">
-        <v>91775</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1296,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1327,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504067</v>
+        <v>504227</v>
       </c>
       <c r="R7" t="n">
-        <v>7021774</v>
+        <v>7022001</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,32 +1395,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130222732</v>
+        <v>130222743</v>
       </c>
       <c r="B8" t="n">
-        <v>92220</v>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1437,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504202</v>
+        <v>504223</v>
       </c>
       <c r="R8" t="n">
-        <v>7022015</v>
+        <v>7022010</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,10 +1520,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130222716</v>
+        <v>130222744</v>
       </c>
       <c r="B9" t="n">
-        <v>91761</v>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,21 +1531,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1562,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504095</v>
+        <v>504178</v>
       </c>
       <c r="R9" t="n">
-        <v>7021805</v>
+        <v>7021976</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,6 +1613,21 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1575,10 +1645,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130222712</v>
+        <v>130222745</v>
       </c>
       <c r="B10" t="n">
-        <v>91761</v>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,21 +1656,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1617,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504057</v>
+        <v>504130</v>
       </c>
       <c r="R10" t="n">
-        <v>7021765</v>
+        <v>7021754</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,6 +1738,21 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1685,10 +1770,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130222736</v>
+        <v>130222746</v>
       </c>
       <c r="B11" t="n">
-        <v>92059</v>
+        <v>91905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,21 +1781,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,10 +1812,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504081</v>
+        <v>503973</v>
       </c>
       <c r="R11" t="n">
-        <v>7021794</v>
+        <v>7021998</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,6 +1863,21 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1795,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130222701</v>
+        <v>130619769</v>
       </c>
       <c r="B12" t="n">
-        <v>83191</v>
+        <v>91905</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,37 +1906,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504090</v>
+        <v>504228</v>
       </c>
       <c r="R12" t="n">
-        <v>7021787</v>
+        <v>7021996</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1863,12 +1960,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På grov torraka av gran, bhd 45 cm</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,56 +1989,50 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130222705</v>
+        <v>130222708</v>
       </c>
       <c r="B13" t="n">
-        <v>91725</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1943,10 +2049,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504210</v>
+        <v>504191</v>
       </c>
       <c r="R13" t="n">
-        <v>7022007</v>
+        <v>7022006</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,10 +2117,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130222702</v>
+        <v>130222709</v>
       </c>
       <c r="B14" t="n">
-        <v>83191</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2022,26 +2128,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2049,10 +2159,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504100</v>
+        <v>504104</v>
       </c>
       <c r="R14" t="n">
-        <v>7021801</v>
+        <v>7021877</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,37 +2227,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222730</v>
+        <v>130222710</v>
       </c>
       <c r="B15" t="n">
-        <v>80220</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2155,10 +2269,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504166</v>
+        <v>504160</v>
       </c>
       <c r="R15" t="n">
-        <v>7021800</v>
+        <v>7021867</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,10 +2337,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130222724</v>
+        <v>130222711</v>
       </c>
       <c r="B16" t="n">
-        <v>57854</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2234,29 +2348,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2266,10 +2379,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504139</v>
+        <v>504154</v>
       </c>
       <c r="R16" t="n">
-        <v>7021798</v>
+        <v>7021848</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,17 +2417,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2338,10 +2447,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130222711</v>
+        <v>130222712</v>
       </c>
       <c r="B17" t="n">
-        <v>91761</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,10 +2489,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>504154</v>
+        <v>504057</v>
       </c>
       <c r="R17" t="n">
-        <v>7021848</v>
+        <v>7021765</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2560,7 @@
         <v>130222713</v>
       </c>
       <c r="B18" t="n">
-        <v>91761</v>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2558,32 +2667,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130222706</v>
+        <v>130222714</v>
       </c>
       <c r="B19" t="n">
-        <v>91725</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,10 +2709,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>504083</v>
+        <v>504091</v>
       </c>
       <c r="R19" t="n">
-        <v>7021773</v>
+        <v>7021759</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2668,10 +2777,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130222700</v>
+        <v>130222715</v>
       </c>
       <c r="B20" t="n">
-        <v>83191</v>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2679,26 +2788,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2706,10 +2819,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>504099</v>
+        <v>504083</v>
       </c>
       <c r="R20" t="n">
-        <v>7021769</v>
+        <v>7021787</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,32 +2887,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130222727</v>
+        <v>130222716</v>
       </c>
       <c r="B21" t="n">
-        <v>92488</v>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2816,10 +2929,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>504089</v>
+        <v>504095</v>
       </c>
       <c r="R21" t="n">
-        <v>7021772</v>
+        <v>7021805</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2867,21 +2980,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2899,40 +2997,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130222720</v>
+        <v>130222747</v>
       </c>
       <c r="B22" t="n">
-        <v>57854</v>
+        <v>91923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2942,10 +3039,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503952</v>
+        <v>504210</v>
       </c>
       <c r="R22" t="n">
-        <v>7022000</v>
+        <v>7022007</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2980,17 +3077,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3014,37 +3107,41 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130222753</v>
+        <v>130222748</v>
       </c>
       <c r="B23" t="n">
-        <v>79211</v>
+        <v>91923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3052,10 +3149,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>504059</v>
+        <v>504123</v>
       </c>
       <c r="R23" t="n">
-        <v>7021781</v>
+        <v>7021748</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3120,37 +3217,41 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130222757</v>
+        <v>130222749</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>91923</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3158,10 +3259,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>504170</v>
+        <v>504067</v>
       </c>
       <c r="R24" t="n">
-        <v>7021800</v>
+        <v>7021774</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3226,10 +3327,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130222725</v>
+        <v>130222731</v>
       </c>
       <c r="B25" t="n">
-        <v>58013</v>
+        <v>92369</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,50 +3338,41 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>504058</v>
+        <v>504091</v>
       </c>
       <c r="R25" t="n">
-        <v>7021715</v>
+        <v>7022065</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3321,12 +3413,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3344,10 +3452,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130222743</v>
+        <v>130222732</v>
       </c>
       <c r="B26" t="n">
-        <v>91757</v>
+        <v>92369</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,21 +3463,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3386,10 +3494,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>504223</v>
+        <v>504202</v>
       </c>
       <c r="R26" t="n">
-        <v>7022010</v>
+        <v>7022015</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3469,10 +3577,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130222755</v>
+        <v>130222733</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>92369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,26 +3588,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3507,10 +3619,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>504177</v>
+        <v>504161</v>
       </c>
       <c r="R27" t="n">
-        <v>7021847</v>
+        <v>7021869</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3558,6 +3670,21 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3575,37 +3702,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130222752</v>
+        <v>130222718</v>
       </c>
       <c r="B28" t="n">
-        <v>79211</v>
+        <v>92632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3613,10 +3744,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>504097</v>
+        <v>504098</v>
       </c>
       <c r="R28" t="n">
-        <v>7021762</v>
+        <v>7022064</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3681,30 +3812,34 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130222750</v>
+        <v>130222719</v>
       </c>
       <c r="B29" t="n">
-        <v>91781</v>
+        <v>92632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
@@ -3719,10 +3854,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>504216</v>
+        <v>504219</v>
       </c>
       <c r="R29" t="n">
-        <v>7022005</v>
+        <v>7022014</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3787,52 +3922,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130222715</v>
+        <v>130619761</v>
       </c>
       <c r="B30" t="n">
-        <v>91761</v>
+        <v>92632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>504083</v>
+        <v>504231</v>
       </c>
       <c r="R30" t="n">
-        <v>7021787</v>
+        <v>7021975</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3859,12 +3987,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På död gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3873,56 +4016,50 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130222746</v>
+        <v>130222704</v>
       </c>
       <c r="B31" t="n">
-        <v>91757</v>
+        <v>91872</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3939,10 +4076,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503973</v>
+        <v>504208</v>
       </c>
       <c r="R31" t="n">
-        <v>7021998</v>
+        <v>7022015</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3990,21 +4127,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4022,32 +4144,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130222742</v>
+        <v>130222705</v>
       </c>
       <c r="B32" t="n">
-        <v>91757</v>
+        <v>91872</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4064,10 +4186,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>504227</v>
+        <v>504210</v>
       </c>
       <c r="R32" t="n">
-        <v>7022001</v>
+        <v>7022007</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4132,32 +4254,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130222734</v>
+        <v>130222706</v>
       </c>
       <c r="B33" t="n">
-        <v>92059</v>
+        <v>91872</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4174,10 +4296,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>504221</v>
+        <v>504083</v>
       </c>
       <c r="R33" t="n">
-        <v>7022011</v>
+        <v>7021773</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4225,21 +4347,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4257,37 +4364,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130222756</v>
+        <v>130222707</v>
       </c>
       <c r="B34" t="n">
-        <v>79211</v>
+        <v>91872</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4295,10 +4406,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>504101</v>
+        <v>504161</v>
       </c>
       <c r="R34" t="n">
-        <v>7021774</v>
+        <v>7021806</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4363,41 +4474,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130222704</v>
+        <v>130222752</v>
       </c>
       <c r="B35" t="n">
-        <v>91725</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4405,10 +4512,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>504208</v>
+        <v>504097</v>
       </c>
       <c r="R35" t="n">
-        <v>7022015</v>
+        <v>7021762</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4473,41 +4580,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130222719</v>
+        <v>130222753</v>
       </c>
       <c r="B36" t="n">
-        <v>92483</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4515,10 +4618,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>504219</v>
+        <v>504059</v>
       </c>
       <c r="R36" t="n">
-        <v>7022014</v>
+        <v>7021781</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4583,42 +4686,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130222722</v>
+        <v>130222754</v>
       </c>
       <c r="B37" t="n">
-        <v>57854</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4626,10 +4724,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503979</v>
+        <v>504081</v>
       </c>
       <c r="R37" t="n">
-        <v>7022007</v>
+        <v>7021796</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4664,17 +4762,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4698,41 +4792,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130222718</v>
+        <v>130222755</v>
       </c>
       <c r="B38" t="n">
-        <v>92483</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4740,10 +4830,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>504098</v>
+        <v>504177</v>
       </c>
       <c r="R38" t="n">
-        <v>7022064</v>
+        <v>7021847</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4808,32 +4898,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130222728</v>
+        <v>130222756</v>
       </c>
       <c r="B39" t="n">
-        <v>80220</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4846,10 +4936,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>504090</v>
+        <v>504101</v>
       </c>
       <c r="R39" t="n">
-        <v>7021781</v>
+        <v>7021774</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4914,32 +5004,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130222729</v>
+        <v>130222757</v>
       </c>
       <c r="B40" t="n">
-        <v>80220</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4952,10 +5042,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>504173</v>
+        <v>504170</v>
       </c>
       <c r="R40" t="n">
-        <v>7021803</v>
+        <v>7021800</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5020,41 +5110,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130222709</v>
+        <v>130222758</v>
       </c>
       <c r="B41" t="n">
-        <v>91761</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5062,10 +5148,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>504104</v>
+        <v>504172</v>
       </c>
       <c r="R41" t="n">
-        <v>7021877</v>
+        <v>7021818</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5130,52 +5216,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130222708</v>
+        <v>130619758</v>
       </c>
       <c r="B42" t="n">
-        <v>91761</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>504191</v>
+        <v>504047</v>
       </c>
       <c r="R42" t="n">
-        <v>7022006</v>
+        <v>7021752</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5202,12 +5281,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5216,76 +5310,63 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130222735</v>
+        <v>130619759</v>
       </c>
       <c r="B43" t="n">
-        <v>92059</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>504166</v>
+        <v>504159</v>
       </c>
       <c r="R43" t="n">
-        <v>7021986</v>
+        <v>7021846</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5312,12 +5393,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5326,91 +5422,63 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130222745</v>
+        <v>130619762</v>
       </c>
       <c r="B44" t="n">
-        <v>91757</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>504130</v>
+        <v>504212</v>
       </c>
       <c r="R44" t="n">
-        <v>7021754</v>
+        <v>7021967</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5437,12 +5505,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5451,91 +5534,63 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130222744</v>
+        <v>130619767</v>
       </c>
       <c r="B45" t="n">
-        <v>91757</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>504178</v>
+        <v>504062</v>
       </c>
       <c r="R45" t="n">
-        <v>7021976</v>
+        <v>7022023</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5562,12 +5617,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5576,49 +5646,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130222733</v>
+        <v>130619768</v>
       </c>
       <c r="B46" t="n">
-        <v>92220</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5626,41 +5675,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>504161</v>
+        <v>504172</v>
       </c>
       <c r="R46" t="n">
-        <v>7021869</v>
+        <v>7022030</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5687,12 +5729,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På torraka av gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5701,71 +5758,50 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130222726</v>
+        <v>130222699</v>
       </c>
       <c r="B47" t="n">
-        <v>80345</v>
+        <v>83307</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5778,10 +5814,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>504106</v>
+        <v>504118</v>
       </c>
       <c r="R47" t="n">
-        <v>7021741</v>
+        <v>7021776</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5846,10 +5882,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130222699</v>
+        <v>130222700</v>
       </c>
       <c r="B48" t="n">
-        <v>83191</v>
+        <v>83307</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5884,10 +5920,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>504118</v>
+        <v>504099</v>
       </c>
       <c r="R48" t="n">
-        <v>7021776</v>
+        <v>7021769</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5952,41 +5988,37 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130222707</v>
+        <v>130222701</v>
       </c>
       <c r="B49" t="n">
-        <v>91725</v>
+        <v>83307</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5994,10 +6026,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>504161</v>
+        <v>504090</v>
       </c>
       <c r="R49" t="n">
-        <v>7021806</v>
+        <v>7021787</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6062,10 +6094,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130222758</v>
+        <v>130222702</v>
       </c>
       <c r="B50" t="n">
-        <v>79211</v>
+        <v>83307</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6073,21 +6105,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6100,10 +6132,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>504172</v>
+        <v>504100</v>
       </c>
       <c r="R50" t="n">
-        <v>7021818</v>
+        <v>7021801</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6171,7 +6203,7 @@
         <v>130222703</v>
       </c>
       <c r="B51" t="n">
-        <v>83191</v>
+        <v>83307</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6274,32 +6306,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130222738</v>
+        <v>130222728</v>
       </c>
       <c r="B52" t="n">
-        <v>78223</v>
+        <v>80336</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228579</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6312,10 +6344,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>504087</v>
+        <v>504090</v>
       </c>
       <c r="R52" t="n">
-        <v>7021791</v>
+        <v>7021781</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6380,32 +6412,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130222737</v>
+        <v>130222729</v>
       </c>
       <c r="B53" t="n">
-        <v>78223</v>
+        <v>80336</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228579</v>
+        <v>6456</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6418,10 +6450,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>504108</v>
+        <v>504173</v>
       </c>
       <c r="R53" t="n">
-        <v>7021877</v>
+        <v>7021803</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6486,42 +6518,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130222723</v>
+        <v>130222730</v>
       </c>
       <c r="B54" t="n">
-        <v>57854</v>
+        <v>80336</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6529,10 +6556,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>504117</v>
+        <v>504166</v>
       </c>
       <c r="R54" t="n">
-        <v>7021735</v>
+        <v>7021800</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6567,17 +6594,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6601,57 +6624,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130222739</v>
+        <v>130619760</v>
       </c>
       <c r="B55" t="n">
-        <v>98957</v>
+        <v>80432</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>504054</v>
+        <v>504274</v>
       </c>
       <c r="R55" t="n">
-        <v>7021735</v>
+        <v>7021941</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6678,17 +6689,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 3 plantor finns på fyndplatsen.</t>
+          <t>På döende eller död sälg</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6697,76 +6718,64 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130222747</v>
+        <v>114916764</v>
       </c>
       <c r="B56" t="n">
-        <v>91775</v>
+        <v>80461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Eliasbodarna, Jmt</t>
+          <t>Eliasbodarna, Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>504210</v>
+        <v>504111</v>
       </c>
       <c r="R56" t="n">
-        <v>7022007</v>
+        <v>7021755</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6793,12 +6802,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6807,56 +6816,50 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Joel Schill</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Joel Schill</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130222754</v>
+        <v>130222726</v>
       </c>
       <c r="B57" t="n">
-        <v>79211</v>
+        <v>80461</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6869,10 +6872,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>504081</v>
+        <v>504106</v>
       </c>
       <c r="R57" t="n">
-        <v>7021796</v>
+        <v>7021741</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6937,46 +6940,42 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130222740</v>
+        <v>130222720</v>
       </c>
       <c r="B58" t="n">
-        <v>98957</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6984,10 +6983,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>504087</v>
+        <v>503952</v>
       </c>
       <c r="R58" t="n">
-        <v>7021765</v>
+        <v>7022000</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7024,7 +7023,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 8 plantor på fyndplatsen.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7033,7 +7032,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7057,10 +7055,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130222741</v>
+        <v>130222721</v>
       </c>
       <c r="B59" t="n">
-        <v>91757</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7068,28 +7066,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7099,10 +7098,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>504078</v>
+        <v>503954</v>
       </c>
       <c r="R59" t="n">
-        <v>7022057</v>
+        <v>7021984</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7137,34 +7136,23 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7182,10 +7170,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130222748</v>
+        <v>130222722</v>
       </c>
       <c r="B60" t="n">
-        <v>91775</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7193,28 +7181,29 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7224,10 +7213,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>504123</v>
+        <v>503979</v>
       </c>
       <c r="R60" t="n">
-        <v>7021748</v>
+        <v>7022007</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7262,13 +7251,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7292,10 +7285,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130222751</v>
+        <v>130222723</v>
       </c>
       <c r="B61" t="n">
-        <v>91781</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7303,24 +7296,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7330,10 +7328,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>504218</v>
+        <v>504117</v>
       </c>
       <c r="R61" t="n">
-        <v>7022019</v>
+        <v>7021735</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7368,34 +7366,23 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7413,10 +7400,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130222721</v>
+        <v>130222724</v>
       </c>
       <c r="B62" t="n">
-        <v>57854</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7446,7 +7433,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7456,10 +7443,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503954</v>
+        <v>504139</v>
       </c>
       <c r="R62" t="n">
-        <v>7021984</v>
+        <v>7021798</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7496,7 +7483,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7528,10 +7515,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130619758</v>
+        <v>130619765</v>
       </c>
       <c r="B63" t="n">
-        <v>79243</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7539,21 +7526,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7563,10 +7550,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>504047</v>
+        <v>503938</v>
       </c>
       <c r="R63" t="n">
-        <v>7021752</v>
+        <v>7021990</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7598,7 +7585,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7608,12 +7595,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack, äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7640,10 +7627,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130619765</v>
+        <v>130619766</v>
       </c>
       <c r="B64" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7675,10 +7662,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503938</v>
+        <v>503958</v>
       </c>
       <c r="R64" t="n">
-        <v>7021990</v>
+        <v>7021988</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7710,7 +7697,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7720,12 +7707,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack, äldre</t>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7752,45 +7739,53 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130619759</v>
+        <v>130619764</v>
       </c>
       <c r="B65" t="n">
-        <v>79243</v>
+        <v>57132</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>504159</v>
+        <v>504059</v>
       </c>
       <c r="R65" t="n">
-        <v>7021846</v>
+        <v>7022053</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7822,7 +7817,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7832,12 +7827,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7864,10 +7859,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130619760</v>
+        <v>114916827</v>
       </c>
       <c r="B66" t="n">
-        <v>80348</v>
+        <v>58114</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7875,34 +7870,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Eliasbodarna, Jmt</t>
+          <t>Eliasbodarna, Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>504274</v>
+        <v>504089</v>
       </c>
       <c r="R66" t="n">
-        <v>7021941</v>
+        <v>7021788</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7929,27 +7929,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:25</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På döende eller död sälg</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7964,22 +7949,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Joel Schill</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Joel Schill</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130619762</v>
+        <v>130222725</v>
       </c>
       <c r="B67" t="n">
-        <v>79243</v>
+        <v>58114</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7987,34 +7972,50 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>504212</v>
+        <v>504058</v>
       </c>
       <c r="R67" t="n">
-        <v>7021967</v>
+        <v>7021715</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8041,27 +8042,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8072,61 +8058,78 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130619761</v>
+        <v>130222739</v>
       </c>
       <c r="B68" t="n">
-        <v>92530</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>504231</v>
+        <v>504054</v>
       </c>
       <c r="R68" t="n">
-        <v>7021975</v>
+        <v>7021735</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8153,27 +8156,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>På död gran</t>
+          <t>Minst 3 plantor finns på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8182,63 +8175,81 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130619769</v>
+        <v>130222740</v>
       </c>
       <c r="B69" t="n">
-        <v>91804</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>504228</v>
+        <v>504087</v>
       </c>
       <c r="R69" t="n">
-        <v>7021996</v>
+        <v>7021765</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8265,27 +8276,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På grov torraka av gran, bhd 45 cm</t>
+          <t>Minst 8 plantor på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8294,28 +8295,34 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130619764</v>
+        <v>130222737</v>
       </c>
       <c r="B70" t="n">
-        <v>57064</v>
+        <v>78339</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8323,31 +8330,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102612</v>
+        <v>228579</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8355,10 +8357,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>504059</v>
+        <v>504108</v>
       </c>
       <c r="R70" t="n">
-        <v>7022053</v>
+        <v>7021877</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8385,27 +8387,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:39</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Sittande högt upp gammal björk, i skog dominerad av barrträd.</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8414,28 +8401,34 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130619768</v>
+        <v>130222738</v>
       </c>
       <c r="B71" t="n">
-        <v>79243</v>
+        <v>78339</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8443,34 +8436,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Eliasbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>504172</v>
+        <v>504087</v>
       </c>
       <c r="R71" t="n">
-        <v>7022030</v>
+        <v>7021791</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8497,27 +8493,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På torraka av gran</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8526,245 +8507,27 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>130619767</v>
-      </c>
-      <c r="B72" t="n">
-        <v>79243</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Eliasbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>504062</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7022023</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Elin Albrechtsson</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Elin Albrechtsson</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>130619766</v>
-      </c>
-      <c r="B73" t="n">
-        <v>57884</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Eliasbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>503958</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7021988</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Elin Albrechtsson</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Elin Albrechtsson</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59147-2025 artfynd.xlsx
+++ b/artfynd/A 59147-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222727</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222734</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222735</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1157,6 +1177,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222736</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1282,6 +1307,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222741</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1392,6 +1422,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222742</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1517,6 +1552,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222743</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1642,6 +1682,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222744</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1767,6 +1812,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222745</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1892,6 +1942,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222746</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2004,6 +2059,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130619769</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2114,6 +2174,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222708</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2224,6 +2289,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222709</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2334,6 +2404,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222710</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2444,6 +2519,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222711</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2554,6 +2634,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222712</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2664,6 +2749,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222713</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2774,6 +2864,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222714</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2884,6 +2979,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222715</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2994,6 +3094,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222716</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3104,6 +3209,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222747</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3214,6 +3324,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222748</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3324,6 +3439,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222749</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3449,6 +3569,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222731</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3574,6 +3699,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222732</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3699,6 +3829,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222733</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3809,6 +3944,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222718</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3919,6 +4059,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222719</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4031,6 +4176,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130619761</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4141,6 +4291,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222704</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4251,6 +4406,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222705</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4361,6 +4521,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222706</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4471,6 +4636,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222707</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4577,6 +4747,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222752</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4683,6 +4858,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222753</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4789,6 +4969,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222754</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4895,6 +5080,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222755</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5001,6 +5191,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222756</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5107,6 +5302,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222757</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5213,6 +5413,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222758</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5325,6 +5530,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130619758</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5437,6 +5647,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130619759</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5549,6 +5764,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130619762</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5661,6 +5881,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130619767</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5773,6 +5998,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130619768</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5879,6 +6109,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222699</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5985,6 +6220,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222700</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6091,6 +6331,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222701</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6197,6 +6442,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222702</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6303,6 +6553,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222703</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6409,6 +6664,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222728</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6515,6 +6775,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222729</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6621,6 +6886,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222730</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6733,6 +7003,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130619760</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6831,6 +7106,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114916764</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6937,6 +7217,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222726</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7052,6 +7337,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222720</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7167,6 +7457,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222721</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7282,6 +7577,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222722</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7397,6 +7697,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222723</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7512,6 +7817,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222724</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7624,6 +7934,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130619765</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7736,6 +8051,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130619766</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7856,6 +8176,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130619764</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7958,6 +8283,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114916827</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8076,6 +8406,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222725</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8196,6 +8531,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222739</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8316,6 +8656,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222740</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8422,6 +8767,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222737</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8528,8 +8878,85 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130222738</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>